--- a/model/outputs/gip_model.xlsx
+++ b/model/outputs/gip_model.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC210"/>
+  <dimension ref="A1:AC225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,13 +717,13 @@
         <v>41.47199999999998</v>
       </c>
       <c r="AA2" t="n">
-        <v>262877.99148</v>
+        <v>245894.4846</v>
       </c>
       <c r="AB2" t="n">
-        <v>262877.99148</v>
+        <v>254264.9166</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8370.432000000001</v>
       </c>
     </row>
     <row r="3">
@@ -810,13 +810,13 @@
         <v>104.976</v>
       </c>
       <c r="AA3" t="n">
-        <v>262877.99148</v>
+        <v>246679.2126</v>
       </c>
       <c r="AB3" t="n">
-        <v>262877.99148</v>
+        <v>253741.7646</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>7062.551999999996</v>
       </c>
     </row>
     <row r="4">
@@ -903,13 +903,13 @@
         <v>25.92000000000002</v>
       </c>
       <c r="AA4" t="n">
-        <v>262877.99148</v>
+        <v>245545.7166</v>
       </c>
       <c r="AB4" t="n">
-        <v>262877.99148</v>
+        <v>256008.7566</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>10463.03999999998</v>
       </c>
     </row>
     <row r="5">
@@ -996,10 +996,10 @@
         <v>67.09770000000003</v>
       </c>
       <c r="AA5" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB5" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>81.648</v>
       </c>
       <c r="AA6" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB6" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>59.37300000000002</v>
       </c>
       <c r="AA7" t="n">
-        <v>262877.99148</v>
+        <v>248297.7141</v>
       </c>
       <c r="AB7" t="n">
-        <v>262877.99148</v>
+        <v>249769.0791</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1471.364999999991</v>
       </c>
     </row>
     <row r="8">
@@ -1275,10 +1275,10 @@
         <v>26.82604800000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB8" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1368,13 +1368,13 @@
         <v>37.896546</v>
       </c>
       <c r="AA9" t="n">
-        <v>236040.92576</v>
+        <v>223734.6192</v>
       </c>
       <c r="AB9" t="n">
-        <v>276296.52434</v>
+        <v>261682.7853</v>
       </c>
       <c r="AC9" t="n">
-        <v>40255.59858000002</v>
+        <v>37948.16610000003</v>
       </c>
     </row>
     <row r="10">
@@ -1461,10 +1461,10 @@
         <v>20.73600000000002</v>
       </c>
       <c r="AA10" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB10" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1554,10 +1554,10 @@
         <v>14.39999999999998</v>
       </c>
       <c r="AA11" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB11" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1647,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB12" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>25.264364</v>
       </c>
       <c r="AA13" t="n">
-        <v>243802.52576</v>
+        <v>231496.2192</v>
       </c>
       <c r="AB13" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC13" t="n">
-        <v>19075.46571999998</v>
+        <v>17537.17739999999</v>
       </c>
     </row>
     <row r="14">
@@ -1833,10 +1833,10 @@
         <v>12.96000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB14" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>20.21149119999998</v>
       </c>
       <c r="AA15" t="n">
-        <v>248262.365192</v>
+        <v>235033.08564</v>
       </c>
       <c r="AB15" t="n">
-        <v>277493.617768</v>
+        <v>263033.70756</v>
       </c>
       <c r="AC15" t="n">
-        <v>29231.252576</v>
+        <v>28000.62192000001</v>
       </c>
     </row>
     <row r="16">
@@ -2019,13 +2019,13 @@
         <v>34.99200000000002</v>
       </c>
       <c r="AA16" t="n">
-        <v>262877.99148</v>
+        <v>247856.3046</v>
       </c>
       <c r="AB16" t="n">
-        <v>262877.99148</v>
+        <v>250210.4886</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2354.184000000008</v>
       </c>
     </row>
     <row r="17">
@@ -2112,10 +2112,10 @@
         <v>33.858</v>
       </c>
       <c r="AA17" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB17" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2205,13 +2205,13 @@
         <v>18.89568</v>
       </c>
       <c r="AA18" t="n">
-        <v>262877.99148</v>
+        <v>248248.6686</v>
       </c>
       <c r="AB18" t="n">
-        <v>262877.99148</v>
+        <v>250602.8526</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2354.184000000008</v>
       </c>
     </row>
     <row r="19">
@@ -2298,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB19" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         <v>19.791</v>
       </c>
       <c r="AA20" t="n">
-        <v>262877.99148</v>
+        <v>248739.1236</v>
       </c>
       <c r="AB20" t="n">
-        <v>262877.99148</v>
+        <v>249229.5786</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>490.4550000000163</v>
       </c>
     </row>
     <row r="21">
@@ -2484,13 +2484,13 @@
         <v>8.100000000000023</v>
       </c>
       <c r="AA21" t="n">
-        <v>262877.99148</v>
+        <v>248052.4866</v>
       </c>
       <c r="AB21" t="n">
-        <v>262877.99148</v>
+        <v>249687.3366</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1634.849999999977</v>
       </c>
     </row>
     <row r="22">
@@ -2577,13 +2577,13 @@
         <v>6.652800000000013</v>
       </c>
       <c r="AA22" t="n">
-        <v>262877.99148</v>
+        <v>248926.5864</v>
       </c>
       <c r="AB22" t="n">
-        <v>262877.99148</v>
+        <v>249262.2756</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>335.6891999999934</v>
       </c>
     </row>
     <row r="23">
@@ -2670,13 +2670,13 @@
         <v>9.216000000000008</v>
       </c>
       <c r="AA23" t="n">
-        <v>262877.99148</v>
+        <v>247080.2958</v>
       </c>
       <c r="AB23" t="n">
-        <v>262877.99148</v>
+        <v>250986.4974</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3906.2016</v>
       </c>
     </row>
     <row r="24">
@@ -2763,13 +2763,13 @@
         <v>5.400000000000006</v>
       </c>
       <c r="AA24" t="n">
-        <v>262877.99148</v>
+        <v>247725.5166</v>
       </c>
       <c r="AB24" t="n">
-        <v>262877.99148</v>
+        <v>249905.3166</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2179.800000000017</v>
       </c>
     </row>
     <row r="25">
@@ -2856,10 +2856,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB25" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -2949,13 +2949,13 @@
         <v>5.644800000000004</v>
       </c>
       <c r="AA26" t="n">
-        <v>262877.99148</v>
+        <v>248346.7596</v>
       </c>
       <c r="AB26" t="n">
-        <v>262877.99148</v>
+        <v>249948.9126</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1602.152999999991</v>
       </c>
     </row>
     <row r="27">
@@ -3042,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB27" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3135,13 +3135,13 @@
         <v>6.236999999999995</v>
       </c>
       <c r="AA28" t="n">
-        <v>262877.99148</v>
+        <v>248850.2934</v>
       </c>
       <c r="AB28" t="n">
-        <v>262877.99148</v>
+        <v>249308.0514</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>457.7580000000016</v>
       </c>
     </row>
     <row r="29">
@@ -3228,10 +3228,10 @@
         <v>8.618400000000008</v>
       </c>
       <c r="AA29" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB29" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB30" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -3414,10 +3414,10 @@
         <v>5.292000000000002</v>
       </c>
       <c r="AA31" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB31" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -3507,10 +3507,10 @@
         <v>8.398079999999993</v>
       </c>
       <c r="AA32" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB32" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -3600,10 +3600,10 @@
         <v>6.560190000000006</v>
       </c>
       <c r="AA33" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB33" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -3693,13 +3693,13 @@
         <v>10.20600000000002</v>
       </c>
       <c r="AA34" t="n">
-        <v>262877.99148</v>
+        <v>248837.2146</v>
       </c>
       <c r="AB34" t="n">
-        <v>262877.99148</v>
+        <v>249425.7606</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>588.545999999973</v>
       </c>
     </row>
     <row r="35">
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB35" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -3879,13 +3879,13 @@
         <v>6.298560000000009</v>
       </c>
       <c r="AA36" t="n">
-        <v>262877.99148</v>
+        <v>248641.0326</v>
       </c>
       <c r="AB36" t="n">
-        <v>262877.99148</v>
+        <v>249425.7606</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>784.7280000000028</v>
       </c>
     </row>
     <row r="37">
@@ -3972,13 +3972,13 @@
         <v>4.319999999999993</v>
       </c>
       <c r="AA37" t="n">
-        <v>262877.99148</v>
+        <v>248542.9416</v>
       </c>
       <c r="AB37" t="n">
-        <v>262877.99148</v>
+        <v>249523.8516</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>980.9100000000035</v>
       </c>
     </row>
     <row r="38">
@@ -4065,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB38" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -4158,13 +4158,13 @@
         <v>3.965472000000005</v>
       </c>
       <c r="AA39" t="n">
-        <v>262877.99148</v>
+        <v>248667.1902</v>
       </c>
       <c r="AB39" t="n">
-        <v>262877.99148</v>
+        <v>249521.6718</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>854.4815999999992</v>
       </c>
     </row>
     <row r="40">
@@ -4251,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB40" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -4344,13 +4344,13 @@
         <v>3.118500000000012</v>
       </c>
       <c r="AA41" t="n">
-        <v>262877.99148</v>
+        <v>248902.6086</v>
       </c>
       <c r="AB41" t="n">
-        <v>262877.99148</v>
+        <v>249131.4876</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>228.8790000000154</v>
       </c>
     </row>
     <row r="42">
@@ -4437,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB42" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -4530,13 +4530,13 @@
         <v>2.268000000000001</v>
       </c>
       <c r="AA43" t="n">
-        <v>262877.99148</v>
+        <v>248968.0026</v>
       </c>
       <c r="AB43" t="n">
-        <v>262877.99148</v>
+        <v>249082.4421</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>114.4394999999786</v>
       </c>
     </row>
     <row r="44">
@@ -4623,13 +4623,13 @@
         <v>2.879999999999995</v>
       </c>
       <c r="AA44" t="n">
-        <v>262877.99148</v>
+        <v>248423.0526</v>
       </c>
       <c r="AB44" t="n">
-        <v>262877.99148</v>
+        <v>249643.7406</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1220.687999999995</v>
       </c>
     </row>
     <row r="45">
@@ -4716,10 +4716,10 @@
         <v>2.879999999999995</v>
       </c>
       <c r="AA45" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB45" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>2.073599999999999</v>
       </c>
       <c r="AA46" t="n">
-        <v>262877.99148</v>
+        <v>248739.1236</v>
       </c>
       <c r="AB46" t="n">
-        <v>262877.99148</v>
+        <v>249327.6696</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>588.5460000000021</v>
       </c>
     </row>
     <row r="47">
@@ -4902,10 +4902,10 @@
         <v>4.860000000000014</v>
       </c>
       <c r="AA47" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB47" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -4995,13 +4995,13 @@
         <v>0.7087500000000091</v>
       </c>
       <c r="AA48" t="n">
-        <v>182351.39148</v>
+        <v>168343.3116</v>
       </c>
       <c r="AB48" t="n">
-        <v>383667.89148</v>
+        <v>370068.5241</v>
       </c>
       <c r="AC48" t="n">
-        <v>201316.5</v>
+        <v>201725.2125</v>
       </c>
     </row>
     <row r="49">
@@ -5088,10 +5088,10 @@
         <v>6.11099999999999</v>
       </c>
       <c r="AA49" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB49" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -5181,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB50" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -5274,13 +5274,13 @@
         <v>3.401999999999987</v>
       </c>
       <c r="AA51" t="n">
-        <v>262877.99148</v>
+        <v>248935.3056</v>
       </c>
       <c r="AB51" t="n">
-        <v>262877.99148</v>
+        <v>249131.4876</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>196.1820000000007</v>
       </c>
     </row>
     <row r="52">
@@ -5367,10 +5367,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB52" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -5460,13 +5460,13 @@
         <v>1.456704000000002</v>
       </c>
       <c r="AA53" t="n">
-        <v>262877.99148</v>
+        <v>248876.451</v>
       </c>
       <c r="AB53" t="n">
-        <v>262877.99148</v>
+        <v>249190.3422</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>313.8911999999837</v>
       </c>
     </row>
     <row r="54">
@@ -5553,13 +5553,13 @@
         <v>1.439999999999998</v>
       </c>
       <c r="AA54" t="n">
-        <v>262877.99148</v>
+        <v>248837.2146</v>
       </c>
       <c r="AB54" t="n">
-        <v>262877.99148</v>
+        <v>249164.1846</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>326.9699999999721</v>
       </c>
     </row>
     <row r="55">
@@ -5646,13 +5646,13 @@
         <v>0.1134000000000128</v>
       </c>
       <c r="AA55" t="n">
-        <v>256491.30348</v>
+        <v>242036.3646</v>
       </c>
       <c r="AB55" t="n">
-        <v>275651.36748</v>
+        <v>263027.4606</v>
       </c>
       <c r="AC55" t="n">
-        <v>19160.06400000001</v>
+        <v>20991.09599999999</v>
       </c>
     </row>
     <row r="56">
@@ -5739,13 +5739,13 @@
         <v>0.1270079999999894</v>
       </c>
       <c r="AA56" t="n">
-        <v>262877.99148</v>
+        <v>248960.15532</v>
       </c>
       <c r="AB56" t="n">
-        <v>262877.99148</v>
+        <v>249155.4654</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>195.3100799999957</v>
       </c>
     </row>
     <row r="57">
@@ -5832,10 +5832,10 @@
         <v>1.295999999999992</v>
       </c>
       <c r="AA57" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB57" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB58" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -6018,13 +6018,13 @@
         <v>0.3240000000000123</v>
       </c>
       <c r="AA59" t="n">
-        <v>216862.79148</v>
+        <v>203018.1966</v>
       </c>
       <c r="AB59" t="n">
-        <v>308893.19148</v>
+        <v>295048.5966</v>
       </c>
       <c r="AC59" t="n">
-        <v>92030.39999999997</v>
+        <v>92030.39999999999</v>
       </c>
     </row>
     <row r="60">
@@ -6111,10 +6111,10 @@
         <v>0.9676800000000014</v>
       </c>
       <c r="AA60" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB60" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -6204,10 +6204,10 @@
         <v>0.2835000000000036</v>
       </c>
       <c r="AA61" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB61" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -6297,13 +6297,13 @@
         <v>0.07560000000000855</v>
       </c>
       <c r="AA62" t="n">
-        <v>256491.30348</v>
+        <v>242646.7086</v>
       </c>
       <c r="AB62" t="n">
-        <v>269264.67948</v>
+        <v>255420.0846</v>
       </c>
       <c r="AC62" t="n">
-        <v>12773.37600000005</v>
+        <v>12773.37599999999</v>
       </c>
     </row>
     <row r="63">
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB63" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -6483,10 +6483,10 @@
         <v>3.016439999999989</v>
       </c>
       <c r="AA64" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB64" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -6576,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB65" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>0.1890000000000214</v>
       </c>
       <c r="AA66" t="n">
-        <v>230667.35148</v>
+        <v>216757.3626</v>
       </c>
       <c r="AB66" t="n">
-        <v>284351.75148</v>
+        <v>270550.7526</v>
       </c>
       <c r="AC66" t="n">
-        <v>53684.39999999999</v>
+        <v>53793.39000000001</v>
       </c>
     </row>
     <row r="67">
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB67" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -6855,10 +6855,10 @@
         <v>0.04032000000000835</v>
       </c>
       <c r="AA68" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB68" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -6948,13 +6948,13 @@
         <v>0.03780000000000427</v>
       </c>
       <c r="AA69" t="n">
-        <v>259228.45548</v>
+        <v>245035.0926</v>
       </c>
       <c r="AB69" t="n">
-        <v>265615.14348</v>
+        <v>252032.1246</v>
       </c>
       <c r="AC69" t="n">
-        <v>6386.687999999966</v>
+        <v>6997.031999999977</v>
       </c>
     </row>
     <row r="70">
@@ -7041,13 +7041,13 @@
         <v>0.03969000000000733</v>
       </c>
       <c r="AA70" t="n">
-        <v>262877.99148</v>
+        <v>248998.5198</v>
       </c>
       <c r="AB70" t="n">
-        <v>262877.99148</v>
+        <v>249059.5542</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>61.03439999997499</v>
       </c>
     </row>
     <row r="71">
@@ -7134,10 +7134,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB71" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -7227,10 +7227,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB72" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>257056.79148</v>
+        <v>243212.1966</v>
       </c>
       <c r="AB73" t="n">
-        <v>268699.19148</v>
+        <v>254854.5966</v>
       </c>
       <c r="AC73" t="n">
-        <v>11642.39999999999</v>
+        <v>11642.40000000002</v>
       </c>
     </row>
     <row r="74">
@@ -7413,13 +7413,13 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>247354.79148</v>
+        <v>233510.1966</v>
       </c>
       <c r="AB74" t="n">
-        <v>274520.39148</v>
+        <v>260675.7966</v>
       </c>
       <c r="AC74" t="n">
-        <v>27165.60000000001</v>
+        <v>27165.60000000003</v>
       </c>
     </row>
     <row r="75">
@@ -7506,10 +7506,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB75" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -7599,10 +7599,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB76" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -7692,10 +7692,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB77" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -7785,10 +7785,10 @@
         <v>7.128000000000014</v>
       </c>
       <c r="AA78" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB78" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -7878,10 +7878,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB79" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -7971,10 +7971,10 @@
         <v>22.113</v>
       </c>
       <c r="AA80" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB80" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -8064,10 +8064,10 @@
         <v>19.44</v>
       </c>
       <c r="AA81" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB81" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -8157,10 +8157,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB82" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -8250,10 +8250,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB83" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB84" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -8436,10 +8436,10 @@
         <v>1.512</v>
       </c>
       <c r="AA85" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB85" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB86" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         <v>0.6803999999999917</v>
       </c>
       <c r="AA87" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB87" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -8715,10 +8715,10 @@
         <v>0.514080000000007</v>
       </c>
       <c r="AA88" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB88" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -8808,10 +8808,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB89" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -8901,10 +8901,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB90" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -8994,10 +8994,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB91" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -9087,10 +9087,10 @@
         <v>7.77600000000001</v>
       </c>
       <c r="AA92" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB92" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -9180,10 +9180,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB93" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -9273,10 +9273,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB94" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB95" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -9459,10 +9459,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB96" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -9552,10 +9552,10 @@
         <v>0.9071999999999889</v>
       </c>
       <c r="AA97" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB97" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB98" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>5.254200000000026</v>
       </c>
       <c r="AA99" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB99" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -9831,10 +9831,10 @@
         <v>4.762799999999999</v>
       </c>
       <c r="AA100" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB100" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -9924,10 +9924,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB101" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -10017,10 +10017,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB102" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB103" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -10203,10 +10203,10 @@
         <v>0.2721599999999853</v>
       </c>
       <c r="AA104" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB104" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB105" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>1.050839999999994</v>
       </c>
       <c r="AA106" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB106" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -10482,10 +10482,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB107" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -10575,10 +10575,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB108" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -10668,10 +10668,10 @@
         <v>1.360800000000012</v>
       </c>
       <c r="AA109" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB109" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -10761,10 +10761,10 @@
         <v>0.9071999999999889</v>
       </c>
       <c r="AA110" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB110" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -10854,10 +10854,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB111" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB112" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -11040,10 +11040,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB113" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -11133,10 +11133,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB114" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -11226,10 +11226,10 @@
         <v>9.216000000000008</v>
       </c>
       <c r="AA115" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB115" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -11319,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB116" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -11412,10 +11412,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB117" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -11505,10 +11505,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB118" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -11598,10 +11598,10 @@
         <v>1.866240000000005</v>
       </c>
       <c r="AA119" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB119" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -11691,10 +11691,10 @@
         <v>3.499199999999973</v>
       </c>
       <c r="AA120" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB120" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -11784,10 +11784,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB121" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -11877,10 +11877,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB122" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -11970,10 +11970,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB123" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB124" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -12156,10 +12156,10 @@
         <v>3.240000000000009</v>
       </c>
       <c r="AA125" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB125" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -12249,10 +12249,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB126" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -12342,10 +12342,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB127" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -12435,10 +12435,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB128" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -12528,10 +12528,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB129" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -12621,10 +12621,10 @@
         <v>2.124359999999996</v>
       </c>
       <c r="AA130" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB130" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -12714,10 +12714,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB131" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -12807,10 +12807,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB132" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -12900,10 +12900,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB133" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -12993,10 +12993,10 @@
         <v>6.912000000000006</v>
       </c>
       <c r="AA134" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB134" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB135" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -13179,10 +13179,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB136" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -13272,10 +13272,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB137" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -13365,10 +13365,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB138" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -13458,10 +13458,10 @@
         <v>2.879999999999995</v>
       </c>
       <c r="AA139" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB139" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB140" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -13644,10 +13644,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB141" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB142" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -13830,10 +13830,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB143" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -13923,10 +13923,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB144" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -14016,10 +14016,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB145" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -14109,10 +14109,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB146" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -14202,10 +14202,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB147" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -14295,34 +14295,34 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB148" t="n">
-        <v>265623.12684</v>
+        <v>250898.2398</v>
       </c>
       <c r="AC148" t="n">
-        <v>2745.135360000073</v>
+        <v>1864.843200000003</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A-135</t>
+          <t>A-136</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Solar PV capacity of the park mini-grids at full build-out</t>
+          <t>Solar PV capacity factor in Mogadishu</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>20</v>
+        <v>0.18</v>
       </c>
       <c r="D149" t="n">
-        <v>40</v>
+        <v>0.204</v>
       </c>
       <c r="E149" t="n">
-        <v>60</v>
+        <v>0.22</v>
       </c>
       <c r="F149" t="n">
         <v>89.76052799999999</v>
@@ -14388,34 +14388,34 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>240618.62124</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB149" t="n">
-        <v>285137.36172</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC149" t="n">
-        <v>44518.74047999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A-136</t>
+          <t>A-137</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Solar PV capacity factor in Mogadishu</t>
+          <t>Share of solar output that displaces diesel generation</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.18</v>
+        <v>0.8</v>
       </c>
       <c r="D150" t="n">
-        <v>0.204</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
         <v>89.76052799999999</v>
@@ -14481,34 +14481,34 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>257640.4926</v>
+        <v>242898.56748</v>
       </c>
       <c r="AB150" t="n">
-        <v>266369.6574</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC150" t="n">
-        <v>8729.16479999997</v>
+        <v>6134.82911999998</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A-137</t>
+          <t>A-138</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Share of solar output that displaces diesel generation</t>
+          <t>Solar PV capital cost</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.8</v>
+        <v>600</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>900</v>
       </c>
       <c r="F151" t="n">
         <v>89.76052799999999</v>
@@ -14574,34 +14574,34 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>253974.243384</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB151" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC151" t="n">
-        <v>8903.748095999967</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A-138</t>
+          <t>A-139</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Solar PV capital cost</t>
+          <t>Battery power capacity per kW of PV</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>600</v>
+        <v>0.3</v>
       </c>
       <c r="D152" t="n">
-        <v>700</v>
+        <v>0.5</v>
       </c>
       <c r="E152" t="n">
-        <v>900</v>
+        <v>0.8</v>
       </c>
       <c r="F152" t="n">
         <v>89.76052799999999</v>
@@ -14667,10 +14667,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB152" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -14679,22 +14679,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A-139</t>
+          <t>A-140</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Battery power capacity per kW of PV</t>
+          <t>Battery storage capital cost (4 hours)</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.3</v>
+        <v>600</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5</v>
+        <v>800</v>
       </c>
       <c r="E153" t="n">
-        <v>0.8</v>
+        <v>1000</v>
       </c>
       <c r="F153" t="n">
         <v>89.76052799999999</v>
@@ -14760,10 +14760,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB153" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -14772,22 +14772,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A-140</t>
+          <t>A-142</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Battery storage capital cost (4 hours)</t>
+          <t>Full cost of diesel generation displaced</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="D154" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E154" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="F154" t="n">
         <v>89.76052799999999</v>
@@ -14853,10 +14853,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB154" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -14865,22 +14865,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A-142</t>
+          <t>A-143</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Full cost of diesel generation displaced</t>
+          <t>Diesel pump price</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>350</v>
+        <v>0.6</v>
       </c>
       <c r="D155" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>550</v>
+        <v>1.5</v>
       </c>
       <c r="F155" t="n">
         <v>89.76052799999999</v>
@@ -14946,10 +14946,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB155" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -14958,22 +14958,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A-143</t>
+          <t>A-144</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Diesel pump price</t>
+          <t>Discount rate for annualising capital costs (MCS cost per tonne)</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.6</v>
+        <v>0.08</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E156" t="n">
-        <v>1.5</v>
+        <v>0.14</v>
       </c>
       <c r="F156" t="n">
         <v>89.76052799999999</v>
@@ -15039,10 +15039,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB156" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -15051,22 +15051,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A-144</t>
+          <t>A-145</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Discount rate for annualising capital costs (MCS cost per tonne)</t>
+          <t>Diesel irrigation pumps replaced by solar pumps by 2032</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0.08</v>
+        <v>1000</v>
       </c>
       <c r="D157" t="n">
-        <v>0.1</v>
+        <v>2000</v>
       </c>
       <c r="E157" t="n">
-        <v>0.14</v>
+        <v>4000</v>
       </c>
       <c r="F157" t="n">
         <v>89.76052799999999</v>
@@ -15132,31 +15132,31 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>262877.99148</v>
+        <v>243044.9091</v>
       </c>
       <c r="AB157" t="n">
-        <v>262877.99148</v>
+        <v>261010.3716</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>17965.46250000002</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A-145</t>
+          <t>A-146</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Diesel irrigation pumps replaced by solar pumps by 2032</t>
+          <t>Diesel use per irrigation pump a year</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D158" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E158" t="n">
         <v>4000</v>
@@ -15225,34 +15225,34 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>256889.50398</v>
+        <v>244242.6066</v>
       </c>
       <c r="AB158" t="n">
-        <v>274854.96648</v>
+        <v>256219.5816</v>
       </c>
       <c r="AC158" t="n">
-        <v>17965.46250000002</v>
+        <v>11976.97499999998</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A-146</t>
+          <t>A-147</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Diesel use per irrigation pump a year</t>
+          <t>Solar pumping system cost per pump replaced</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="D159" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="E159" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F159" t="n">
         <v>89.76052799999999</v>
@@ -15318,34 +15318,34 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>258087.20148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB159" t="n">
-        <v>270064.17648</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC159" t="n">
-        <v>11976.97500000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A-147</t>
+          <t>A-148</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Solar pumping system cost per pump replaced</t>
+          <t>Solar pump system life</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4000</v>
+        <v>10</v>
       </c>
       <c r="D160" t="n">
-        <v>7000</v>
+        <v>15</v>
       </c>
       <c r="E160" t="n">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="F160" t="n">
         <v>89.76052799999999</v>
@@ -15411,10 +15411,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB160" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -15423,22 +15423,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A-148</t>
+          <t>A-149</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Solar pump system life</t>
+          <t>Mogadishu waste deposited at the managed landfill with gas capture (full operation)</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>10</v>
+        <v>150000</v>
       </c>
       <c r="D161" t="n">
-        <v>15</v>
+        <v>230000</v>
       </c>
       <c r="E161" t="n">
-        <v>20</v>
+        <v>450000</v>
       </c>
       <c r="F161" t="n">
         <v>89.76052799999999</v>
@@ -15504,34 +15504,34 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>262877.99148</v>
+        <v>239241.3966</v>
       </c>
       <c r="AB161" t="n">
-        <v>262877.99148</v>
+        <v>275961.3966</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>36720</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A-149</t>
+          <t>A-150</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mogadishu waste deposited at the managed landfill with gas capture (full operation)</t>
+          <t>Landfill gas collection and destruction efficiency over the site's life</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>150000</v>
+        <v>0.3</v>
       </c>
       <c r="D162" t="n">
-        <v>230000</v>
+        <v>0.5</v>
       </c>
       <c r="E162" t="n">
-        <v>450000</v>
+        <v>0.7</v>
       </c>
       <c r="F162" t="n">
         <v>89.76052799999999</v>
@@ -15597,34 +15597,34 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>253085.99148</v>
+        <v>192729.3966</v>
       </c>
       <c r="AB162" t="n">
-        <v>289805.99148</v>
+        <v>305337.3966</v>
       </c>
       <c r="AC162" t="n">
-        <v>36719.99999999997</v>
+        <v>112608</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A-150</t>
+          <t>A-151</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Landfill gas collection and destruction efficiency over the site's life</t>
+          <t>Long-run methane potential per tonne of waste at a managed anaerobic site</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>0.5</v>
+        <v>1.36</v>
       </c>
       <c r="E163" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="F163" t="n">
         <v>89.76052799999999</v>
@@ -15690,34 +15690,34 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>206573.99148</v>
+        <v>241581.3966</v>
       </c>
       <c r="AB163" t="n">
-        <v>319181.99148</v>
+        <v>256071.3966</v>
       </c>
       <c r="AC163" t="n">
-        <v>112608</v>
+        <v>14490</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A-151</t>
+          <t>A-152</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Long-run methane potential per tonne of waste at a managed anaerobic site</t>
+          <t>Landfill and gas capture capital cost per tonne of annual capacity</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D164" t="n">
-        <v>1.36</v>
+        <v>40</v>
       </c>
       <c r="E164" t="n">
-        <v>1.7</v>
+        <v>70</v>
       </c>
       <c r="F164" t="n">
         <v>89.76052799999999</v>
@@ -15783,34 +15783,34 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>255425.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB164" t="n">
-        <v>269915.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC164" t="n">
-        <v>14489.99999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A-152</t>
+          <t>A-153</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Landfill and gas capture capital cost per tonne of annual capacity</t>
+          <t>Landfill cell and gas system life</t>
         </is>
       </c>
       <c r="C165" t="n">
+        <v>15</v>
+      </c>
+      <c r="D165" t="n">
+        <v>20</v>
+      </c>
+      <c r="E165" t="n">
         <v>25</v>
-      </c>
-      <c r="D165" t="n">
-        <v>40</v>
-      </c>
-      <c r="E165" t="n">
-        <v>70</v>
       </c>
       <c r="F165" t="n">
         <v>89.76052799999999</v>
@@ -15876,10 +15876,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB165" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -15888,22 +15888,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A-153</t>
+          <t>A-154</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Landfill cell and gas system life</t>
+          <t>Electric buses in service by 2032</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D166" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E166" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="F166" t="n">
         <v>89.76052799999999</v>
@@ -15969,34 +15969,34 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>262877.99148</v>
+        <v>246831.5466</v>
       </c>
       <c r="AB166" t="n">
-        <v>262877.99148</v>
+        <v>253437.0966</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>6605.549999999988</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A-154</t>
+          <t>A-155</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Electric buses in service by 2032</t>
+          <t>Distance per bus a year</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>50</v>
+        <v>45000</v>
       </c>
       <c r="D167" t="n">
-        <v>100</v>
+        <v>60000</v>
       </c>
       <c r="E167" t="n">
-        <v>200</v>
+        <v>75000</v>
       </c>
       <c r="F167" t="n">
         <v>89.76052799999999</v>
@@ -16062,34 +16062,34 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>260676.14148</v>
+        <v>247932.4716</v>
       </c>
       <c r="AB167" t="n">
-        <v>267281.69148</v>
+        <v>250134.3216</v>
       </c>
       <c r="AC167" t="n">
-        <v>6605.549999999988</v>
+        <v>2201.850000000006</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A-155</t>
+          <t>A-156</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Distance per bus a year</t>
+          <t>Diesel use of the bus replaced</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>45000</v>
+        <v>0.33</v>
       </c>
       <c r="D168" t="n">
-        <v>60000</v>
+        <v>0.4</v>
       </c>
       <c r="E168" t="n">
-        <v>75000</v>
+        <v>0.5</v>
       </c>
       <c r="F168" t="n">
         <v>89.76052799999999</v>
@@ -16155,34 +16155,34 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>261777.06648</v>
+        <v>248027.3307</v>
       </c>
       <c r="AB168" t="n">
-        <v>263978.91648</v>
+        <v>250470.6336</v>
       </c>
       <c r="AC168" t="n">
-        <v>2201.850000000035</v>
+        <v>2443.30290000001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A-156</t>
+          <t>A-157</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Diesel use of the bus replaced</t>
+          <t>Electric bus energy use</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E169" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F169" t="n">
         <v>89.76052799999999</v>
@@ -16248,34 +16248,34 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>261871.92558</v>
+        <v>249257.6046</v>
       </c>
       <c r="AB169" t="n">
-        <v>264315.22848</v>
+        <v>248697.0846</v>
       </c>
       <c r="AC169" t="n">
-        <v>2443.30290000001</v>
+        <v>560.5199999999895</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A-157</t>
+          <t>A-158</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Electric bus energy use</t>
+          <t>Share of bus charging from solar</t>
         </is>
       </c>
       <c r="C170" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E170" t="n">
         <v>1</v>
-      </c>
-      <c r="D170" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1.5</v>
       </c>
       <c r="F170" t="n">
         <v>89.76052799999999</v>
@@ -16341,34 +16341,34 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>263102.19948</v>
+        <v>247688.1486</v>
       </c>
       <c r="AB170" t="n">
-        <v>262541.67948</v>
+        <v>250378.6446</v>
       </c>
       <c r="AC170" t="n">
-        <v>560.5200000000186</v>
+        <v>2690.495999999985</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A-158</t>
+          <t>A-159</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Share of bus charging from solar</t>
+          <t>Electric bus and charger cost</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.4</v>
+        <v>250000</v>
       </c>
       <c r="D171" t="n">
-        <v>0.7</v>
+        <v>350000</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>450000</v>
       </c>
       <c r="F171" t="n">
         <v>89.76052799999999</v>
@@ -16434,34 +16434,34 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>261532.74348</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB171" t="n">
-        <v>264223.23948</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC171" t="n">
-        <v>2690.495999999985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A-159</t>
+          <t>A-160</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Electric bus and charger cost</t>
+          <t>Diesel bus cost (counterfactual)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="D172" t="n">
-        <v>350000</v>
+        <v>150000</v>
       </c>
       <c r="E172" t="n">
-        <v>450000</v>
+        <v>200000</v>
       </c>
       <c r="F172" t="n">
         <v>89.76052799999999</v>
@@ -16527,10 +16527,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB172" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -16539,22 +16539,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A-160</t>
+          <t>A-161</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Diesel bus cost (counterfactual)</t>
+          <t>Bus life</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>120000</v>
+        <v>10</v>
       </c>
       <c r="D173" t="n">
-        <v>150000</v>
+        <v>12</v>
       </c>
       <c r="E173" t="n">
-        <v>200000</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
         <v>89.76052799999999</v>
@@ -16620,10 +16620,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB173" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -16632,22 +16632,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A-161</t>
+          <t>A-163</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Bus life</t>
+          <t>Charcoal saved per efficient stove a year</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="D174" t="n">
-        <v>12</v>
+        <v>0.35</v>
       </c>
       <c r="E174" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="F174" t="n">
         <v>89.76052799999999</v>
@@ -16713,34 +16713,34 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>262877.99148</v>
+        <v>180010.5966</v>
       </c>
       <c r="AB174" t="n">
-        <v>262877.99148</v>
+        <v>318056.1966</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>138045.6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A-163</t>
+          <t>A-164</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Charcoal saved per efficient stove a year</t>
+          <t>Fraction of non-renewable biomass (physical estimate, national)</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D175" t="n">
-        <v>0.35</v>
+        <v>0.64</v>
       </c>
       <c r="E175" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F175" t="n">
         <v>89.76052799999999</v>
@@ -16806,31 +16806,31 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>193855.19148</v>
+        <v>183848.4306</v>
       </c>
       <c r="AB175" t="n">
-        <v>331900.79148</v>
+        <v>292490.0406</v>
       </c>
       <c r="AC175" t="n">
-        <v>138045.6</v>
+        <v>108641.61</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A-164</t>
+          <t>A-166</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Fraction of non-renewable biomass (physical estimate, national)</t>
+          <t>Share of stoves sold in Banaadir</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>0.4</v>
       </c>
       <c r="D176" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E176" t="n">
         <v>0.8</v>
@@ -16899,34 +16899,34 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>197693.02548</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB176" t="n">
-        <v>306334.63548</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC176" t="n">
-        <v>108641.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A-166</t>
+          <t>A-169</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Share of stoves sold in Banaadir</t>
+          <t>Stove life</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E177" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="F177" t="n">
         <v>89.76052799999999</v>
@@ -16992,34 +16992,34 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>262877.99148</v>
+        <v>212165.7965999999</v>
       </c>
       <c r="AB177" t="n">
-        <v>262877.99148</v>
+        <v>274258.5966</v>
       </c>
       <c r="AC177" t="n">
-        <v>0</v>
+        <v>62092.80000000005</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A-169</t>
+          <t>A-170</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Stove life</t>
+          <t>Charcoal price in Mogadishu</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>0.28</v>
       </c>
       <c r="D178" t="n">
-        <v>3</v>
+        <v>0.32</v>
       </c>
       <c r="E178" t="n">
-        <v>5</v>
+        <v>0.45</v>
       </c>
       <c r="F178" t="n">
         <v>89.76052799999999</v>
@@ -17085,34 +17085,34 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>226010.39148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB178" t="n">
-        <v>288103.19148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC178" t="n">
-        <v>62092.80000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A-170</t>
+          <t>A-171</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Charcoal price in Mogadishu</t>
+          <t>Fruit: share of domestic sales that replaces imported juice and fruit</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="D179" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="E179" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="F179" t="n">
         <v>89.76052799999999</v>
@@ -17151,13 +17151,13 @@
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8869256391176473</v>
       </c>
       <c r="S179" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8520891591176474</v>
       </c>
       <c r="T179" t="n">
-        <v>0</v>
+        <v>0.03483647999999995</v>
       </c>
       <c r="U179" t="n">
         <v>17836.8</v>
@@ -17169,19 +17169,19 @@
         <v>0</v>
       </c>
       <c r="X179" t="n">
-        <v>227.379276</v>
+        <v>226.834956</v>
       </c>
       <c r="Y179" t="n">
-        <v>227.379276</v>
+        <v>227.923596</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>1.088639999999998</v>
       </c>
       <c r="AA179" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB179" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -17190,22 +17190,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A-171</t>
+          <t>A-172</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Fruit: share of domestic sales that replaces imported juice and fruit</t>
+          <t>Dairy: share of domestic sales that replaces imported milk powder (the rest replaces raw milk sold informally)</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D180" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E180" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F180" t="n">
         <v>89.76052799999999</v>
@@ -17244,13 +17244,13 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0.8869256391176473</v>
+        <v>1.003876679117647</v>
       </c>
       <c r="S180" t="n">
-        <v>0.8520891591176474</v>
+        <v>0.7351381191176473</v>
       </c>
       <c r="T180" t="n">
-        <v>0.03483647999999995</v>
+        <v>0.2687385599999995</v>
       </c>
       <c r="U180" t="n">
         <v>17836.8</v>
@@ -17262,19 +17262,19 @@
         <v>0</v>
       </c>
       <c r="X180" t="n">
-        <v>226.834956</v>
+        <v>223.180236</v>
       </c>
       <c r="Y180" t="n">
-        <v>227.923596</v>
+        <v>231.578316</v>
       </c>
       <c r="Z180" t="n">
-        <v>1.088639999999998</v>
+        <v>8.398079999999993</v>
       </c>
       <c r="AA180" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB180" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -17283,22 +17283,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A-172</t>
+          <t>A-177</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dairy: share of domestic sales that replaces imported milk powder (the rest replaces raw milk sold informally)</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: direct jobs per unit of annual capacity in operation</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="D181" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E181" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="F181" t="n">
         <v>89.76052799999999</v>
@@ -17337,37 +17337,37 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>1.003876679117647</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S181" t="n">
-        <v>0.7351381191176473</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T181" t="n">
-        <v>0.2687385599999995</v>
+        <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>17836.8</v>
+        <v>17776.8</v>
       </c>
       <c r="V181" t="n">
-        <v>17836.8</v>
+        <v>17956.8</v>
       </c>
       <c r="W181" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="X181" t="n">
-        <v>223.180236</v>
+        <v>227.379276</v>
       </c>
       <c r="Y181" t="n">
-        <v>231.578316</v>
+        <v>227.379276</v>
       </c>
       <c r="Z181" t="n">
-        <v>8.398079999999993</v>
+        <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB181" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -17376,22 +17376,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A-177</t>
+          <t>A-178</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: direct jobs per unit of annual capacity in operation</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: capital cost per unit of annual capacity</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.05</v>
+        <v>2000</v>
       </c>
       <c r="D182" t="n">
-        <v>0.1</v>
+        <v>3000</v>
       </c>
       <c r="E182" t="n">
-        <v>0.2</v>
+        <v>6000</v>
       </c>
       <c r="F182" t="n">
         <v>89.76052799999999</v>
@@ -17439,13 +17439,13 @@
         <v>0</v>
       </c>
       <c r="U182" t="n">
-        <v>17776.8</v>
+        <v>17836.8</v>
       </c>
       <c r="V182" t="n">
-        <v>17956.8</v>
+        <v>17836.8</v>
       </c>
       <c r="W182" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="X182" t="n">
         <v>227.379276</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB182" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -17469,22 +17469,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A-178</t>
+          <t>A-179</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: capital cost per unit of annual capacity</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of output sold in Somalia (replacing imports); the rest is exported</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>3000</v>
+        <v>0.05</v>
       </c>
       <c r="E183" t="n">
-        <v>6000</v>
+        <v>0.15</v>
       </c>
       <c r="F183" t="n">
         <v>89.76052799999999</v>
@@ -17523,13 +17523,13 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8840225991176468</v>
       </c>
       <c r="S183" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8404769991176467</v>
       </c>
       <c r="T183" t="n">
-        <v>0</v>
+        <v>0.04354560000000007</v>
       </c>
       <c r="U183" t="n">
         <v>17836.8</v>
@@ -17550,10 +17550,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB183" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -17562,22 +17562,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A-179</t>
+          <t>A-180</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of output sold in Somalia (replacing imports); the rest is exported</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: imported inputs as a share of gross output</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D184" t="n">
         <v>0.05</v>
       </c>
       <c r="E184" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F184" t="n">
         <v>89.76052799999999</v>
@@ -17589,40 +17589,40 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>200.5319613970588</v>
+        <v>200.6070055147059</v>
       </c>
       <c r="J184" t="n">
-        <v>200.5319613970588</v>
+        <v>200.406887867647</v>
       </c>
       <c r="K184" t="n">
-        <v>0</v>
+        <v>0.2001176470588462</v>
       </c>
       <c r="L184" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008234540703530691</v>
       </c>
       <c r="M184" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008226326250072432</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>8.214453458258233e-06</v>
       </c>
       <c r="O184" t="n">
-        <v>120.3191768382353</v>
+        <v>120.3642033088235</v>
       </c>
       <c r="P184" t="n">
-        <v>120.3191768382353</v>
+        <v>120.2441327205882</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>0.1200705882352935</v>
       </c>
       <c r="R184" t="n">
-        <v>0.8840225991176468</v>
+        <v>0.8716086344117647</v>
       </c>
       <c r="S184" t="n">
-        <v>0.8404769991176467</v>
+        <v>0.8660053402941175</v>
       </c>
       <c r="T184" t="n">
-        <v>0.04354560000000007</v>
+        <v>0.005603294117647262</v>
       </c>
       <c r="U184" t="n">
         <v>17836.8</v>
@@ -17634,19 +17634,19 @@
         <v>0</v>
       </c>
       <c r="X184" t="n">
-        <v>227.379276</v>
+        <v>227.651436</v>
       </c>
       <c r="Y184" t="n">
-        <v>227.379276</v>
+        <v>226.925676</v>
       </c>
       <c r="Z184" t="n">
-        <v>0</v>
+        <v>0.7257599999999798</v>
       </c>
       <c r="AA184" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB184" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -17655,22 +17655,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A-180</t>
+          <t>A-181</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: imported inputs as a share of gross output</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="D185" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F185" t="n">
         <v>89.76052799999999</v>
@@ -17682,40 +17682,40 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>200.6070055147059</v>
+        <v>200.0316672794117</v>
       </c>
       <c r="J185" t="n">
-        <v>200.406887867647</v>
+        <v>201.5325496323529</v>
       </c>
       <c r="K185" t="n">
-        <v>0.2001176470588462</v>
+        <v>1.500882352941204</v>
       </c>
       <c r="L185" t="n">
-        <v>0.008234540703530691</v>
+        <v>0.008210924149838204</v>
       </c>
       <c r="M185" t="n">
-        <v>0.008226326250072432</v>
+        <v>0.008272532550775124</v>
       </c>
       <c r="N185" t="n">
-        <v>8.214453458258233e-06</v>
+        <v>6.160840093692027e-05</v>
       </c>
       <c r="O185" t="n">
-        <v>120.3642033088235</v>
+        <v>120.0190003676471</v>
       </c>
       <c r="P185" t="n">
-        <v>120.2441327205882</v>
+        <v>120.9195297794117</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.1200705882352935</v>
+        <v>0.900529411764694</v>
       </c>
       <c r="R185" t="n">
-        <v>0.8716086344117647</v>
+        <v>0.8554991638235295</v>
       </c>
       <c r="S185" t="n">
-        <v>0.8660053402941175</v>
+        <v>0.8975238697058823</v>
       </c>
       <c r="T185" t="n">
-        <v>0.005603294117647262</v>
+        <v>0.04202470588235274</v>
       </c>
       <c r="U185" t="n">
         <v>17836.8</v>
@@ -17727,19 +17727,19 @@
         <v>0</v>
       </c>
       <c r="X185" t="n">
-        <v>227.651436</v>
+        <v>227.379276</v>
       </c>
       <c r="Y185" t="n">
-        <v>226.925676</v>
+        <v>227.379276</v>
       </c>
       <c r="Z185" t="n">
-        <v>0.7257599999999798</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB185" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -17748,22 +17748,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A-181</t>
+          <t>A-182</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
+          <t>Aromatic resins: share of resin processed that would otherwise have been exported raw</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D186" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E186" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
         <v>89.76052799999999</v>
@@ -17775,40 +17775,40 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>200.0316672794117</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J186" t="n">
-        <v>201.5325496323529</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K186" t="n">
-        <v>1.500882352941204</v>
+        <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0.008210924149838204</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M186" t="n">
-        <v>0.008272532550775124</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N186" t="n">
-        <v>6.160840093692027e-05</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>120.0190003676471</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P186" t="n">
-        <v>120.9195297794117</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q186" t="n">
-        <v>0.900529411764694</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0.8554991638235295</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S186" t="n">
-        <v>0.8975238697058823</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T186" t="n">
-        <v>0.04202470588235274</v>
+        <v>0</v>
       </c>
       <c r="U186" t="n">
         <v>17836.8</v>
@@ -17820,19 +17820,19 @@
         <v>0</v>
       </c>
       <c r="X186" t="n">
-        <v>227.379276</v>
+        <v>228.286476</v>
       </c>
       <c r="Y186" t="n">
-        <v>227.379276</v>
+        <v>226.925676</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>1.360799999999983</v>
       </c>
       <c r="AA186" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB186" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -17841,22 +17841,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A-182</t>
+          <t>A-183</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Aromatic resins: share of resin processed that would otherwise have been exported raw</t>
+          <t>Aromatic resins: raw-resin export value forgone per tonne</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.7</v>
+        <v>4000</v>
       </c>
       <c r="D187" t="n">
-        <v>0.9</v>
+        <v>6000</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>8000</v>
       </c>
       <c r="F187" t="n">
         <v>89.76052799999999</v>
@@ -17913,19 +17913,19 @@
         <v>0</v>
       </c>
       <c r="X187" t="n">
-        <v>228.286476</v>
+        <v>228.740076</v>
       </c>
       <c r="Y187" t="n">
-        <v>226.925676</v>
+        <v>226.018476</v>
       </c>
       <c r="Z187" t="n">
-        <v>1.360799999999983</v>
+        <v>2.721599999999995</v>
       </c>
       <c r="AA187" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB187" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -17934,22 +17934,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A-183</t>
+          <t>A-188</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Aromatic resins: raw-resin export value forgone per tonne</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: direct jobs per unit of annual capacity in operation</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4000</v>
+        <v>0.001</v>
       </c>
       <c r="D188" t="n">
-        <v>6000</v>
+        <v>0.002</v>
       </c>
       <c r="E188" t="n">
-        <v>8000</v>
+        <v>0.004</v>
       </c>
       <c r="F188" t="n">
         <v>89.76052799999999</v>
@@ -17997,28 +17997,28 @@
         <v>0</v>
       </c>
       <c r="U188" t="n">
-        <v>17836.8</v>
+        <v>17696.8</v>
       </c>
       <c r="V188" t="n">
-        <v>17836.8</v>
+        <v>18116.8</v>
       </c>
       <c r="W188" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="X188" t="n">
-        <v>228.740076</v>
+        <v>227.379276</v>
       </c>
       <c r="Y188" t="n">
-        <v>226.018476</v>
+        <v>227.379276</v>
       </c>
       <c r="Z188" t="n">
-        <v>2.721599999999995</v>
+        <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB188" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -18027,22 +18027,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A-188</t>
+          <t>A-189</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: direct jobs per unit of annual capacity in operation</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: capital cost per unit of annual capacity</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.001</v>
+        <v>5</v>
       </c>
       <c r="D189" t="n">
-        <v>0.002</v>
+        <v>10</v>
       </c>
       <c r="E189" t="n">
-        <v>0.004</v>
+        <v>20</v>
       </c>
       <c r="F189" t="n">
         <v>89.76052799999999</v>
@@ -18090,13 +18090,13 @@
         <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>17696.8</v>
+        <v>17836.8</v>
       </c>
       <c r="V189" t="n">
-        <v>18116.8</v>
+        <v>17836.8</v>
       </c>
       <c r="W189" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="X189" t="n">
         <v>227.379276</v>
@@ -18108,10 +18108,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB189" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -18120,22 +18120,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A-189</t>
+          <t>A-190</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: capital cost per unit of annual capacity</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of output sold in Somalia (replacing imports); the rest is exported</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="D190" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
         <v>89.76052799999999</v>
@@ -18174,13 +18174,13 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8755553991176471</v>
       </c>
       <c r="S190" t="n">
         <v>0.8695073991176471</v>
       </c>
       <c r="T190" t="n">
-        <v>0</v>
+        <v>0.006048000000000053</v>
       </c>
       <c r="U190" t="n">
         <v>17836.8</v>
@@ -18192,19 +18192,19 @@
         <v>0</v>
       </c>
       <c r="X190" t="n">
-        <v>227.379276</v>
+        <v>227.568276</v>
       </c>
       <c r="Y190" t="n">
         <v>227.379276</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>0.188999999999993</v>
       </c>
       <c r="AA190" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB190" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -18213,22 +18213,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A-190</t>
+          <t>A-191</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of output sold in Somalia (replacing imports); the rest is exported</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: imported inputs as a share of gross output</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F191" t="n">
         <v>89.76052799999999</v>
@@ -18240,40 +18240,40 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>200.5319613970588</v>
+        <v>200.7056746323529</v>
       </c>
       <c r="J191" t="n">
-        <v>200.5319613970588</v>
+        <v>200.2713915441176</v>
       </c>
       <c r="K191" t="n">
-        <v>0</v>
+        <v>0.4342830882353041</v>
       </c>
       <c r="L191" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008238590885444135</v>
       </c>
       <c r="M191" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008220764380543406</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>1.782650490072916e-05</v>
       </c>
       <c r="O191" t="n">
-        <v>120.3191768382353</v>
+        <v>120.4234047794118</v>
       </c>
       <c r="P191" t="n">
-        <v>120.3191768382353</v>
+        <v>120.1628349264706</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>0.260569852941174</v>
       </c>
       <c r="R191" t="n">
-        <v>0.8755553991176471</v>
+        <v>0.8743713697058827</v>
       </c>
       <c r="S191" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8622114432352943</v>
       </c>
       <c r="T191" t="n">
-        <v>0.006048000000000053</v>
+        <v>0.01215992647058839</v>
       </c>
       <c r="U191" t="n">
         <v>17836.8</v>
@@ -18285,19 +18285,19 @@
         <v>0</v>
       </c>
       <c r="X191" t="n">
-        <v>227.568276</v>
+        <v>227.757276</v>
       </c>
       <c r="Y191" t="n">
-        <v>227.379276</v>
+        <v>226.812276</v>
       </c>
       <c r="Z191" t="n">
-        <v>0.188999999999993</v>
+        <v>0.9449999999999932</v>
       </c>
       <c r="AA191" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB191" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -18306,22 +18306,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A-191</t>
+          <t>A-192</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: imported inputs as a share of gross output</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D192" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="E192" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F192" t="n">
         <v>89.76052799999999</v>
@@ -18333,40 +18333,40 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>200.7056746323529</v>
+        <v>200.2540202205882</v>
       </c>
       <c r="J192" t="n">
-        <v>200.2713915441176</v>
+        <v>200.8099025735294</v>
       </c>
       <c r="K192" t="n">
-        <v>0.4342830882353041</v>
+        <v>0.5558823529411825</v>
       </c>
       <c r="L192" t="n">
-        <v>0.008238590885444135</v>
+        <v>0.008220051320347376</v>
       </c>
       <c r="M192" t="n">
-        <v>0.008220764380543406</v>
+        <v>0.008242869246620311</v>
       </c>
       <c r="N192" t="n">
-        <v>1.782650490072916e-05</v>
+        <v>2.281792627293472e-05</v>
       </c>
       <c r="O192" t="n">
-        <v>120.4234047794118</v>
+        <v>120.1524121323529</v>
       </c>
       <c r="P192" t="n">
-        <v>120.1628349264706</v>
+        <v>120.4859415441177</v>
       </c>
       <c r="Q192" t="n">
-        <v>0.260569852941174</v>
+        <v>0.3335294117647152</v>
       </c>
       <c r="R192" t="n">
-        <v>0.8743713697058827</v>
+        <v>0.8617250461764707</v>
       </c>
       <c r="S192" t="n">
-        <v>0.8622114432352943</v>
+        <v>0.877289752058824</v>
       </c>
       <c r="T192" t="n">
-        <v>0.01215992647058839</v>
+        <v>0.01556470588235326</v>
       </c>
       <c r="U192" t="n">
         <v>17836.8</v>
@@ -18378,19 +18378,19 @@
         <v>0</v>
       </c>
       <c r="X192" t="n">
-        <v>227.757276</v>
+        <v>227.379276</v>
       </c>
       <c r="Y192" t="n">
-        <v>226.812276</v>
+        <v>227.379276</v>
       </c>
       <c r="Z192" t="n">
-        <v>0.9449999999999932</v>
+        <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB192" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -18399,12 +18399,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A-192</t>
+          <t>A-193</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
+          <t>Stoves: share of domestic sales that replaces imported stoves</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -18414,7 +18414,7 @@
         <v>0.5</v>
       </c>
       <c r="E193" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F193" t="n">
         <v>89.76052799999999</v>
@@ -18426,40 +18426,40 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>200.2540202205882</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J193" t="n">
-        <v>200.8099025735294</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K193" t="n">
-        <v>0.5558823529411825</v>
+        <v>0</v>
       </c>
       <c r="L193" t="n">
-        <v>0.008220051320347376</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M193" t="n">
-        <v>0.008242869246620311</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N193" t="n">
-        <v>2.281792627293472e-05</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>120.1524121323529</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P193" t="n">
-        <v>120.4859415441177</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.3335294117647152</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>0.8617250461764707</v>
+        <v>0.8936993991176471</v>
       </c>
       <c r="S193" t="n">
-        <v>0.877289752058824</v>
+        <v>0.8332193991176471</v>
       </c>
       <c r="T193" t="n">
-        <v>0.01556470588235326</v>
+        <v>0.06047999999999998</v>
       </c>
       <c r="U193" t="n">
         <v>17836.8</v>
@@ -18471,19 +18471,19 @@
         <v>0</v>
       </c>
       <c r="X193" t="n">
-        <v>227.379276</v>
+        <v>226.623276</v>
       </c>
       <c r="Y193" t="n">
-        <v>227.379276</v>
+        <v>228.513276</v>
       </c>
       <c r="Z193" t="n">
-        <v>0</v>
+        <v>1.889999999999986</v>
       </c>
       <c r="AA193" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB193" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -18492,22 +18492,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A-193</t>
+          <t>A-200</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Stoves: share of domestic sales that replaces imported stoves</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: direct jobs per unit of annual capacity in operation</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.3</v>
+        <v>0.005</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="E194" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="F194" t="n">
         <v>89.76052799999999</v>
@@ -18546,37 +18546,37 @@
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.8936993991176471</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S194" t="n">
-        <v>0.8332193991176471</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T194" t="n">
-        <v>0.06047999999999998</v>
+        <v>0</v>
       </c>
       <c r="U194" t="n">
-        <v>17836.8</v>
+        <v>17756.8</v>
       </c>
       <c r="V194" t="n">
-        <v>17836.8</v>
+        <v>17996.8</v>
       </c>
       <c r="W194" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X194" t="n">
-        <v>226.623276</v>
+        <v>227.379276</v>
       </c>
       <c r="Y194" t="n">
-        <v>228.513276</v>
+        <v>227.379276</v>
       </c>
       <c r="Z194" t="n">
-        <v>1.889999999999986</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB194" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -18585,22 +18585,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A-200</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: direct jobs per unit of annual capacity in operation</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: capital cost per unit of annual capacity</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.005</v>
+        <v>80</v>
       </c>
       <c r="D195" t="n">
-        <v>0.01</v>
+        <v>150</v>
       </c>
       <c r="E195" t="n">
-        <v>0.02</v>
+        <v>250</v>
       </c>
       <c r="F195" t="n">
         <v>89.76052799999999</v>
@@ -18648,13 +18648,13 @@
         <v>0</v>
       </c>
       <c r="U195" t="n">
-        <v>17756.8</v>
+        <v>17836.8</v>
       </c>
       <c r="V195" t="n">
-        <v>17996.8</v>
+        <v>17836.8</v>
       </c>
       <c r="W195" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="X195" t="n">
         <v>227.379276</v>
@@ -18666,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB195" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -18678,22 +18678,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: capital cost per unit of annual capacity</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of output sold in Somalia (replacing imports); the rest is exported</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>80</v>
+        <v>0.9</v>
       </c>
       <c r="D196" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
         <v>89.76052799999999</v>
@@ -18750,19 +18750,19 @@
         <v>0</v>
       </c>
       <c r="X196" t="n">
-        <v>227.379276</v>
+        <v>227.530476</v>
       </c>
       <c r="Y196" t="n">
         <v>227.379276</v>
       </c>
       <c r="Z196" t="n">
-        <v>0</v>
+        <v>0.1511999999999887</v>
       </c>
       <c r="AA196" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB196" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -18771,22 +18771,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-203</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of output sold in Somalia (replacing imports); the rest is exported</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: imported inputs as a share of gross output</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.9</v>
+        <v>0.02</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F197" t="n">
         <v>89.76052799999999</v>
@@ -18798,40 +18798,40 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>200.5319613970588</v>
+        <v>200.5653143382353</v>
       </c>
       <c r="J197" t="n">
-        <v>200.5319613970588</v>
+        <v>200.4763731617647</v>
       </c>
       <c r="K197" t="n">
-        <v>0</v>
+        <v>0.08894117647059829</v>
       </c>
       <c r="L197" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008232829359060221</v>
       </c>
       <c r="M197" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.00822917849085655</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>3.65086820367129e-06</v>
       </c>
       <c r="O197" t="n">
-        <v>120.3191768382353</v>
+        <v>120.3391886029412</v>
       </c>
       <c r="P197" t="n">
-        <v>120.3191768382353</v>
+        <v>120.2858238970588</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>0.05336470588234477</v>
       </c>
       <c r="R197" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8704412814705883</v>
       </c>
       <c r="S197" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8679509285294119</v>
       </c>
       <c r="T197" t="n">
-        <v>0</v>
+        <v>0.002490352941176388</v>
       </c>
       <c r="U197" t="n">
         <v>17836.8</v>
@@ -18843,19 +18843,19 @@
         <v>0</v>
       </c>
       <c r="X197" t="n">
-        <v>227.530476</v>
+        <v>227.424636</v>
       </c>
       <c r="Y197" t="n">
-        <v>227.379276</v>
+        <v>227.303676</v>
       </c>
       <c r="Z197" t="n">
-        <v>0.1511999999999887</v>
+        <v>0.1209599999999966</v>
       </c>
       <c r="AA197" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB197" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -18864,22 +18864,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A-203</t>
+          <t>A-204</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: imported inputs as a share of gross output</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.02</v>
+        <v>0.6</v>
       </c>
       <c r="D198" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="E198" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F198" t="n">
         <v>89.76052799999999</v>
@@ -18891,40 +18891,40 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>200.5653143382353</v>
+        <v>200.3512996323529</v>
       </c>
       <c r="J198" t="n">
-        <v>200.4763731617647</v>
+        <v>200.6222922794117</v>
       </c>
       <c r="K198" t="n">
-        <v>0.08894117647059829</v>
+        <v>0.2709926470588186</v>
       </c>
       <c r="L198" t="n">
-        <v>0.008232829359060221</v>
+        <v>0.008224044457445141</v>
       </c>
       <c r="M198" t="n">
-        <v>0.00822917849085655</v>
+        <v>0.008235168196503195</v>
       </c>
       <c r="N198" t="n">
-        <v>3.65086820367129e-06</v>
+        <v>1.112373905805437e-05</v>
       </c>
       <c r="O198" t="n">
-        <v>120.3391886029412</v>
+        <v>120.2107797794118</v>
       </c>
       <c r="P198" t="n">
-        <v>120.2858238970588</v>
+        <v>120.3733753676471</v>
       </c>
       <c r="Q198" t="n">
-        <v>0.05336470588234477</v>
+        <v>0.1625955882352912</v>
       </c>
       <c r="R198" t="n">
-        <v>0.8704412814705883</v>
+        <v>0.8644488697058823</v>
       </c>
       <c r="S198" t="n">
-        <v>0.8679509285294119</v>
+        <v>0.8720366638235295</v>
       </c>
       <c r="T198" t="n">
-        <v>0.002490352941176388</v>
+        <v>0.007587794117647206</v>
       </c>
       <c r="U198" t="n">
         <v>17836.8</v>
@@ -18936,19 +18936,19 @@
         <v>0</v>
       </c>
       <c r="X198" t="n">
-        <v>227.424636</v>
+        <v>227.379276</v>
       </c>
       <c r="Y198" t="n">
-        <v>227.303676</v>
+        <v>227.379276</v>
       </c>
       <c r="Z198" t="n">
-        <v>0.1209599999999966</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB198" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -18957,22 +18957,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A-204</t>
+          <t>A-207</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
+          <t>Charcoal replaced per tonne of pellets or briquettes</t>
         </is>
       </c>
       <c r="C199" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D199" t="n">
         <v>0.6</v>
       </c>
-      <c r="D199" t="n">
-        <v>0.8</v>
-      </c>
       <c r="E199" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F199" t="n">
         <v>89.76052799999999</v>
@@ -18984,40 +18984,40 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>200.3512996323529</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J199" t="n">
-        <v>200.6222922794117</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K199" t="n">
-        <v>0.2709926470588186</v>
+        <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0.008224044457445141</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M199" t="n">
-        <v>0.008235168196503195</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N199" t="n">
-        <v>1.112373905805437e-05</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>120.2107797794118</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P199" t="n">
-        <v>120.3733753676471</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q199" t="n">
-        <v>0.1625955882352912</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>0.8644488697058823</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S199" t="n">
-        <v>0.8720366638235295</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T199" t="n">
-        <v>0.007587794117647206</v>
+        <v>0</v>
       </c>
       <c r="U199" t="n">
         <v>17836.8</v>
@@ -19038,34 +19038,34 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>262877.99148</v>
+        <v>245840.0526</v>
       </c>
       <c r="AB199" t="n">
-        <v>262877.99148</v>
+        <v>252226.7406</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>6386.688000000024</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A-207</t>
+          <t>A-208</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Charcoal replaced per tonne of pellets or briquettes</t>
+          <t>Park solar and storage: premium on equipment cost for site works, interconnection, security and fragile-state delivery</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="D200" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E200" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E200" t="n">
-        <v>0.75</v>
       </c>
       <c r="F200" t="n">
         <v>89.76052799999999</v>
@@ -19131,34 +19131,34 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>259684.64748</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB200" t="n">
-        <v>266071.33548</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC200" t="n">
-        <v>6386.687999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A-208</t>
+          <t>A-209</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Park solar and storage: premium on equipment cost for site works, interconnection, security and fragile-state delivery</t>
+          <t>Park solar and storage: annual operation and maintenance cost as a share of installed cost</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.15</v>
+        <v>0.015</v>
       </c>
       <c r="D201" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="E201" t="n">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="F201" t="n">
         <v>89.76052799999999</v>
@@ -19224,10 +19224,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB201" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -19236,22 +19236,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A-209</t>
+          <t>A-210</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Park solar and storage: annual operation and maintenance cost as a share of installed cost</t>
+          <t>Solar PV plant life</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.015</v>
+        <v>20</v>
       </c>
       <c r="D202" t="n">
-        <v>0.02</v>
+        <v>25</v>
       </c>
       <c r="E202" t="n">
-        <v>0.03</v>
+        <v>30</v>
       </c>
       <c r="F202" t="n">
         <v>89.76052799999999</v>
@@ -19317,10 +19317,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB202" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -19329,22 +19329,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A-210</t>
+          <t>A-211</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Solar PV plant life</t>
+          <t>Battery life before replacement</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D203" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E203" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F203" t="n">
         <v>89.76052799999999</v>
@@ -19410,10 +19410,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB203" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -19422,22 +19422,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A-211</t>
+          <t>A-212</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Battery life before replacement</t>
+          <t>Average annual flood losses in Mogadishu (baseline, 2026)</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D204" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E204" t="n">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="F204" t="n">
         <v>89.76052799999999</v>
@@ -19503,10 +19503,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB204" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -19515,22 +19515,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A-212</t>
+          <t>A-213</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Average annual flood losses in Mogadishu (baseline, 2026)</t>
+          <t>Annual growth of flood losses with population and urbanisation</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>80</v>
+        <v>0.03</v>
       </c>
       <c r="D205" t="n">
-        <v>120</v>
+        <v>0.043</v>
       </c>
       <c r="E205" t="n">
-        <v>160</v>
+        <v>0.06</v>
       </c>
       <c r="F205" t="n">
         <v>89.76052799999999</v>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB205" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -19608,22 +19608,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A-213</t>
+          <t>A-214</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Annual growth of flood losses with population and urbanisation</t>
+          <t>Share of Mogadishu's flood losses arising in catchments drained by 2032 (priority catchments, including the park-to-port corridor)</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="D206" t="n">
-        <v>0.043</v>
+        <v>0.3</v>
       </c>
       <c r="E206" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="F206" t="n">
         <v>89.76052799999999</v>
@@ -19689,10 +19689,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB206" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -19701,22 +19701,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A-214</t>
+          <t>A-215</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Share of Mogadishu's flood losses arising in catchments drained by 2032 (priority catchments, including the park-to-port corridor)</t>
+          <t>Reduction in flood losses in a drained catchment</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D207" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="E207" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F207" t="n">
         <v>89.76052799999999</v>
@@ -19782,10 +19782,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB207" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -19794,22 +19794,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A-215</t>
+          <t>A-216</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Reduction in flood losses in a drained catchment</t>
+          <t>Drainage investment per dollar of annual avoided flood loss</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
       <c r="D208" t="n">
-        <v>0.45</v>
+        <v>12</v>
       </c>
       <c r="E208" t="n">
-        <v>0.6</v>
+        <v>18</v>
       </c>
       <c r="F208" t="n">
         <v>89.76052799999999</v>
@@ -19875,10 +19875,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB208" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -19887,22 +19887,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A-216</t>
+          <t>A-217</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Drainage investment per dollar of annual avoided flood loss</t>
+          <t>Economic life of trunk drainage</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D209" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E209" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F209" t="n">
         <v>89.76052799999999</v>
@@ -19968,10 +19968,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AB209" t="n">
-        <v>262877.99148</v>
+        <v>249033.3966</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -19980,22 +19980,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A-217</t>
+          <t>A-218</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Economic life of trunk drainage</t>
+          <t>Share of the parks' electricity demand met by the solar-plus-storage system</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D210" t="n">
-        <v>30</v>
+        <v>0.7</v>
       </c>
       <c r="E210" t="n">
-        <v>40</v>
+        <v>0.85</v>
       </c>
       <c r="F210" t="n">
         <v>89.76052799999999</v>
@@ -20061,13 +20061,1408 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>262877.99148</v>
+        <v>240269.355</v>
       </c>
       <c r="AB210" t="n">
-        <v>262877.99148</v>
+        <v>255606.4278</v>
       </c>
       <c r="AC210" t="n">
-        <v>0</v>
+        <v>15337.07280000002</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>A-219</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: meat</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>100</v>
+      </c>
+      <c r="D211" t="n">
+        <v>150</v>
+      </c>
+      <c r="E211" t="n">
+        <v>250</v>
+      </c>
+      <c r="F211" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G211" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J211" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P211" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V211" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>248542.9416</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>250014.3066</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1471.36500000002</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>A-220</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: tanning</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G212" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J212" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P212" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V212" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>248575.6386</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>250406.6706</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1831.032000000007</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>A-221</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: fish</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>200</v>
+      </c>
+      <c r="D213" t="n">
+        <v>300</v>
+      </c>
+      <c r="E213" t="n">
+        <v>500</v>
+      </c>
+      <c r="F213" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G213" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J213" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P213" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V213" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W213" t="n">
+        <v>0</v>
+      </c>
+      <c r="X213" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>247463.9406</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>252172.3086</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>4708.368000000017</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>A-222</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: sesame</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>40</v>
+      </c>
+      <c r="D214" t="n">
+        <v>60</v>
+      </c>
+      <c r="E214" t="n">
+        <v>100</v>
+      </c>
+      <c r="F214" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G214" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J214" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P214" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V214" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W214" t="n">
+        <v>0</v>
+      </c>
+      <c r="X214" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>248880.8106</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>249338.5686</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>457.7580000000016</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>A-223</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: sesame oil</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>50</v>
+      </c>
+      <c r="D215" t="n">
+        <v>80</v>
+      </c>
+      <c r="E215" t="n">
+        <v>120</v>
+      </c>
+      <c r="F215" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G215" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J215" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P215" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V215" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W215" t="n">
+        <v>0</v>
+      </c>
+      <c r="X215" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>248987.6208</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>249094.431</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>106.8102000000072</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>A-224</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: fruit</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>30</v>
+      </c>
+      <c r="D216" t="n">
+        <v>50</v>
+      </c>
+      <c r="E216" t="n">
+        <v>100</v>
+      </c>
+      <c r="F216" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G216" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J216" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P216" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V216" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0</v>
+      </c>
+      <c r="X216" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>248876.451</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>249425.7606</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>549.3095999999787</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>A-225</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: flour</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>50</v>
+      </c>
+      <c r="D217" t="n">
+        <v>70</v>
+      </c>
+      <c r="E217" t="n">
+        <v>100</v>
+      </c>
+      <c r="F217" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G217" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J217" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P217" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V217" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W217" t="n">
+        <v>0</v>
+      </c>
+      <c r="X217" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>247638.3246</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>251126.0046</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>3487.679999999993</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>A-226</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: dairy</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F218" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G218" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J218" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P218" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V218" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W218" t="n">
+        <v>0</v>
+      </c>
+      <c r="X218" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>248248.6686</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>250602.8526</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>2354.184000000008</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>A-227</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: soap</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>100</v>
+      </c>
+      <c r="D219" t="n">
+        <v>150</v>
+      </c>
+      <c r="E219" t="n">
+        <v>250</v>
+      </c>
+      <c r="F219" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G219" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J219" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P219" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V219" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W219" t="n">
+        <v>0</v>
+      </c>
+      <c r="X219" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>248706.4266</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>249687.3366</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>980.9099999999744</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>A-228</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: diapers</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>250</v>
+      </c>
+      <c r="D220" t="n">
+        <v>400</v>
+      </c>
+      <c r="E220" t="n">
+        <v>600</v>
+      </c>
+      <c r="F220" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G220" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J220" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P220" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V220" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W220" t="n">
+        <v>0</v>
+      </c>
+      <c r="X220" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>248758.7418</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>249399.603</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>640.8612000000139</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>A-229</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: garments</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D221" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F221" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G221" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J221" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P221" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V221" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W221" t="n">
+        <v>0</v>
+      </c>
+      <c r="X221" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>245545.7166</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>252521.0766</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>6975.359999999986</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>A-230</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: aromatics</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>250</v>
+      </c>
+      <c r="D222" t="n">
+        <v>500</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F222" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G222" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J222" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P222" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V222" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W222" t="n">
+        <v>0</v>
+      </c>
+      <c r="X222" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>248918.9571</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>249262.2756</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>343.3184999999939</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>A-231</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: stoves</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="n">
+        <v>5</v>
+      </c>
+      <c r="E223" t="n">
+        <v>10</v>
+      </c>
+      <c r="F223" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G223" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J223" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P223" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V223" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W223" t="n">
+        <v>0</v>
+      </c>
+      <c r="X223" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>248837.2146</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>249360.3666</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>523.1520000000019</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>A-232</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: pellets</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>60</v>
+      </c>
+      <c r="D224" t="n">
+        <v>100</v>
+      </c>
+      <c r="E224" t="n">
+        <v>150</v>
+      </c>
+      <c r="F224" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G224" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J224" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P224" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V224" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W224" t="n">
+        <v>0</v>
+      </c>
+      <c r="X224" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>248545.1214</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>249643.7406</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1098.619199999986</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>A-233</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: bpo</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D225" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E225" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F225" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G225" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J225" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P225" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V225" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W225" t="n">
+        <v>0</v>
+      </c>
+      <c r="X225" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>247289.5566</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>252521.0766</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>5231.51999999996</v>
       </c>
     </row>
   </sheetData>
@@ -20123,13 +21518,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.39275371301252</v>
+        <v>81.44596327597952</v>
       </c>
       <c r="D2" t="n">
-        <v>97.00669632775585</v>
+        <v>97.63404874142611</v>
       </c>
       <c r="E2" t="n">
-        <v>115.7116465868197</v>
+        <v>116.8126343691399</v>
       </c>
     </row>
     <row r="3">
@@ -20144,13 +21539,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>170.1518640830367</v>
+        <v>172.1118091905987</v>
       </c>
       <c r="D3" t="n">
-        <v>211.9164822040024</v>
+        <v>212.8904495380881</v>
       </c>
       <c r="E3" t="n">
-        <v>263.6423108537051</v>
+        <v>262.534945747679</v>
       </c>
     </row>
     <row r="4">
@@ -20165,13 +21560,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.007023686071349466</v>
+        <v>0.007077910492579431</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008747665939044448</v>
+        <v>0.00879795446367878</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01087462442437725</v>
+        <v>0.01082217852013053</v>
       </c>
     </row>
     <row r="5">
@@ -20186,13 +21581,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>95.68245349446697</v>
+        <v>97.83814728936549</v>
       </c>
       <c r="D5" t="n">
-        <v>126.6464463484671</v>
+        <v>127.3436906898425</v>
       </c>
       <c r="E5" t="n">
-        <v>165.8374108444503</v>
+        <v>165.6513162072338</v>
       </c>
     </row>
     <row r="6">
@@ -20207,13 +21602,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.199333015870678</v>
+        <v>-1.282847262687824</v>
       </c>
       <c r="D6" t="n">
-        <v>1.136918981764121</v>
+        <v>1.167649896930699</v>
       </c>
       <c r="E6" t="n">
-        <v>3.733131883194384</v>
+        <v>3.779589108507905</v>
       </c>
     </row>
     <row r="7">
@@ -20228,13 +21623,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15152.3303566877</v>
+        <v>15406.88953188914</v>
       </c>
       <c r="D7" t="n">
-        <v>19171.66716032305</v>
+        <v>19183.643069857</v>
       </c>
       <c r="E7" t="n">
-        <v>23695.54875478762</v>
+        <v>23786.2079315459</v>
       </c>
     </row>
     <row r="8">
@@ -20249,13 +21644,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>193.9833879934914</v>
+        <v>195.3903185770723</v>
       </c>
       <c r="D8" t="n">
-        <v>240.428366131565</v>
+        <v>241.8317638397809</v>
       </c>
       <c r="E8" t="n">
-        <v>299.2286106385028</v>
+        <v>299.2290659270003</v>
       </c>
     </row>
     <row r="9">
@@ -20270,13 +21665,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>182396.6803795566</v>
+        <v>174070.2198095541</v>
       </c>
       <c r="D9" t="n">
-        <v>256964.908761674</v>
+        <v>251471.456493912</v>
       </c>
       <c r="E9" t="n">
-        <v>355947.6572853113</v>
+        <v>346872.4762293933</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +21685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K218"/>
+  <dimension ref="A1:K234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27060,14 +28455,19 @@
       <c r="G147" t="n">
         <v>4000</v>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>C-0530</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>Afgoye farmers (news report, 2026)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Judgment; to be surveyed.</t>
+          <t>A farmer spent USD 100 to 150 per irrigation round with a fuel-powered pump (C-0530), and fuel sells at about USD 1 a litre (C-0533), so up to 100 to 150 litres a round; about 20 rounds a year when fuel is affordable gives some 2,500 litres. No survey exists; the range covers smaller and larger pumps.</t>
         </is>
       </c>
       <c r="K147" t="b">
@@ -27091,7 +28491,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -27102,16 +28502,21 @@
         <v>4000</v>
       </c>
       <c r="G148" t="n">
-        <v>10000</v>
+        <v>8000</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>C-0532</t>
+        </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>Afgoye farmer's solar system (news report, 2026)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Judgment.</t>
+          <t>A farmer's solar irrigation system cost USD 4,600 (C-0532); the base adds installation and water-governance costs, and the high end allows for larger pumps.</t>
         </is>
       </c>
       <c r="K148" t="b">
@@ -30325,6 +31730,710 @@
         </is>
       </c>
       <c r="K218" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>A-218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>minigrid.solar_share</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Share of the parks' electricity demand met by the solar-plus-storage system</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>PV with four-hour batteries covers daytime load and the evening shoulder; night shifts and cloudy days fall back on other supply. The PV plant is sized to this share of mature park demand (judgment).</t>
+        </is>
+      </c>
+      <c r="K219" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>A-219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>meat.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: meat</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>150</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>kWh per t carcass meat</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>100</v>
+      </c>
+      <c r="G220" t="n">
+        <v>250</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Slaughter, chilling to 0 to 4 C and chilled storage. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K220" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>A-220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>tanning.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: tanning</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>kWh per skin</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Drums, pumps, effluent treatment and drying. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K221" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>A-221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>fish.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: fish</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>300</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>kWh per t</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>200</v>
+      </c>
+      <c r="G222" t="n">
+        <v>500</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Ice making, blast freezing and cold storage. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K222" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>A-222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>sesame.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: sesame</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>60</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>kWh per t seed</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>40</v>
+      </c>
+      <c r="G223" t="n">
+        <v>100</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Cleaning, hulling, drying and sorting. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K223" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>A-223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>sesame_oil.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: sesame oil</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>80</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>kWh per t seed</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>50</v>
+      </c>
+      <c r="G224" t="n">
+        <v>120</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Expellers, filtration and refining. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K224" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>A-224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>fruit.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: fruit</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>50</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>kWh per t fruit</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>30</v>
+      </c>
+      <c r="G225" t="n">
+        <v>100</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Packhouse cooling and a small juice and puree line. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K225" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>A-225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>flour.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: flour</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>70</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>kWh per t flour</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>50</v>
+      </c>
+      <c r="G226" t="n">
+        <v>100</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Milling, conveying and silo aeration. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K226" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>A-226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>dairy.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: dairy</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>kWh per litre</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Chilling, pasteurisation and packing. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K227" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>A-227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>soap.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: soap</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>150</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>kWh per t</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>100</v>
+      </c>
+      <c r="G228" t="n">
+        <v>250</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Mixing, milling, plodding and stamping. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K228" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>A-228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>diapers.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: diapers</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>400</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>kWh per t</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>250</v>
+      </c>
+      <c r="G229" t="n">
+        <v>600</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>High-speed converting lines. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K229" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>A-229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>garments.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: garments</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>kWh per job place a year</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G230" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Sewing machines, lighting, cutting and ventilation. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K230" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>A-230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>aromatics.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: aromatics</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>500</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>kWh per t resin</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>250</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Grinding and electrically heated distillation; biomass boilers would lower it. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>A-231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>stoves.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: stoves</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>5</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>kWh per stove</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>2</v>
+      </c>
+      <c r="G232" t="n">
+        <v>10</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Metal presses, welding and liner kilns (kilns partly fuel-fired). Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>A-232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>pellets.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: pellets</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>100</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>kWh per t</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>60</v>
+      </c>
+      <c r="G233" t="n">
+        <v>150</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Chipping, drying fans and pelletising. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>A-233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>bpo.kwh_per_unit</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Electricity use per unit of output: bpo</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>kWh per seat a year</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G234" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Round-the-clock computers, servers and air conditioning. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+        </is>
+      </c>
+      <c r="K234" t="b">
         <v>1</v>
       </c>
     </row>
@@ -30339,7 +32448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33279,12 +35388,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>minigrid.pv_mw</t>
+          <t>minigrid.solar_share</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>A-135</t>
+          <t>A-218</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -33296,267 +35405,267 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>minigrid.capacity_factor</t>
+          <t>meat.kwh_per_unit</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>A-136</t>
+          <t>A-219</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>minigrid.diesel_displaced_share</t>
+          <t>tanning.kwh_per_unit</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>A-137</t>
+          <t>A-220</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>minigrid.pv_capex_per_kw</t>
+          <t>fish.kwh_per_unit</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>A-138</t>
+          <t>A-221</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>minigrid.battery_kw_per_pv_kw</t>
+          <t>sesame.kwh_per_unit</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>A-139</t>
+          <t>A-222</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>minigrid.battery_capex_per_kw</t>
+          <t>sesame_oil.kwh_per_unit</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>A-140</t>
+          <t>A-223</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>minigrid.site_premium</t>
+          <t>fruit.kwh_per_unit</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>A-208</t>
+          <t>A-224</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>minigrid.om_share</t>
+          <t>flour.kwh_per_unit</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>A-209</t>
+          <t>A-225</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>minigrid.pv_lifetime_years</t>
+          <t>dairy.kwh_per_unit</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>A-210</t>
+          <t>A-226</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>minigrid.battery_lifetime_years</t>
+          <t>soap.kwh_per_unit</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>A-211</t>
+          <t>A-227</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>minigrid.diesel_cost_usd_per_mwh</t>
+          <t>diapers.kwh_per_unit</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>A-142</t>
+          <t>A-228</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>fuel.diesel_price_usd_per_litre</t>
+          <t>garments.kwh_per_unit</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>A-143</t>
+          <t>A-229</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>finance.discount_rate</t>
+          <t>aromatics.kwh_per_unit</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>A-144</t>
+          <t>A-230</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>irrigation.pumps</t>
+          <t>stoves.kwh_per_unit</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>A-145</t>
+          <t>A-231</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>irrigation.diesel_litres_per_pump</t>
+          <t>pellets.kwh_per_unit</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>A-146</t>
+          <t>A-232</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>irrigation.capex_per_pump</t>
+          <t>bpo.kwh_per_unit</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>A-147</t>
+          <t>A-233</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>irrigation.lifetime_years</t>
+          <t>minigrid.capacity_factor</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>A-148</t>
+          <t>A-136</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -33568,12 +35677,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>waste.tonnes_per_year</t>
+          <t>minigrid.diesel_displaced_share</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>A-149</t>
+          <t>A-137</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -33585,46 +35694,46 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>waste.capture_efficiency</t>
+          <t>minigrid.pv_capex_per_kw</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>A-150</t>
+          <t>A-138</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>waste.lo_tco2e_per_t_mcf1</t>
+          <t>minigrid.battery_kw_per_pv_kw</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>A-151</t>
+          <t>A-139</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>waste.capex_per_t_per_year</t>
+          <t>minigrid.battery_capex_per_kw</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>A-152</t>
+          <t>A-140</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -33636,63 +35745,63 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>waste.lifetime_years</t>
+          <t>minigrid.site_premium</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>A-153</t>
+          <t>A-208</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>resilience.aal_musd</t>
+          <t>minigrid.om_share</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>A-212</t>
+          <t>A-209</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>resilience.loss_growth</t>
+          <t>minigrid.pv_lifetime_years</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>A-213</t>
+          <t>A-210</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>resilience.drainage_coverage</t>
+          <t>minigrid.battery_lifetime_years</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>A-214</t>
+          <t>A-211</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -33704,12 +35813,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>resilience.flood_reduction</t>
+          <t>minigrid.diesel_cost_usd_per_mwh</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>A-215</t>
+          <t>A-142</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -33721,46 +35830,46 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>resilience.capex_per_usd_avoided</t>
+          <t>fuel.diesel_price_usd_per_litre</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>A-216</t>
+          <t>A-143</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>resilience.lifetime_years</t>
+          <t>finance.discount_rate</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>A-217</t>
+          <t>A-144</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ebus.buses</t>
+          <t>irrigation.pumps</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>A-154</t>
+          <t>A-145</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -33772,12 +35881,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ebus.km_per_bus</t>
+          <t>irrigation.diesel_litres_per_pump</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>A-155</t>
+          <t>A-146</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -33789,46 +35898,46 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ebus.diesel_litres_per_km</t>
+          <t>irrigation.capex_per_pump</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>A-156</t>
+          <t>A-147</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ebus.kwh_per_km</t>
+          <t>irrigation.lifetime_years</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>A-157</t>
+          <t>A-148</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ebus.solar_charged_share</t>
+          <t>waste.tonnes_per_year</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>A-158</t>
+          <t>A-149</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -33840,29 +35949,29 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ebus.capex_per_bus</t>
+          <t>waste.capture_efficiency</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>A-159</t>
+          <t>A-150</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ebus.diesel_bus_capex</t>
+          <t>waste.lo_tco2e_per_t_mcf1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>A-160</t>
+          <t>A-151</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -33874,29 +35983,29 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ebus.lifetime_years</t>
+          <t>waste.capex_per_t_per_year</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>A-161</t>
+          <t>A-152</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>cooking.charcoal_saved_t_per_stove</t>
+          <t>waste.lifetime_years</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>A-163</t>
+          <t>A-153</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -33908,29 +36017,29 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>cooking.fnrb_national</t>
+          <t>resilience.aal_musd</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>A-164</t>
+          <t>A-212</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>cooking.fnrb_banaadir_creditable</t>
+          <t>resilience.loss_growth</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>A-165</t>
+          <t>A-213</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -33942,29 +36051,29 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>cooking.banaadir_share</t>
+          <t>resilience.drainage_coverage</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>A-166</t>
+          <t>A-214</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>cooking.stove_lifetime_years</t>
+          <t>resilience.flood_reduction</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>A-169</t>
+          <t>A-215</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -33976,215 +36085,470 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>cooking.charcoal_price_usd_per_kg</t>
+          <t>resilience.capex_per_usd_avoided</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>A-170</t>
+          <t>A-216</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>gdp.2028</t>
+          <t>resilience.lifetime_years</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>C-0020</t>
+          <t>A-217</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>16875104000</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 16.875 billion in 2028 (WEO April 2026).</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>gdp.2029</t>
+          <t>ebus.buses</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>C-0021</t>
+          <t>A-154</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>18340870000</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 18.341 billion in 2029 (WEO April 2026).</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>gdp.2030</t>
+          <t>ebus.km_per_bus</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>C-0022</t>
+          <t>A-155</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>19851193000</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 19.851 billion in 2030 (WEO April 2026).</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>gdp.2031</t>
+          <t>ebus.diesel_litres_per_km</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>C-0023</t>
+          <t>A-156</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>21991019000</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 21.991 billion in 2031 (WEO April 2026).</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>fuel.diesel_kgco2e_per_litre</t>
+          <t>ebus.kwh_per_km</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>C-0306</t>
+          <t>A-157</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>2.66155</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>The UK Government's 2026 conversion factors put direct (Scope 1) emissions from burning 100% mineral diesel at 2.66155 kg CO2e per litre.</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>waste.mcf_baseline</t>
+          <t>ebus.solar_charged_share</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>C-0319</t>
+          <t>A-158</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>The IPCC default methane correction factor for an uncategorised disposal site is 0.6.</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>waste.mcf_project</t>
+          <t>ebus.capex_per_bus</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>C-0318</t>
+          <t>A-159</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>The IPCC default methane correction factor for a managed anaerobic disposal site is 1.0.</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
+          <t>ebus.diesel_bus_capex</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>A-160</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ebus.lifetime_years</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>A-161</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>cooking.charcoal_saved_t_per_stove</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>A-163</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>cooking.fnrb_national</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>A-164</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>cooking.fnrb_banaadir_creditable</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>A-165</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>cooking.banaadir_share</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>A-166</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>cooking.stove_lifetime_years</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>A-169</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>cooking.charcoal_price_usd_per_kg</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>A-170</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>gdp.2028</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>C-0020</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>16875104000</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 16.875 billion in 2028 (WEO April 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>gdp.2029</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>C-0021</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>18340870000</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 18.341 billion in 2029 (WEO April 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>gdp.2030</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>C-0022</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>19851193000</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 19.851 billion in 2030 (WEO April 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>gdp.2031</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>C-0023</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>21991019000</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 21.991 billion in 2031 (WEO April 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>fuel.diesel_kgco2e_per_litre</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>C-0306</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>2.66155</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>The UK Government's 2026 conversion factors put direct (Scope 1) emissions from burning 100% mineral diesel at 2.66155 kg CO2e per litre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>waste.mcf_baseline</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>C-0319</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>The IPCC default methane correction factor for an uncategorised disposal site is 0.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>waste.mcf_project</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>C-0318</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>The IPCC default methane correction factor for a managed anaerobic disposal site is 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
           <t>cooking.co2_per_t_charcoal</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>D-0029</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D222" t="n">
+      <c r="D237" t="n">
         <v>3.3</v>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>Burning a tonne of charcoal releases about 3.30 tonnes of CO2 on IPCC defaults (29.5 TJ per Gg, 112,000 kg CO2 per TJ). This CO2 is biogenic and is excluded from national inventory totals; methane and nitrous oxide are not included.</t>
         </is>
@@ -56735,10 +59099,10 @@
         <v>2028</v>
       </c>
       <c r="D2" t="n">
-        <v>261.874944</v>
+        <v>117.06564</v>
       </c>
       <c r="E2" t="n">
-        <v>2720000</v>
+        <v>1215918.31557585</v>
       </c>
       <c r="F2" t="n">
         <v>-6.843106392136601</v>
@@ -56759,10 +59123,10 @@
         <v>2029</v>
       </c>
       <c r="D3" t="n">
-        <v>1658.541312</v>
+        <v>741.41572</v>
       </c>
       <c r="E3" t="n">
-        <v>8160000.000000001</v>
+        <v>3647754.94672755</v>
       </c>
       <c r="F3" t="n">
         <v>-6.843106392136601</v>
@@ -56783,10 +59147,10 @@
         <v>2030</v>
       </c>
       <c r="D4" t="n">
-        <v>4539.165696</v>
+        <v>2029.13776</v>
       </c>
       <c r="E4" t="n">
-        <v>10880000</v>
+        <v>4863673.262303399</v>
       </c>
       <c r="F4" t="n">
         <v>-6.843106392136601</v>
@@ -56807,10 +59171,10 @@
         <v>2031</v>
       </c>
       <c r="D5" t="n">
-        <v>8030.831615999999</v>
+        <v>3590.01296</v>
       </c>
       <c r="E5" t="n">
-        <v>10880000</v>
+        <v>4863673.262303398</v>
       </c>
       <c r="F5" t="n">
         <v>-6.843106392136601</v>
@@ -56831,10 +59195,10 @@
         <v>2032</v>
       </c>
       <c r="D6" t="n">
-        <v>11522.497536</v>
+        <v>5150.88816</v>
       </c>
       <c r="E6" t="n">
-        <v>10880000.00000001</v>
+        <v>4863673.2623034</v>
       </c>
       <c r="F6" t="n">
         <v>-6.843106392136601</v>
@@ -56858,10 +59222,10 @@
         <v>59.884875</v>
       </c>
       <c r="E7" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="F7" t="n">
-        <v>254.7726972214843</v>
+        <v>158.7316480366227</v>
       </c>
     </row>
     <row r="8">
@@ -56882,10 +59246,10 @@
         <v>379.270875</v>
       </c>
       <c r="E8" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="F8" t="n">
-        <v>254.7726972214843</v>
+        <v>158.7316480366227</v>
       </c>
     </row>
     <row r="9">
@@ -56906,10 +59270,10 @@
         <v>1038.0045</v>
       </c>
       <c r="E9" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="F9" t="n">
-        <v>254.7726972214843</v>
+        <v>158.7316480366227</v>
       </c>
     </row>
     <row r="10">
@@ -56930,10 +59294,10 @@
         <v>1836.4695</v>
       </c>
       <c r="E10" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="F10" t="n">
-        <v>254.7726972214843</v>
+        <v>158.7316480366227</v>
       </c>
     </row>
     <row r="11">
@@ -56954,10 +59318,10 @@
         <v>2634.9345</v>
       </c>
       <c r="E11" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="F11" t="n">
-        <v>254.7726972214843</v>
+        <v>158.7316480366227</v>
       </c>
     </row>
     <row r="12">
@@ -57335,10 +59699,10 @@
         <v>2028</v>
       </c>
       <c r="D27" t="n">
-        <v>3709.895039999999</v>
+        <v>2556.178799999999</v>
       </c>
       <c r="E27" t="n">
-        <v>8580000</v>
+        <v>5911761.348374966</v>
       </c>
       <c r="F27" t="n">
         <v>-412.1244334084436</v>
@@ -57359,10 +59723,10 @@
         <v>2029</v>
       </c>
       <c r="D28" t="n">
-        <v>12366.3168</v>
+        <v>8520.595999999998</v>
       </c>
       <c r="E28" t="n">
-        <v>11440000</v>
+        <v>7882348.464499954</v>
       </c>
       <c r="F28" t="n">
         <v>-412.1244334084436</v>
@@ -57383,10 +59747,10 @@
         <v>2030</v>
       </c>
       <c r="D29" t="n">
-        <v>23496.00192</v>
+        <v>16189.1324</v>
       </c>
       <c r="E29" t="n">
-        <v>14300000</v>
+        <v>9852935.580624944</v>
       </c>
       <c r="F29" t="n">
         <v>-412.1244334084436</v>
@@ -57407,10 +59771,10 @@
         <v>2031</v>
       </c>
       <c r="D30" t="n">
-        <v>34625.68704</v>
+        <v>23857.6688</v>
       </c>
       <c r="E30" t="n">
-        <v>11440000.00000001</v>
+        <v>7882348.464499957</v>
       </c>
       <c r="F30" t="n">
         <v>-412.1244334084436</v>
@@ -57431,10 +59795,10 @@
         <v>2032</v>
       </c>
       <c r="D31" t="n">
-        <v>44518.74048</v>
+        <v>30674.1456</v>
       </c>
       <c r="E31" t="n">
-        <v>11440000</v>
+        <v>7882348.464499953</v>
       </c>
       <c r="F31" t="n">
         <v>-412.1244334084436</v>
@@ -57458,10 +59822,10 @@
         <v>998.08125</v>
       </c>
       <c r="E32" t="n">
-        <v>2100000</v>
+        <v>1500000</v>
       </c>
       <c r="F32" t="n">
-        <v>-237.4080609852747</v>
+        <v>-276.9260191336836</v>
       </c>
     </row>
     <row r="33">
@@ -57482,10 +59846,10 @@
         <v>3326.9375</v>
       </c>
       <c r="E33" t="n">
-        <v>2800000</v>
+        <v>2000000</v>
       </c>
       <c r="F33" t="n">
-        <v>-237.4080609852747</v>
+        <v>-276.9260191336836</v>
       </c>
     </row>
     <row r="34">
@@ -57506,10 +59870,10 @@
         <v>6321.18125</v>
       </c>
       <c r="E34" t="n">
-        <v>3500000</v>
+        <v>2500000</v>
       </c>
       <c r="F34" t="n">
-        <v>-237.4080609852747</v>
+        <v>-276.9260191336836</v>
       </c>
     </row>
     <row r="35">
@@ -57530,10 +59894,10 @@
         <v>9315.424999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>2800000.000000001</v>
+        <v>2000000</v>
       </c>
       <c r="F35" t="n">
-        <v>-237.4080609852747</v>
+        <v>-276.9260191336836</v>
       </c>
     </row>
     <row r="36">
@@ -57554,10 +59918,10 @@
         <v>11976.975</v>
       </c>
       <c r="E36" t="n">
-        <v>2799999.999999999</v>
+        <v>2000000</v>
       </c>
       <c r="F36" t="n">
-        <v>-237.4080609852747</v>
+        <v>-276.9260191336836</v>
       </c>
     </row>
     <row r="37">
@@ -57935,10 +60299,10 @@
         <v>2028</v>
       </c>
       <c r="D52" t="n">
-        <v>14893.4016</v>
+        <v>16477.8348</v>
       </c>
       <c r="E52" t="n">
-        <v>13455000</v>
+        <v>14886408.9741594</v>
       </c>
       <c r="F52" t="n">
         <v>-677.5362002721241</v>
@@ -57959,10 +60323,10 @@
         <v>2029</v>
       </c>
       <c r="D53" t="n">
-        <v>36169.6896</v>
+        <v>40017.59879999999</v>
       </c>
       <c r="E53" t="n">
-        <v>13455000</v>
+        <v>14886408.9741594</v>
       </c>
       <c r="F53" t="n">
         <v>-677.5362002721241</v>
@@ -57983,10 +60347,10 @@
         <v>2030</v>
       </c>
       <c r="D54" t="n">
-        <v>57445.97760000001</v>
+        <v>63557.3628</v>
       </c>
       <c r="E54" t="n">
-        <v>13455000</v>
+        <v>14886408.9741594</v>
       </c>
       <c r="F54" t="n">
         <v>-677.5362002721241</v>
@@ -58007,10 +60371,10 @@
         <v>2031</v>
       </c>
       <c r="D55" t="n">
-        <v>72764.90496</v>
+        <v>80505.99288000001</v>
       </c>
       <c r="E55" t="n">
-        <v>8073000.000000002</v>
+        <v>8931845.384495642</v>
       </c>
       <c r="F55" t="n">
         <v>-677.5362002721241</v>
@@ -58031,10 +60395,10 @@
         <v>2032</v>
       </c>
       <c r="D56" t="n">
-        <v>82551.99743999999</v>
+        <v>91334.28431999999</v>
       </c>
       <c r="E56" t="n">
-        <v>5381999.999999998</v>
+        <v>5954563.589663759</v>
       </c>
       <c r="F56" t="n">
         <v>-677.5362002721241</v>

--- a/model/outputs/gip_model.xlsx
+++ b/model/outputs/gip_model.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC225"/>
+  <dimension ref="A1:AC228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,10 +717,10 @@
         <v>41.47199999999998</v>
       </c>
       <c r="AA2" t="n">
-        <v>245894.4846</v>
+        <v>236303.2553810272</v>
       </c>
       <c r="AB2" t="n">
-        <v>254264.9166</v>
+        <v>244673.6873810272</v>
       </c>
       <c r="AC2" t="n">
         <v>8370.432000000001</v>
@@ -810,13 +810,13 @@
         <v>104.976</v>
       </c>
       <c r="AA3" t="n">
-        <v>246679.2126</v>
+        <v>238578.9665810272</v>
       </c>
       <c r="AB3" t="n">
-        <v>253741.7646</v>
+        <v>241168.5689810272</v>
       </c>
       <c r="AC3" t="n">
-        <v>7062.551999999996</v>
+        <v>2589.602399999974</v>
       </c>
     </row>
     <row r="4">
@@ -903,10 +903,10 @@
         <v>25.92000000000002</v>
       </c>
       <c r="AA4" t="n">
-        <v>245545.7166</v>
+        <v>235954.4873810272</v>
       </c>
       <c r="AB4" t="n">
-        <v>256008.7566</v>
+        <v>246417.5273810272</v>
       </c>
       <c r="AC4" t="n">
         <v>10463.03999999998</v>
@@ -996,10 +996,10 @@
         <v>67.09770000000003</v>
       </c>
       <c r="AA5" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB5" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>81.648</v>
       </c>
       <c r="AA6" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB6" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1182,10 +1182,10 @@
         <v>59.37300000000002</v>
       </c>
       <c r="AA7" t="n">
-        <v>248297.7141</v>
+        <v>238706.4848810272</v>
       </c>
       <c r="AB7" t="n">
-        <v>249769.0791</v>
+        <v>240177.8498810272</v>
       </c>
       <c r="AC7" t="n">
         <v>1471.364999999991</v>
@@ -1275,10 +1275,10 @@
         <v>26.82604800000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB8" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1368,13 +1368,13 @@
         <v>37.896546</v>
       </c>
       <c r="AA9" t="n">
-        <v>223734.6192</v>
+        <v>215209.0821164686</v>
       </c>
       <c r="AB9" t="n">
-        <v>261682.7853</v>
+        <v>251558.7100133065</v>
       </c>
       <c r="AC9" t="n">
-        <v>37948.16610000003</v>
+        <v>36349.62789683789</v>
       </c>
     </row>
     <row r="10">
@@ -1461,10 +1461,10 @@
         <v>20.73600000000002</v>
       </c>
       <c r="AA10" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB10" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1554,10 +1554,10 @@
         <v>14.39999999999998</v>
       </c>
       <c r="AA11" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB11" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1647,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB12" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>25.264364</v>
       </c>
       <c r="AA13" t="n">
-        <v>231496.2192</v>
+        <v>222970.6821164686</v>
       </c>
       <c r="AB13" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC13" t="n">
-        <v>17537.17739999999</v>
+        <v>16471.48526455858</v>
       </c>
     </row>
     <row r="14">
@@ -1833,10 +1833,10 @@
         <v>12.96000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB14" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>20.21149119999998</v>
       </c>
       <c r="AA15" t="n">
-        <v>235033.08564</v>
+        <v>225868.1332752038</v>
       </c>
       <c r="AB15" t="n">
-        <v>263033.70756</v>
+        <v>253016.2014868506</v>
       </c>
       <c r="AC15" t="n">
-        <v>28000.62192000001</v>
+        <v>27148.06821164687</v>
       </c>
     </row>
     <row r="16">
@@ -2019,13 +2019,13 @@
         <v>34.99200000000002</v>
       </c>
       <c r="AA16" t="n">
-        <v>247856.3046</v>
+        <v>239010.5669810272</v>
       </c>
       <c r="AB16" t="n">
-        <v>250210.4886</v>
+        <v>239873.7677810272</v>
       </c>
       <c r="AC16" t="n">
-        <v>2354.184000000008</v>
+        <v>863.2007999999914</v>
       </c>
     </row>
     <row r="17">
@@ -2112,10 +2112,10 @@
         <v>33.858</v>
       </c>
       <c r="AA17" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB17" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2205,13 +2205,13 @@
         <v>18.89568</v>
       </c>
       <c r="AA18" t="n">
-        <v>248248.6686</v>
+        <v>239206.7489810272</v>
       </c>
       <c r="AB18" t="n">
-        <v>250602.8526</v>
+        <v>239913.0041810272</v>
       </c>
       <c r="AC18" t="n">
-        <v>2354.184000000008</v>
+        <v>706.2551999999851</v>
       </c>
     </row>
     <row r="19">
@@ -2298,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB19" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         <v>19.791</v>
       </c>
       <c r="AA20" t="n">
-        <v>248739.1236</v>
+        <v>239147.8943810272</v>
       </c>
       <c r="AB20" t="n">
-        <v>249229.5786</v>
+        <v>239638.3493810272</v>
       </c>
       <c r="AC20" t="n">
-        <v>490.4550000000163</v>
+        <v>490.4549999999872</v>
       </c>
     </row>
     <row r="21">
@@ -2484,13 +2484,13 @@
         <v>8.100000000000023</v>
       </c>
       <c r="AA21" t="n">
-        <v>248052.4866</v>
+        <v>238461.2573810272</v>
       </c>
       <c r="AB21" t="n">
-        <v>249687.3366</v>
+        <v>240096.1073810272</v>
       </c>
       <c r="AC21" t="n">
-        <v>1634.849999999977</v>
+        <v>1634.850000000006</v>
       </c>
     </row>
     <row r="22">
@@ -2577,10 +2577,10 @@
         <v>6.652800000000013</v>
       </c>
       <c r="AA22" t="n">
-        <v>248926.5864</v>
+        <v>239335.3571810272</v>
       </c>
       <c r="AB22" t="n">
-        <v>249262.2756</v>
+        <v>239671.0463810272</v>
       </c>
       <c r="AC22" t="n">
         <v>335.6891999999934</v>
@@ -2670,13 +2670,13 @@
         <v>9.216000000000008</v>
       </c>
       <c r="AA23" t="n">
-        <v>247080.2958</v>
+        <v>236931.0377810272</v>
       </c>
       <c r="AB23" t="n">
-        <v>250986.4974</v>
+        <v>241953.2969810272</v>
       </c>
       <c r="AC23" t="n">
-        <v>3906.2016</v>
+        <v>5022.2592</v>
       </c>
     </row>
     <row r="24">
@@ -2763,13 +2763,13 @@
         <v>5.400000000000006</v>
       </c>
       <c r="AA24" t="n">
-        <v>247725.5166</v>
+        <v>238134.2873810272</v>
       </c>
       <c r="AB24" t="n">
-        <v>249905.3166</v>
+        <v>240314.0873810272</v>
       </c>
       <c r="AC24" t="n">
-        <v>2179.800000000017</v>
+        <v>2179.799999999988</v>
       </c>
     </row>
     <row r="25">
@@ -2856,10 +2856,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB25" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -2949,10 +2949,10 @@
         <v>5.644800000000004</v>
       </c>
       <c r="AA26" t="n">
-        <v>248346.7596</v>
+        <v>238755.5303810272</v>
       </c>
       <c r="AB26" t="n">
-        <v>249948.9126</v>
+        <v>240357.6833810272</v>
       </c>
       <c r="AC26" t="n">
         <v>1602.152999999991</v>
@@ -3042,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB27" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3135,13 +3135,13 @@
         <v>6.236999999999995</v>
       </c>
       <c r="AA28" t="n">
-        <v>248850.2934</v>
+        <v>239259.0641810272</v>
       </c>
       <c r="AB28" t="n">
-        <v>249308.0514</v>
+        <v>239716.8221810272</v>
       </c>
       <c r="AC28" t="n">
-        <v>457.7580000000016</v>
+        <v>457.7580000000307</v>
       </c>
     </row>
     <row r="29">
@@ -3228,10 +3228,10 @@
         <v>8.618400000000008</v>
       </c>
       <c r="AA29" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB29" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB30" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -3414,10 +3414,10 @@
         <v>5.292000000000002</v>
       </c>
       <c r="AA31" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB31" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -3507,10 +3507,10 @@
         <v>8.398079999999993</v>
       </c>
       <c r="AA32" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB32" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -3600,10 +3600,10 @@
         <v>6.560190000000006</v>
       </c>
       <c r="AA33" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB33" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -3693,13 +3693,13 @@
         <v>10.20600000000002</v>
       </c>
       <c r="AA34" t="n">
-        <v>248837.2146</v>
+        <v>239245.9853810272</v>
       </c>
       <c r="AB34" t="n">
-        <v>249425.7606</v>
+        <v>239834.5313810272</v>
       </c>
       <c r="AC34" t="n">
-        <v>588.545999999973</v>
+        <v>588.5460000000021</v>
       </c>
     </row>
     <row r="35">
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB35" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -3879,13 +3879,13 @@
         <v>6.298560000000009</v>
       </c>
       <c r="AA36" t="n">
-        <v>248641.0326</v>
+        <v>239324.4581810272</v>
       </c>
       <c r="AB36" t="n">
-        <v>249425.7606</v>
+        <v>239559.8765810272</v>
       </c>
       <c r="AC36" t="n">
-        <v>784.7280000000028</v>
+        <v>235.418399999995</v>
       </c>
     </row>
     <row r="37">
@@ -3972,13 +3972,13 @@
         <v>4.319999999999993</v>
       </c>
       <c r="AA37" t="n">
-        <v>248542.9416</v>
+        <v>239311.3793810272</v>
       </c>
       <c r="AB37" t="n">
-        <v>249523.8516</v>
+        <v>239572.9553810272</v>
       </c>
       <c r="AC37" t="n">
-        <v>980.9100000000035</v>
+        <v>261.5760000000009</v>
       </c>
     </row>
     <row r="38">
@@ -4065,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB38" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>3.965472000000005</v>
       </c>
       <c r="AA39" t="n">
-        <v>248667.1902</v>
+        <v>239075.9609810272</v>
       </c>
       <c r="AB39" t="n">
-        <v>249521.6718</v>
+        <v>239930.4425810272</v>
       </c>
       <c r="AC39" t="n">
         <v>854.4815999999992</v>
@@ -4251,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB40" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -4344,10 +4344,10 @@
         <v>3.118500000000012</v>
       </c>
       <c r="AA41" t="n">
-        <v>248902.6086</v>
+        <v>239311.3793810272</v>
       </c>
       <c r="AB41" t="n">
-        <v>249131.4876</v>
+        <v>239540.2583810272</v>
       </c>
       <c r="AC41" t="n">
         <v>228.8790000000154</v>
@@ -4437,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB42" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -4530,13 +4530,13 @@
         <v>2.268000000000001</v>
       </c>
       <c r="AA43" t="n">
-        <v>248968.0026</v>
+        <v>239376.7733810272</v>
       </c>
       <c r="AB43" t="n">
-        <v>249082.4421</v>
+        <v>239491.2128810272</v>
       </c>
       <c r="AC43" t="n">
-        <v>114.4394999999786</v>
+        <v>114.4395000000077</v>
       </c>
     </row>
     <row r="44">
@@ -4623,13 +4623,13 @@
         <v>2.879999999999995</v>
       </c>
       <c r="AA44" t="n">
-        <v>248423.0526</v>
+        <v>238657.4393810272</v>
       </c>
       <c r="AB44" t="n">
-        <v>249643.7406</v>
+        <v>240226.8953810272</v>
       </c>
       <c r="AC44" t="n">
-        <v>1220.687999999995</v>
+        <v>1569.456000000006</v>
       </c>
     </row>
     <row r="45">
@@ -4716,10 +4716,10 @@
         <v>2.879999999999995</v>
       </c>
       <c r="AA45" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB45" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>2.073599999999999</v>
       </c>
       <c r="AA46" t="n">
-        <v>248739.1236</v>
+        <v>239147.8943810272</v>
       </c>
       <c r="AB46" t="n">
-        <v>249327.6696</v>
+        <v>239736.4403810272</v>
       </c>
       <c r="AC46" t="n">
-        <v>588.5460000000021</v>
+        <v>588.545999999973</v>
       </c>
     </row>
     <row r="47">
@@ -4902,10 +4902,10 @@
         <v>4.860000000000014</v>
       </c>
       <c r="AA47" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB47" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -4995,10 +4995,10 @@
         <v>0.7087500000000091</v>
       </c>
       <c r="AA48" t="n">
-        <v>168343.3116</v>
+        <v>158752.0823810272</v>
       </c>
       <c r="AB48" t="n">
-        <v>370068.5241</v>
+        <v>360477.2948810272</v>
       </c>
       <c r="AC48" t="n">
         <v>201725.2125</v>
@@ -5088,10 +5088,10 @@
         <v>6.11099999999999</v>
       </c>
       <c r="AA49" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB49" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -5181,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB50" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -5274,13 +5274,13 @@
         <v>3.401999999999987</v>
       </c>
       <c r="AA51" t="n">
-        <v>248935.3056</v>
+        <v>239344.0763810272</v>
       </c>
       <c r="AB51" t="n">
-        <v>249131.4876</v>
+        <v>239540.2583810272</v>
       </c>
       <c r="AC51" t="n">
-        <v>196.1820000000007</v>
+        <v>196.1820000000298</v>
       </c>
     </row>
     <row r="52">
@@ -5367,10 +5367,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB52" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -5460,10 +5460,10 @@
         <v>1.456704000000002</v>
       </c>
       <c r="AA53" t="n">
-        <v>248876.451</v>
+        <v>239285.2217810272</v>
       </c>
       <c r="AB53" t="n">
-        <v>249190.3422</v>
+        <v>239599.1129810272</v>
       </c>
       <c r="AC53" t="n">
         <v>313.8911999999837</v>
@@ -5553,13 +5553,13 @@
         <v>1.439999999999998</v>
       </c>
       <c r="AA54" t="n">
-        <v>248837.2146</v>
+        <v>239389.8521810272</v>
       </c>
       <c r="AB54" t="n">
-        <v>249164.1846</v>
+        <v>239477.0441810272</v>
       </c>
       <c r="AC54" t="n">
-        <v>326.9699999999721</v>
+        <v>87.19200000001001</v>
       </c>
     </row>
     <row r="55">
@@ -5646,13 +5646,13 @@
         <v>0.1134000000000128</v>
       </c>
       <c r="AA55" t="n">
-        <v>242036.3646</v>
+        <v>232445.1353810272</v>
       </c>
       <c r="AB55" t="n">
-        <v>263027.4606</v>
+        <v>253436.2313810272</v>
       </c>
       <c r="AC55" t="n">
-        <v>20991.09599999999</v>
+        <v>20991.09600000002</v>
       </c>
     </row>
     <row r="56">
@@ -5739,13 +5739,13 @@
         <v>0.1270079999999894</v>
       </c>
       <c r="AA56" t="n">
-        <v>248960.15532</v>
+        <v>239387.2364210272</v>
       </c>
       <c r="AB56" t="n">
-        <v>249155.4654</v>
+        <v>239533.7189810272</v>
       </c>
       <c r="AC56" t="n">
-        <v>195.3100799999957</v>
+        <v>146.4825600000331</v>
       </c>
     </row>
     <row r="57">
@@ -5832,10 +5832,10 @@
         <v>1.295999999999992</v>
       </c>
       <c r="AA57" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB57" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB58" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -6018,13 +6018,13 @@
         <v>0.3240000000000123</v>
       </c>
       <c r="AA59" t="n">
-        <v>203018.1966</v>
+        <v>193426.9673810272</v>
       </c>
       <c r="AB59" t="n">
-        <v>295048.5966</v>
+        <v>285457.3673810272</v>
       </c>
       <c r="AC59" t="n">
-        <v>92030.39999999999</v>
+        <v>92030.40000000002</v>
       </c>
     </row>
     <row r="60">
@@ -6111,10 +6111,10 @@
         <v>0.9676800000000014</v>
       </c>
       <c r="AA60" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB60" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -6204,10 +6204,10 @@
         <v>0.2835000000000036</v>
       </c>
       <c r="AA61" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB61" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -6297,13 +6297,13 @@
         <v>0.07560000000000855</v>
       </c>
       <c r="AA62" t="n">
-        <v>242646.7086</v>
+        <v>233055.4793810272</v>
       </c>
       <c r="AB62" t="n">
-        <v>255420.0846</v>
+        <v>245828.8553810272</v>
       </c>
       <c r="AC62" t="n">
-        <v>12773.37599999999</v>
+        <v>12773.37600000002</v>
       </c>
     </row>
     <row r="63">
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB63" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -6483,10 +6483,10 @@
         <v>3.016439999999989</v>
       </c>
       <c r="AA64" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB64" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -6576,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB65" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>0.1890000000000214</v>
       </c>
       <c r="AA66" t="n">
-        <v>216757.3626</v>
+        <v>207166.1333810272</v>
       </c>
       <c r="AB66" t="n">
-        <v>270550.7526</v>
+        <v>260959.5233810272</v>
       </c>
       <c r="AC66" t="n">
-        <v>53793.39000000001</v>
+        <v>53793.38999999998</v>
       </c>
     </row>
     <row r="67">
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB67" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -6855,10 +6855,10 @@
         <v>0.04032000000000835</v>
       </c>
       <c r="AA68" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB68" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -6948,13 +6948,13 @@
         <v>0.03780000000000427</v>
       </c>
       <c r="AA69" t="n">
-        <v>245035.0926</v>
+        <v>235443.8633810272</v>
       </c>
       <c r="AB69" t="n">
-        <v>252032.1246</v>
+        <v>242440.8953810272</v>
       </c>
       <c r="AC69" t="n">
-        <v>6997.031999999977</v>
+        <v>6997.032000000007</v>
       </c>
     </row>
     <row r="70">
@@ -7041,13 +7041,13 @@
         <v>0.03969000000000733</v>
       </c>
       <c r="AA70" t="n">
-        <v>248998.5198</v>
+        <v>239416.0097810272</v>
       </c>
       <c r="AB70" t="n">
-        <v>249059.5542</v>
+        <v>239461.7855810272</v>
       </c>
       <c r="AC70" t="n">
-        <v>61.03439999997499</v>
+        <v>45.77580000000307</v>
       </c>
     </row>
     <row r="71">
@@ -7134,10 +7134,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB71" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -7227,10 +7227,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB72" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>243212.1966</v>
+        <v>233620.9673810272</v>
       </c>
       <c r="AB73" t="n">
-        <v>254854.5966</v>
+        <v>245263.3673810272</v>
       </c>
       <c r="AC73" t="n">
-        <v>11642.40000000002</v>
+        <v>11642.39999999999</v>
       </c>
     </row>
     <row r="74">
@@ -7413,13 +7413,13 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>233510.1966</v>
+        <v>223918.9673810272</v>
       </c>
       <c r="AB74" t="n">
-        <v>260675.7966</v>
+        <v>251084.5673810272</v>
       </c>
       <c r="AC74" t="n">
-        <v>27165.60000000003</v>
+        <v>27165.60000000001</v>
       </c>
     </row>
     <row r="75">
@@ -7506,10 +7506,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB75" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -7599,10 +7599,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB76" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -7692,10 +7692,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB77" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -7785,10 +7785,10 @@
         <v>7.128000000000014</v>
       </c>
       <c r="AA78" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB78" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -7878,10 +7878,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB79" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -7971,10 +7971,10 @@
         <v>22.113</v>
       </c>
       <c r="AA80" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB80" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -8064,10 +8064,10 @@
         <v>19.44</v>
       </c>
       <c r="AA81" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB81" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -8157,10 +8157,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB82" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -8250,10 +8250,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB83" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB84" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -8436,10 +8436,10 @@
         <v>1.512</v>
       </c>
       <c r="AA85" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB85" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB86" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         <v>0.6803999999999917</v>
       </c>
       <c r="AA87" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB87" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -8715,10 +8715,10 @@
         <v>0.514080000000007</v>
       </c>
       <c r="AA88" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB88" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -8808,10 +8808,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB89" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -8901,10 +8901,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB90" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -8994,10 +8994,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB91" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -9087,10 +9087,10 @@
         <v>7.77600000000001</v>
       </c>
       <c r="AA92" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB92" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -9180,10 +9180,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB93" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -9273,10 +9273,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB94" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB95" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -9459,10 +9459,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB96" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -9552,10 +9552,10 @@
         <v>0.9071999999999889</v>
       </c>
       <c r="AA97" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB97" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB98" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>5.254200000000026</v>
       </c>
       <c r="AA99" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB99" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -9831,10 +9831,10 @@
         <v>4.762799999999999</v>
       </c>
       <c r="AA100" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB100" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -9924,10 +9924,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB101" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -10017,10 +10017,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB102" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB103" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -10203,10 +10203,10 @@
         <v>0.2721599999999853</v>
       </c>
       <c r="AA104" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB104" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB105" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>1.050839999999994</v>
       </c>
       <c r="AA106" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB106" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -10482,10 +10482,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB107" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -10575,10 +10575,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB108" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -10668,10 +10668,10 @@
         <v>1.360800000000012</v>
       </c>
       <c r="AA109" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB109" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -10761,10 +10761,10 @@
         <v>0.9071999999999889</v>
       </c>
       <c r="AA110" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB110" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -10854,10 +10854,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB111" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB112" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -11040,10 +11040,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB113" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -11133,10 +11133,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB114" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -11226,10 +11226,10 @@
         <v>9.216000000000008</v>
       </c>
       <c r="AA115" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB115" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -11319,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB116" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -11412,10 +11412,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB117" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -11505,10 +11505,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB118" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -11598,10 +11598,10 @@
         <v>1.866240000000005</v>
       </c>
       <c r="AA119" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB119" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -11691,10 +11691,10 @@
         <v>3.499199999999973</v>
       </c>
       <c r="AA120" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB120" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -11784,10 +11784,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB121" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -11877,10 +11877,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB122" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -11970,10 +11970,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB123" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB124" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -12156,10 +12156,10 @@
         <v>3.240000000000009</v>
       </c>
       <c r="AA125" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB125" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -12249,10 +12249,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB126" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -12342,10 +12342,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB127" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -12435,10 +12435,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB128" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -12528,10 +12528,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB129" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -12621,10 +12621,10 @@
         <v>2.124359999999996</v>
       </c>
       <c r="AA130" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB130" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -12714,10 +12714,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB131" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -12807,10 +12807,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB132" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -12900,10 +12900,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB133" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -12993,10 +12993,10 @@
         <v>6.912000000000006</v>
       </c>
       <c r="AA134" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB134" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB135" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -13179,10 +13179,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB136" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -13272,10 +13272,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB137" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -13365,10 +13365,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB138" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -13458,10 +13458,10 @@
         <v>2.879999999999995</v>
       </c>
       <c r="AA139" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB139" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB140" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -13644,10 +13644,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB141" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB142" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -13830,10 +13830,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB143" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -13923,10 +13923,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB144" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -14016,10 +14016,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB145" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -14109,10 +14109,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB146" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -14202,10 +14202,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB147" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -14295,13 +14295,13 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB148" t="n">
-        <v>250898.2398</v>
+        <v>241088.5769810272</v>
       </c>
       <c r="AC148" t="n">
-        <v>1864.843200000003</v>
+        <v>1646.409600000014</v>
       </c>
     </row>
     <row r="149">
@@ -14388,10 +14388,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB149" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -14481,13 +14481,13 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>242898.56748</v>
+        <v>233994.4112210272</v>
       </c>
       <c r="AB150" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC150" t="n">
-        <v>6134.82911999998</v>
+        <v>5447.75615999999</v>
       </c>
     </row>
     <row r="151">
@@ -14574,10 +14574,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB151" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -14667,10 +14667,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB152" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -14760,10 +14760,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB153" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -14853,10 +14853,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB154" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -14946,10 +14946,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB155" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -15039,10 +15039,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB156" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -15051,22 +15051,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A-145</t>
+          <t>A-148</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Diesel irrigation pumps replaced by solar pumps by 2032</t>
+          <t>Solar pump system life</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D157" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="E157" t="n">
-        <v>4000</v>
+        <v>20</v>
       </c>
       <c r="F157" t="n">
         <v>89.76052799999999</v>
@@ -15132,34 +15132,34 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>243044.9091</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB157" t="n">
-        <v>261010.3716</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC157" t="n">
-        <v>17965.46250000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A-146</t>
+          <t>A-149</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Diesel use per irrigation pump a year</t>
+          <t>Mogadishu waste deposited at the managed landfill with gas capture (full operation)</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1500</v>
+        <v>150000</v>
       </c>
       <c r="D158" t="n">
-        <v>2500</v>
+        <v>230000</v>
       </c>
       <c r="E158" t="n">
-        <v>4000</v>
+        <v>450000</v>
       </c>
       <c r="F158" t="n">
         <v>89.76052799999999</v>
@@ -15225,34 +15225,34 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>244242.6066</v>
+        <v>229650.1673810272</v>
       </c>
       <c r="AB158" t="n">
-        <v>256219.5816</v>
+        <v>266370.1673810272</v>
       </c>
       <c r="AC158" t="n">
-        <v>11976.97499999998</v>
+        <v>36720</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A-147</t>
+          <t>A-150</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Solar pumping system cost per pump replaced</t>
+          <t>Landfill gas collection and destruction efficiency over the site's life</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4000</v>
+        <v>0.3</v>
       </c>
       <c r="D159" t="n">
-        <v>5000</v>
+        <v>0.5</v>
       </c>
       <c r="E159" t="n">
-        <v>8000</v>
+        <v>0.7</v>
       </c>
       <c r="F159" t="n">
         <v>89.76052799999999</v>
@@ -15318,34 +15318,34 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>249033.3966</v>
+        <v>183138.1673810272</v>
       </c>
       <c r="AB159" t="n">
-        <v>249033.3966</v>
+        <v>295746.1673810272</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>112608</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A-148</t>
+          <t>A-151</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Solar pump system life</t>
+          <t>Long-run methane potential per tonne of waste at a managed anaerobic site</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>15</v>
+        <v>1.36</v>
       </c>
       <c r="E160" t="n">
-        <v>20</v>
+        <v>1.7</v>
       </c>
       <c r="F160" t="n">
         <v>89.76052799999999</v>
@@ -15411,34 +15411,34 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>249033.3966</v>
+        <v>231990.1673810272</v>
       </c>
       <c r="AB160" t="n">
-        <v>249033.3966</v>
+        <v>246480.1673810272</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>14490</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A-149</t>
+          <t>A-152</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mogadishu waste deposited at the managed landfill with gas capture (full operation)</t>
+          <t>Landfill and gas capture capital cost per tonne of annual capacity</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>150000</v>
+        <v>25</v>
       </c>
       <c r="D161" t="n">
-        <v>230000</v>
+        <v>40</v>
       </c>
       <c r="E161" t="n">
-        <v>450000</v>
+        <v>70</v>
       </c>
       <c r="F161" t="n">
         <v>89.76052799999999</v>
@@ -15504,34 +15504,34 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>239241.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB161" t="n">
-        <v>275961.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC161" t="n">
-        <v>36720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A-150</t>
+          <t>A-153</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Landfill gas collection and destruction efficiency over the site's life</t>
+          <t>Landfill cell and gas system life</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="D162" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7</v>
+        <v>25</v>
       </c>
       <c r="F162" t="n">
         <v>89.76052799999999</v>
@@ -15597,34 +15597,34 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>192729.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB162" t="n">
-        <v>305337.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC162" t="n">
-        <v>112608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A-151</t>
+          <t>A-154</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Long-run methane potential per tonne of waste at a managed anaerobic site</t>
+          <t>Electric buses in service by 2032</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D163" t="n">
-        <v>1.36</v>
+        <v>100</v>
       </c>
       <c r="E163" t="n">
-        <v>1.7</v>
+        <v>200</v>
       </c>
       <c r="F163" t="n">
         <v>89.76052799999999</v>
@@ -15690,34 +15690,34 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>241581.3966</v>
+        <v>237240.3173810272</v>
       </c>
       <c r="AB163" t="n">
-        <v>256071.3966</v>
+        <v>243845.8673810272</v>
       </c>
       <c r="AC163" t="n">
-        <v>14490</v>
+        <v>6605.550000000017</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A-152</t>
+          <t>A-155</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Landfill and gas capture capital cost per tonne of annual capacity</t>
+          <t>Distance per bus a year</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>25</v>
+        <v>45000</v>
       </c>
       <c r="D164" t="n">
-        <v>40</v>
+        <v>60000</v>
       </c>
       <c r="E164" t="n">
-        <v>70</v>
+        <v>75000</v>
       </c>
       <c r="F164" t="n">
         <v>89.76052799999999</v>
@@ -15783,34 +15783,34 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>249033.3966</v>
+        <v>238341.2423810272</v>
       </c>
       <c r="AB164" t="n">
-        <v>249033.3966</v>
+        <v>240543.0923810272</v>
       </c>
       <c r="AC164" t="n">
-        <v>0</v>
+        <v>2201.849999999977</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A-153</t>
+          <t>A-156</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Landfill cell and gas system life</t>
+          <t>Diesel use of the bus replaced</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>15</v>
+        <v>0.33</v>
       </c>
       <c r="D165" t="n">
-        <v>20</v>
+        <v>0.4</v>
       </c>
       <c r="E165" t="n">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="F165" t="n">
         <v>89.76052799999999</v>
@@ -15876,34 +15876,34 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>249033.3966</v>
+        <v>238436.1014810272</v>
       </c>
       <c r="AB165" t="n">
-        <v>249033.3966</v>
+        <v>240879.4043810272</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>2443.30290000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A-154</t>
+          <t>A-157</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Electric buses in service by 2032</t>
+          <t>Electric bus energy use</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>100</v>
+        <v>1.2</v>
       </c>
       <c r="E166" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="F166" t="n">
         <v>89.76052799999999</v>
@@ -15969,34 +15969,34 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>246831.5466</v>
+        <v>239666.3753810272</v>
       </c>
       <c r="AB166" t="n">
-        <v>253437.0966</v>
+        <v>239105.8553810272</v>
       </c>
       <c r="AC166" t="n">
-        <v>6605.549999999988</v>
+        <v>560.5199999999895</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A-155</t>
+          <t>A-158</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Distance per bus a year</t>
+          <t>Share of bus charging from solar</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>45000</v>
+        <v>0.4</v>
       </c>
       <c r="D167" t="n">
-        <v>60000</v>
+        <v>0.7</v>
       </c>
       <c r="E167" t="n">
-        <v>75000</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
         <v>89.76052799999999</v>
@@ -16062,34 +16062,34 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>247932.4716</v>
+        <v>238096.9193810272</v>
       </c>
       <c r="AB167" t="n">
-        <v>250134.3216</v>
+        <v>240787.4153810272</v>
       </c>
       <c r="AC167" t="n">
-        <v>2201.850000000006</v>
+        <v>2690.496000000014</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A-156</t>
+          <t>A-159</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Diesel use of the bus replaced</t>
+          <t>Electric bus and charger cost</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.33</v>
+        <v>250000</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4</v>
+        <v>350000</v>
       </c>
       <c r="E168" t="n">
-        <v>0.5</v>
+        <v>450000</v>
       </c>
       <c r="F168" t="n">
         <v>89.76052799999999</v>
@@ -16155,34 +16155,34 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>248027.3307</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB168" t="n">
-        <v>250470.6336</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC168" t="n">
-        <v>2443.30290000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A-157</t>
+          <t>A-160</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Electric bus energy use</t>
+          <t>Diesel bus cost (counterfactual)</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>120000</v>
       </c>
       <c r="D169" t="n">
-        <v>1.2</v>
+        <v>150000</v>
       </c>
       <c r="E169" t="n">
-        <v>1.5</v>
+        <v>200000</v>
       </c>
       <c r="F169" t="n">
         <v>89.76052799999999</v>
@@ -16248,34 +16248,34 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>249257.6046</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB169" t="n">
-        <v>248697.0846</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC169" t="n">
-        <v>560.5199999999895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A-158</t>
+          <t>A-161</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Share of bus charging from solar</t>
+          <t>Bus life</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.4</v>
+        <v>10</v>
       </c>
       <c r="D170" t="n">
-        <v>0.7</v>
+        <v>12</v>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F170" t="n">
         <v>89.76052799999999</v>
@@ -16341,34 +16341,34 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>247688.1486</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB170" t="n">
-        <v>250378.6446</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC170" t="n">
-        <v>2690.495999999985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A-159</t>
+          <t>A-163</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Electric bus and charger cost</t>
+          <t>Charcoal saved per efficient stove a year</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>250000</v>
+        <v>0.2</v>
       </c>
       <c r="D171" t="n">
-        <v>350000</v>
+        <v>0.35</v>
       </c>
       <c r="E171" t="n">
-        <v>450000</v>
+        <v>0.5</v>
       </c>
       <c r="F171" t="n">
         <v>89.76052799999999</v>
@@ -16434,34 +16434,34 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>249033.3966</v>
+        <v>170419.3673810272</v>
       </c>
       <c r="AB171" t="n">
-        <v>249033.3966</v>
+        <v>308464.9673810272</v>
       </c>
       <c r="AC171" t="n">
-        <v>0</v>
+        <v>138045.6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A-160</t>
+          <t>A-164</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Diesel bus cost (counterfactual)</t>
+          <t>Fraction of non-renewable biomass (physical estimate, national)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>120000</v>
+        <v>0.4</v>
       </c>
       <c r="D172" t="n">
-        <v>150000</v>
+        <v>0.64</v>
       </c>
       <c r="E172" t="n">
-        <v>200000</v>
+        <v>0.8</v>
       </c>
       <c r="F172" t="n">
         <v>89.76052799999999</v>
@@ -16527,34 +16527,34 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>249033.3966</v>
+        <v>174257.2013810272</v>
       </c>
       <c r="AB172" t="n">
-        <v>249033.3966</v>
+        <v>282898.8113810272</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>108641.61</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A-161</t>
+          <t>A-166</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Bus life</t>
+          <t>Share of stoves sold in Banaadir</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="D173" t="n">
-        <v>12</v>
+        <v>0.6</v>
       </c>
       <c r="E173" t="n">
-        <v>15</v>
+        <v>0.8</v>
       </c>
       <c r="F173" t="n">
         <v>89.76052799999999</v>
@@ -16620,10 +16620,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB173" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -16632,22 +16632,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A-163</t>
+          <t>A-169</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Charcoal saved per efficient stove a year</t>
+          <t>Stove life</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>0.35</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F174" t="n">
         <v>89.76052799999999</v>
@@ -16713,34 +16713,34 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>180010.5966</v>
+        <v>202574.5673810272</v>
       </c>
       <c r="AB174" t="n">
-        <v>318056.1966</v>
+        <v>264667.3673810272</v>
       </c>
       <c r="AC174" t="n">
-        <v>138045.6</v>
+        <v>62092.80000000005</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A-164</t>
+          <t>A-170</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Fraction of non-renewable biomass (physical estimate, national)</t>
+          <t>Charcoal price in Mogadishu</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="D175" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="E175" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="F175" t="n">
         <v>89.76052799999999</v>
@@ -16806,34 +16806,34 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>183848.4306</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB175" t="n">
-        <v>292490.0406</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC175" t="n">
-        <v>108641.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A-166</t>
+          <t>A-171</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Share of stoves sold in Banaadir</t>
+          <t>Fruit: share of domestic sales that replaces imported juice and fruit</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D176" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F176" t="n">
         <v>89.76052799999999</v>
@@ -16872,13 +16872,13 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8869256391176473</v>
       </c>
       <c r="S176" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8520891591176474</v>
       </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>0.03483647999999995</v>
       </c>
       <c r="U176" t="n">
         <v>17836.8</v>
@@ -16890,19 +16890,19 @@
         <v>0</v>
       </c>
       <c r="X176" t="n">
-        <v>227.379276</v>
+        <v>226.834956</v>
       </c>
       <c r="Y176" t="n">
-        <v>227.379276</v>
+        <v>227.923596</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>1.088639999999998</v>
       </c>
       <c r="AA176" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB176" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -16911,22 +16911,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A-169</t>
+          <t>A-172</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Stove life</t>
+          <t>Dairy: share of domestic sales that replaces imported milk powder (the rest replaces raw milk sold informally)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="D177" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="E177" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="F177" t="n">
         <v>89.76052799999999</v>
@@ -16965,13 +16965,13 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0.8695073991176471</v>
+        <v>1.003876679117647</v>
       </c>
       <c r="S177" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.7351381191176473</v>
       </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>0.2687385599999995</v>
       </c>
       <c r="U177" t="n">
         <v>17836.8</v>
@@ -16983,43 +16983,43 @@
         <v>0</v>
       </c>
       <c r="X177" t="n">
-        <v>227.379276</v>
+        <v>223.180236</v>
       </c>
       <c r="Y177" t="n">
-        <v>227.379276</v>
+        <v>231.578316</v>
       </c>
       <c r="Z177" t="n">
-        <v>0</v>
+        <v>8.398079999999993</v>
       </c>
       <c r="AA177" t="n">
-        <v>212165.7965999999</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB177" t="n">
-        <v>274258.5966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC177" t="n">
-        <v>62092.80000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A-170</t>
+          <t>A-177</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Charcoal price in Mogadishu</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: direct jobs per unit of annual capacity in operation</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.28</v>
+        <v>0.05</v>
       </c>
       <c r="D178" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="E178" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="F178" t="n">
         <v>89.76052799999999</v>
@@ -17067,13 +17067,13 @@
         <v>0</v>
       </c>
       <c r="U178" t="n">
-        <v>17836.8</v>
+        <v>17776.8</v>
       </c>
       <c r="V178" t="n">
-        <v>17836.8</v>
+        <v>17956.8</v>
       </c>
       <c r="W178" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="X178" t="n">
         <v>227.379276</v>
@@ -17085,10 +17085,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB178" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -17097,22 +17097,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A-171</t>
+          <t>A-178</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fruit: share of domestic sales that replaces imported juice and fruit</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: capital cost per unit of annual capacity</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.3</v>
+        <v>2000</v>
       </c>
       <c r="D179" t="n">
-        <v>0.5</v>
+        <v>3000</v>
       </c>
       <c r="E179" t="n">
-        <v>0.7</v>
+        <v>6000</v>
       </c>
       <c r="F179" t="n">
         <v>89.76052799999999</v>
@@ -17151,13 +17151,13 @@
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.8869256391176473</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S179" t="n">
-        <v>0.8520891591176474</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T179" t="n">
-        <v>0.03483647999999995</v>
+        <v>0</v>
       </c>
       <c r="U179" t="n">
         <v>17836.8</v>
@@ -17169,19 +17169,19 @@
         <v>0</v>
       </c>
       <c r="X179" t="n">
-        <v>226.834956</v>
+        <v>227.379276</v>
       </c>
       <c r="Y179" t="n">
-        <v>227.923596</v>
+        <v>227.379276</v>
       </c>
       <c r="Z179" t="n">
-        <v>1.088639999999998</v>
+        <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB179" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -17190,22 +17190,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A-172</t>
+          <t>A-179</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dairy: share of domestic sales that replaces imported milk powder (the rest replaces raw milk sold informally)</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of output sold in Somalia (replacing imports); the rest is exported</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="E180" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="F180" t="n">
         <v>89.76052799999999</v>
@@ -17244,13 +17244,13 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>1.003876679117647</v>
+        <v>0.8840225991176468</v>
       </c>
       <c r="S180" t="n">
-        <v>0.7351381191176473</v>
+        <v>0.8404769991176467</v>
       </c>
       <c r="T180" t="n">
-        <v>0.2687385599999995</v>
+        <v>0.04354560000000007</v>
       </c>
       <c r="U180" t="n">
         <v>17836.8</v>
@@ -17262,19 +17262,19 @@
         <v>0</v>
       </c>
       <c r="X180" t="n">
-        <v>223.180236</v>
+        <v>227.379276</v>
       </c>
       <c r="Y180" t="n">
-        <v>231.578316</v>
+        <v>227.379276</v>
       </c>
       <c r="Z180" t="n">
-        <v>8.398079999999993</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB180" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -17283,22 +17283,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A-177</t>
+          <t>A-180</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: direct jobs per unit of annual capacity in operation</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: imported inputs as a share of gross output</t>
         </is>
       </c>
       <c r="C181" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D181" t="n">
         <v>0.05</v>
       </c>
-      <c r="D181" t="n">
+      <c r="E181" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0.2</v>
       </c>
       <c r="F181" t="n">
         <v>89.76052799999999</v>
@@ -17310,64 +17310,64 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>200.5319613970588</v>
+        <v>200.6070055147059</v>
       </c>
       <c r="J181" t="n">
-        <v>200.5319613970588</v>
+        <v>200.406887867647</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>0.2001176470588462</v>
       </c>
       <c r="L181" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008234540703530691</v>
       </c>
       <c r="M181" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008226326250072432</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>8.214453458258233e-06</v>
       </c>
       <c r="O181" t="n">
-        <v>120.3191768382353</v>
+        <v>120.3642033088235</v>
       </c>
       <c r="P181" t="n">
-        <v>120.3191768382353</v>
+        <v>120.2441327205882</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>0.1200705882352935</v>
       </c>
       <c r="R181" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8716086344117647</v>
       </c>
       <c r="S181" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8660053402941175</v>
       </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>0.005603294117647262</v>
       </c>
       <c r="U181" t="n">
-        <v>17776.8</v>
+        <v>17836.8</v>
       </c>
       <c r="V181" t="n">
-        <v>17956.8</v>
+        <v>17836.8</v>
       </c>
       <c r="W181" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="X181" t="n">
-        <v>227.379276</v>
+        <v>227.651436</v>
       </c>
       <c r="Y181" t="n">
-        <v>227.379276</v>
+        <v>226.925676</v>
       </c>
       <c r="Z181" t="n">
-        <v>0</v>
+        <v>0.7257599999999798</v>
       </c>
       <c r="AA181" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB181" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -17376,22 +17376,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A-178</t>
+          <t>A-181</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: capital cost per unit of annual capacity</t>
+          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2000</v>
+        <v>0.2</v>
       </c>
       <c r="D182" t="n">
-        <v>3000</v>
+        <v>0.3</v>
       </c>
       <c r="E182" t="n">
-        <v>6000</v>
+        <v>0.5</v>
       </c>
       <c r="F182" t="n">
         <v>89.76052799999999</v>
@@ -17403,40 +17403,40 @@
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>200.5319613970588</v>
+        <v>200.0316672794117</v>
       </c>
       <c r="J182" t="n">
-        <v>200.5319613970588</v>
+        <v>201.5325496323529</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>1.500882352941204</v>
       </c>
       <c r="L182" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008210924149838204</v>
       </c>
       <c r="M182" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008272532550775124</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>6.160840093692027e-05</v>
       </c>
       <c r="O182" t="n">
-        <v>120.3191768382353</v>
+        <v>120.0190003676471</v>
       </c>
       <c r="P182" t="n">
-        <v>120.3191768382353</v>
+        <v>120.9195297794117</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>0.900529411764694</v>
       </c>
       <c r="R182" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8554991638235295</v>
       </c>
       <c r="S182" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8975238697058823</v>
       </c>
       <c r="T182" t="n">
-        <v>0</v>
+        <v>0.04202470588235274</v>
       </c>
       <c r="U182" t="n">
         <v>17836.8</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB182" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -17469,22 +17469,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A-179</t>
+          <t>A-182</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of output sold in Somalia (replacing imports); the rest is exported</t>
+          <t>Aromatic resins: share of resin processed that would otherwise have been exported raw</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D183" t="n">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="E183" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
         <v>89.76052799999999</v>
@@ -17523,13 +17523,13 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>0.8840225991176468</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S183" t="n">
-        <v>0.8404769991176467</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T183" t="n">
-        <v>0.04354560000000007</v>
+        <v>0</v>
       </c>
       <c r="U183" t="n">
         <v>17836.8</v>
@@ -17541,19 +17541,19 @@
         <v>0</v>
       </c>
       <c r="X183" t="n">
-        <v>227.379276</v>
+        <v>228.286476</v>
       </c>
       <c r="Y183" t="n">
-        <v>227.379276</v>
+        <v>226.925676</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1.360799999999983</v>
       </c>
       <c r="AA183" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB183" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -17562,22 +17562,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A-180</t>
+          <t>A-183</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: imported inputs as a share of gross output</t>
+          <t>Aromatic resins: raw-resin export value forgone per tonne</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.02</v>
+        <v>4000</v>
       </c>
       <c r="D184" t="n">
-        <v>0.05</v>
+        <v>6000</v>
       </c>
       <c r="E184" t="n">
-        <v>0.1</v>
+        <v>8000</v>
       </c>
       <c r="F184" t="n">
         <v>89.76052799999999</v>
@@ -17589,40 +17589,40 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>200.6070055147059</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J184" t="n">
-        <v>200.406887867647</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K184" t="n">
-        <v>0.2001176470588462</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0.008234540703530691</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M184" t="n">
-        <v>0.008226326250072432</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N184" t="n">
-        <v>8.214453458258233e-06</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>120.3642033088235</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P184" t="n">
-        <v>120.2441327205882</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.1200705882352935</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>0.8716086344117647</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S184" t="n">
-        <v>0.8660053402941175</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T184" t="n">
-        <v>0.005603294117647262</v>
+        <v>0</v>
       </c>
       <c r="U184" t="n">
         <v>17836.8</v>
@@ -17634,19 +17634,19 @@
         <v>0</v>
       </c>
       <c r="X184" t="n">
-        <v>227.651436</v>
+        <v>228.740076</v>
       </c>
       <c r="Y184" t="n">
-        <v>226.925676</v>
+        <v>226.018476</v>
       </c>
       <c r="Z184" t="n">
-        <v>0.7257599999999798</v>
+        <v>2.721599999999995</v>
       </c>
       <c r="AA184" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB184" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -17655,22 +17655,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A-181</t>
+          <t>A-188</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Frankincense and myrrh: grading, cleaning, distillation of essential oils and extracts: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: direct jobs per unit of annual capacity in operation</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.2</v>
+        <v>0.001</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3</v>
+        <v>0.002</v>
       </c>
       <c r="E185" t="n">
-        <v>0.5</v>
+        <v>0.004</v>
       </c>
       <c r="F185" t="n">
         <v>89.76052799999999</v>
@@ -17682,49 +17682,49 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>200.0316672794117</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J185" t="n">
-        <v>201.5325496323529</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K185" t="n">
-        <v>1.500882352941204</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0.008210924149838204</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M185" t="n">
-        <v>0.008272532550775124</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N185" t="n">
-        <v>6.160840093692027e-05</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
-        <v>120.0190003676471</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P185" t="n">
-        <v>120.9195297794117</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.900529411764694</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>0.8554991638235295</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S185" t="n">
-        <v>0.8975238697058823</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T185" t="n">
-        <v>0.04202470588235274</v>
+        <v>0</v>
       </c>
       <c r="U185" t="n">
-        <v>17836.8</v>
+        <v>17696.8</v>
       </c>
       <c r="V185" t="n">
-        <v>17836.8</v>
+        <v>18116.8</v>
       </c>
       <c r="W185" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="X185" t="n">
         <v>227.379276</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB185" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -17748,22 +17748,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A-182</t>
+          <t>A-189</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Aromatic resins: share of resin processed that would otherwise have been exported raw</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: capital cost per unit of annual capacity</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="D186" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F186" t="n">
         <v>89.76052799999999</v>
@@ -17820,19 +17820,19 @@
         <v>0</v>
       </c>
       <c r="X186" t="n">
-        <v>228.286476</v>
+        <v>227.379276</v>
       </c>
       <c r="Y186" t="n">
-        <v>226.925676</v>
+        <v>227.379276</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.360799999999983</v>
+        <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB186" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -17841,22 +17841,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A-183</t>
+          <t>A-190</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Aromatic resins: raw-resin export value forgone per tonne</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of output sold in Somalia (replacing imports); the rest is exported</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4000</v>
+        <v>0.9</v>
       </c>
       <c r="D187" t="n">
-        <v>6000</v>
+        <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
         <v>89.76052799999999</v>
@@ -17895,13 +17895,13 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8755553991176471</v>
       </c>
       <c r="S187" t="n">
         <v>0.8695073991176471</v>
       </c>
       <c r="T187" t="n">
-        <v>0</v>
+        <v>0.006048000000000053</v>
       </c>
       <c r="U187" t="n">
         <v>17836.8</v>
@@ -17913,19 +17913,19 @@
         <v>0</v>
       </c>
       <c r="X187" t="n">
-        <v>228.740076</v>
+        <v>227.568276</v>
       </c>
       <c r="Y187" t="n">
-        <v>226.018476</v>
+        <v>227.379276</v>
       </c>
       <c r="Z187" t="n">
-        <v>2.721599999999995</v>
+        <v>0.188999999999993</v>
       </c>
       <c r="AA187" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB187" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -17934,22 +17934,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A-188</t>
+          <t>A-191</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: direct jobs per unit of annual capacity in operation</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: imported inputs as a share of gross output</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.001</v>
+        <v>0.25</v>
       </c>
       <c r="D188" t="n">
-        <v>0.002</v>
+        <v>0.35</v>
       </c>
       <c r="E188" t="n">
-        <v>0.004</v>
+        <v>0.5</v>
       </c>
       <c r="F188" t="n">
         <v>89.76052799999999</v>
@@ -17961,64 +17961,64 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>200.5319613970588</v>
+        <v>200.7056746323529</v>
       </c>
       <c r="J188" t="n">
-        <v>200.5319613970588</v>
+        <v>200.2713915441176</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>0.4342830882353041</v>
       </c>
       <c r="L188" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008238590885444135</v>
       </c>
       <c r="M188" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008220764380543406</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1.782650490072916e-05</v>
       </c>
       <c r="O188" t="n">
-        <v>120.3191768382353</v>
+        <v>120.4234047794118</v>
       </c>
       <c r="P188" t="n">
-        <v>120.3191768382353</v>
+        <v>120.1628349264706</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>0.260569852941174</v>
       </c>
       <c r="R188" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8743713697058827</v>
       </c>
       <c r="S188" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8622114432352943</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>0.01215992647058839</v>
       </c>
       <c r="U188" t="n">
-        <v>17696.8</v>
+        <v>17836.8</v>
       </c>
       <c r="V188" t="n">
-        <v>18116.8</v>
+        <v>17836.8</v>
       </c>
       <c r="W188" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="X188" t="n">
-        <v>227.379276</v>
+        <v>227.757276</v>
       </c>
       <c r="Y188" t="n">
-        <v>227.379276</v>
+        <v>226.812276</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>0.9449999999999932</v>
       </c>
       <c r="AA188" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB188" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -18027,22 +18027,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A-189</t>
+          <t>A-192</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: capital cost per unit of annual capacity</t>
+          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="D189" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="E189" t="n">
-        <v>20</v>
+        <v>0.7</v>
       </c>
       <c r="F189" t="n">
         <v>89.76052799999999</v>
@@ -18054,40 +18054,40 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>200.5319613970588</v>
+        <v>200.2540202205882</v>
       </c>
       <c r="J189" t="n">
-        <v>200.5319613970588</v>
+        <v>200.8099025735294</v>
       </c>
       <c r="K189" t="n">
-        <v>0</v>
+        <v>0.5558823529411825</v>
       </c>
       <c r="L189" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008220051320347376</v>
       </c>
       <c r="M189" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008242869246620311</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.281792627293472e-05</v>
       </c>
       <c r="O189" t="n">
-        <v>120.3191768382353</v>
+        <v>120.1524121323529</v>
       </c>
       <c r="P189" t="n">
-        <v>120.3191768382353</v>
+        <v>120.4859415441177</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>0.3335294117647152</v>
       </c>
       <c r="R189" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8617250461764707</v>
       </c>
       <c r="S189" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.877289752058824</v>
       </c>
       <c r="T189" t="n">
-        <v>0</v>
+        <v>0.01556470588235326</v>
       </c>
       <c r="U189" t="n">
         <v>17836.8</v>
@@ -18108,10 +18108,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB189" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -18120,22 +18120,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A-190</t>
+          <t>A-193</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of output sold in Somalia (replacing imports); the rest is exported</t>
+          <t>Stoves: share of domestic sales that replaces imported stoves</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F190" t="n">
         <v>89.76052799999999</v>
@@ -18174,13 +18174,13 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.8755553991176471</v>
+        <v>0.8936993991176471</v>
       </c>
       <c r="S190" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8332193991176471</v>
       </c>
       <c r="T190" t="n">
-        <v>0.006048000000000053</v>
+        <v>0.06047999999999998</v>
       </c>
       <c r="U190" t="n">
         <v>17836.8</v>
@@ -18192,19 +18192,19 @@
         <v>0</v>
       </c>
       <c r="X190" t="n">
-        <v>227.568276</v>
+        <v>226.623276</v>
       </c>
       <c r="Y190" t="n">
-        <v>227.379276</v>
+        <v>228.513276</v>
       </c>
       <c r="Z190" t="n">
-        <v>0.188999999999993</v>
+        <v>1.889999999999986</v>
       </c>
       <c r="AA190" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB190" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -18213,22 +18213,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A-191</t>
+          <t>A-200</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: imported inputs as a share of gross output</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: direct jobs per unit of annual capacity in operation</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.25</v>
+        <v>0.005</v>
       </c>
       <c r="D191" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="E191" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="F191" t="n">
         <v>89.76052799999999</v>
@@ -18240,64 +18240,64 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>200.7056746323529</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J191" t="n">
-        <v>200.2713915441176</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K191" t="n">
-        <v>0.4342830882353041</v>
+        <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0.008238590885444135</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M191" t="n">
-        <v>0.008220764380543406</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N191" t="n">
-        <v>1.782650490072916e-05</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>120.4234047794118</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P191" t="n">
-        <v>120.1628349264706</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.260569852941174</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>0.8743713697058827</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S191" t="n">
-        <v>0.8622114432352943</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T191" t="n">
-        <v>0.01215992647058839</v>
+        <v>0</v>
       </c>
       <c r="U191" t="n">
-        <v>17836.8</v>
+        <v>17756.8</v>
       </c>
       <c r="V191" t="n">
-        <v>17836.8</v>
+        <v>17996.8</v>
       </c>
       <c r="W191" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X191" t="n">
-        <v>227.757276</v>
+        <v>227.379276</v>
       </c>
       <c r="Y191" t="n">
-        <v>226.812276</v>
+        <v>227.379276</v>
       </c>
       <c r="Z191" t="n">
-        <v>0.9449999999999932</v>
+        <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB191" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -18306,22 +18306,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A-192</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Efficient cookstoves (jikos) for charcoal and pellets: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: capital cost per unit of annual capacity</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.3</v>
+        <v>80</v>
       </c>
       <c r="D192" t="n">
-        <v>0.5</v>
+        <v>150</v>
       </c>
       <c r="E192" t="n">
-        <v>0.7</v>
+        <v>250</v>
       </c>
       <c r="F192" t="n">
         <v>89.76052799999999</v>
@@ -18333,40 +18333,40 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>200.2540202205882</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J192" t="n">
-        <v>200.8099025735294</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K192" t="n">
-        <v>0.5558823529411825</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0.008220051320347376</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M192" t="n">
-        <v>0.008242869246620311</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N192" t="n">
-        <v>2.281792627293472e-05</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>120.1524121323529</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P192" t="n">
-        <v>120.4859415441177</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q192" t="n">
-        <v>0.3335294117647152</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>0.8617250461764707</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S192" t="n">
-        <v>0.877289752058824</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T192" t="n">
-        <v>0.01556470588235326</v>
+        <v>0</v>
       </c>
       <c r="U192" t="n">
         <v>17836.8</v>
@@ -18387,10 +18387,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB192" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -18399,22 +18399,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A-193</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Stoves: share of domestic sales that replaces imported stoves</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of output sold in Somalia (replacing imports); the rest is exported</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="D193" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
         <v>89.76052799999999</v>
@@ -18453,13 +18453,13 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>0.8936993991176471</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S193" t="n">
-        <v>0.8332193991176471</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T193" t="n">
-        <v>0.06047999999999998</v>
+        <v>0</v>
       </c>
       <c r="U193" t="n">
         <v>17836.8</v>
@@ -18471,19 +18471,19 @@
         <v>0</v>
       </c>
       <c r="X193" t="n">
-        <v>226.623276</v>
+        <v>227.530476</v>
       </c>
       <c r="Y193" t="n">
-        <v>228.513276</v>
+        <v>227.379276</v>
       </c>
       <c r="Z193" t="n">
-        <v>1.889999999999986</v>
+        <v>0.1511999999999887</v>
       </c>
       <c r="AA193" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB193" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -18492,22 +18492,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A-200</t>
+          <t>A-203</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: direct jobs per unit of annual capacity in operation</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: imported inputs as a share of gross output</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="D194" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E194" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F194" t="n">
         <v>89.76052799999999</v>
@@ -18519,64 +18519,64 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>200.5319613970588</v>
+        <v>200.5653143382353</v>
       </c>
       <c r="J194" t="n">
-        <v>200.5319613970588</v>
+        <v>200.4763731617647</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>0.08894117647059829</v>
       </c>
       <c r="L194" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008232829359060221</v>
       </c>
       <c r="M194" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.00822917849085655</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>3.65086820367129e-06</v>
       </c>
       <c r="O194" t="n">
-        <v>120.3191768382353</v>
+        <v>120.3391886029412</v>
       </c>
       <c r="P194" t="n">
-        <v>120.3191768382353</v>
+        <v>120.2858238970588</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>0.05336470588234477</v>
       </c>
       <c r="R194" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8704412814705883</v>
       </c>
       <c r="S194" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8679509285294119</v>
       </c>
       <c r="T194" t="n">
-        <v>0</v>
+        <v>0.002490352941176388</v>
       </c>
       <c r="U194" t="n">
-        <v>17756.8</v>
+        <v>17836.8</v>
       </c>
       <c r="V194" t="n">
-        <v>17996.8</v>
+        <v>17836.8</v>
       </c>
       <c r="W194" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="X194" t="n">
-        <v>227.379276</v>
+        <v>227.424636</v>
       </c>
       <c r="Y194" t="n">
-        <v>227.379276</v>
+        <v>227.303676</v>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>0.1209599999999966</v>
       </c>
       <c r="AA194" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB194" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -18585,22 +18585,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-204</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: capital cost per unit of annual capacity</t>
+          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>80</v>
+        <v>0.6</v>
       </c>
       <c r="D195" t="n">
-        <v>150</v>
+        <v>0.8</v>
       </c>
       <c r="E195" t="n">
-        <v>250</v>
+        <v>0.9</v>
       </c>
       <c r="F195" t="n">
         <v>89.76052799999999</v>
@@ -18612,40 +18612,40 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>200.5319613970588</v>
+        <v>200.3512996323529</v>
       </c>
       <c r="J195" t="n">
-        <v>200.5319613970588</v>
+        <v>200.6222922794117</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>0.2709926470588186</v>
       </c>
       <c r="L195" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008224044457445141</v>
       </c>
       <c r="M195" t="n">
-        <v>0.008231460283483844</v>
+        <v>0.008235168196503195</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1.112373905805437e-05</v>
       </c>
       <c r="O195" t="n">
-        <v>120.3191768382353</v>
+        <v>120.2107797794118</v>
       </c>
       <c r="P195" t="n">
-        <v>120.3191768382353</v>
+        <v>120.3733753676471</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>0.1625955882352912</v>
       </c>
       <c r="R195" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8644488697058823</v>
       </c>
       <c r="S195" t="n">
-        <v>0.8695073991176471</v>
+        <v>0.8720366638235295</v>
       </c>
       <c r="T195" t="n">
-        <v>0</v>
+        <v>0.007587794117647206</v>
       </c>
       <c r="U195" t="n">
         <v>17836.8</v>
@@ -18666,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB195" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -18678,22 +18678,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-207</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of output sold in Somalia (replacing imports); the rest is exported</t>
+          <t>Charcoal replaced per tonne of pellets or briquettes</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F196" t="n">
         <v>89.76052799999999</v>
@@ -18750,43 +18750,43 @@
         <v>0</v>
       </c>
       <c r="X196" t="n">
-        <v>227.530476</v>
+        <v>227.379276</v>
       </c>
       <c r="Y196" t="n">
         <v>227.379276</v>
       </c>
       <c r="Z196" t="n">
-        <v>0.1511999999999887</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>249033.3966</v>
+        <v>236248.8233810272</v>
       </c>
       <c r="AB196" t="n">
-        <v>249033.3966</v>
+        <v>242635.5113810272</v>
       </c>
       <c r="AC196" t="n">
-        <v>0</v>
+        <v>6386.687999999995</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A-203</t>
+          <t>A-208</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: imported inputs as a share of gross output</t>
+          <t>Park solar and storage: premium on equipment cost for site works, interconnection, security and fragile-state delivery</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="D197" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="F197" t="n">
         <v>89.76052799999999</v>
@@ -18798,40 +18798,40 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>200.5653143382353</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J197" t="n">
-        <v>200.4763731617647</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K197" t="n">
-        <v>0.08894117647059829</v>
+        <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0.008232829359060221</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M197" t="n">
-        <v>0.00822917849085655</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N197" t="n">
-        <v>3.65086820367129e-06</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>120.3391886029412</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P197" t="n">
-        <v>120.2858238970588</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q197" t="n">
-        <v>0.05336470588234477</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>0.8704412814705883</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S197" t="n">
-        <v>0.8679509285294119</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T197" t="n">
-        <v>0.002490352941176388</v>
+        <v>0</v>
       </c>
       <c r="U197" t="n">
         <v>17836.8</v>
@@ -18843,19 +18843,19 @@
         <v>0</v>
       </c>
       <c r="X197" t="n">
-        <v>227.424636</v>
+        <v>227.379276</v>
       </c>
       <c r="Y197" t="n">
-        <v>227.303676</v>
+        <v>227.379276</v>
       </c>
       <c r="Z197" t="n">
-        <v>0.1209599999999966</v>
+        <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB197" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -18864,22 +18864,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A-204</t>
+          <t>A-209</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Biomass pellets and briquettes from Prosopis and crop residues: share of domestic input supply that is additional (new production, not diverted from other buyers)</t>
+          <t>Park solar and storage: annual operation and maintenance cost as a share of installed cost</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.6</v>
+        <v>0.015</v>
       </c>
       <c r="D198" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="E198" t="n">
-        <v>0.9</v>
+        <v>0.03</v>
       </c>
       <c r="F198" t="n">
         <v>89.76052799999999</v>
@@ -18891,40 +18891,40 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>200.3512996323529</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="J198" t="n">
-        <v>200.6222922794117</v>
+        <v>200.5319613970588</v>
       </c>
       <c r="K198" t="n">
-        <v>0.2709926470588186</v>
+        <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0.008224044457445141</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="M198" t="n">
-        <v>0.008235168196503195</v>
+        <v>0.008231460283483844</v>
       </c>
       <c r="N198" t="n">
-        <v>1.112373905805437e-05</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>120.2107797794118</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="P198" t="n">
-        <v>120.3733753676471</v>
+        <v>120.3191768382353</v>
       </c>
       <c r="Q198" t="n">
-        <v>0.1625955882352912</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0.8644488697058823</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="S198" t="n">
-        <v>0.8720366638235295</v>
+        <v>0.8695073991176471</v>
       </c>
       <c r="T198" t="n">
-        <v>0.007587794117647206</v>
+        <v>0</v>
       </c>
       <c r="U198" t="n">
         <v>17836.8</v>
@@ -18945,10 +18945,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB198" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -18957,22 +18957,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A-207</t>
+          <t>A-210</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Charcoal replaced per tonne of pellets or briquettes</t>
+          <t>Solar PV plant life</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0.45</v>
+        <v>20</v>
       </c>
       <c r="D199" t="n">
-        <v>0.6</v>
+        <v>25</v>
       </c>
       <c r="E199" t="n">
-        <v>0.75</v>
+        <v>30</v>
       </c>
       <c r="F199" t="n">
         <v>89.76052799999999</v>
@@ -19038,34 +19038,34 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>245840.0526</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB199" t="n">
-        <v>252226.7406</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC199" t="n">
-        <v>6386.688000000024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A-208</t>
+          <t>A-211</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Park solar and storage: premium on equipment cost for site works, interconnection, security and fragile-state delivery</t>
+          <t>Battery life before replacement</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.15</v>
+        <v>10</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="E200" t="n">
-        <v>0.6</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
         <v>89.76052799999999</v>
@@ -19131,10 +19131,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB200" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -19143,22 +19143,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A-209</t>
+          <t>A-212</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Park solar and storage: annual operation and maintenance cost as a share of installed cost</t>
+          <t>Average annual flood losses in Mogadishu (baseline, 2026)</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.015</v>
+        <v>80</v>
       </c>
       <c r="D201" t="n">
-        <v>0.02</v>
+        <v>120</v>
       </c>
       <c r="E201" t="n">
-        <v>0.03</v>
+        <v>160</v>
       </c>
       <c r="F201" t="n">
         <v>89.76052799999999</v>
@@ -19224,10 +19224,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB201" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -19236,22 +19236,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A-210</t>
+          <t>A-213</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Solar PV plant life</t>
+          <t>Annual growth of flood losses with population and urbanisation</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>20</v>
+        <v>0.03</v>
       </c>
       <c r="D202" t="n">
-        <v>25</v>
+        <v>0.043</v>
       </c>
       <c r="E202" t="n">
-        <v>30</v>
+        <v>0.06</v>
       </c>
       <c r="F202" t="n">
         <v>89.76052799999999</v>
@@ -19317,10 +19317,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB202" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -19329,22 +19329,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A-211</t>
+          <t>A-214</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Battery life before replacement</t>
+          <t>Share of Mogadishu's flood losses arising in catchments drained by 2032 (priority catchments, including the park-to-port corridor)</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="D203" t="n">
-        <v>12</v>
+        <v>0.3</v>
       </c>
       <c r="E203" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="F203" t="n">
         <v>89.76052799999999</v>
@@ -19410,10 +19410,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB203" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -19422,22 +19422,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A-212</t>
+          <t>A-215</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Average annual flood losses in Mogadishu (baseline, 2026)</t>
+          <t>Reduction in flood losses in a drained catchment</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>80</v>
+        <v>0.3</v>
       </c>
       <c r="D204" t="n">
-        <v>120</v>
+        <v>0.45</v>
       </c>
       <c r="E204" t="n">
-        <v>160</v>
+        <v>0.6</v>
       </c>
       <c r="F204" t="n">
         <v>89.76052799999999</v>
@@ -19503,10 +19503,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB204" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -19515,22 +19515,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A-213</t>
+          <t>A-216</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Annual growth of flood losses with population and urbanisation</t>
+          <t>Drainage investment per dollar of annual avoided flood loss</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.03</v>
+        <v>9</v>
       </c>
       <c r="D205" t="n">
-        <v>0.043</v>
+        <v>12</v>
       </c>
       <c r="E205" t="n">
-        <v>0.06</v>
+        <v>18</v>
       </c>
       <c r="F205" t="n">
         <v>89.76052799999999</v>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB205" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -19608,22 +19608,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A-214</t>
+          <t>A-217</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Share of Mogadishu's flood losses arising in catchments drained by 2032 (priority catchments, including the park-to-port corridor)</t>
+          <t>Economic life of trunk drainage</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.15</v>
+        <v>20</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="E206" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="F206" t="n">
         <v>89.76052799999999</v>
@@ -19689,10 +19689,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AB206" t="n">
-        <v>249033.3966</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -19701,22 +19701,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A-215</t>
+          <t>A-218</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Reduction in flood losses in a drained catchment</t>
+          <t>Share of the parks' electricity demand met by the solar-plus-storage system</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D207" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="E207" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="F207" t="n">
         <v>89.76052799999999</v>
@@ -19782,34 +19782,34 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>249033.3966</v>
+        <v>231659.6585810272</v>
       </c>
       <c r="AB207" t="n">
-        <v>249033.3966</v>
+        <v>245279.0489810272</v>
       </c>
       <c r="AC207" t="n">
-        <v>0</v>
+        <v>13619.3904</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A-216</t>
+          <t>A-219</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Drainage investment per dollar of annual avoided flood loss</t>
+          <t>Electricity use per unit of output: meat</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D208" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="E208" t="n">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="F208" t="n">
         <v>89.76052799999999</v>
@@ -19875,34 +19875,34 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>249033.3966</v>
+        <v>238461.2573810272</v>
       </c>
       <c r="AB208" t="n">
-        <v>249033.3966</v>
+        <v>240913.5323810272</v>
       </c>
       <c r="AC208" t="n">
-        <v>0</v>
+        <v>2452.274999999994</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A-217</t>
+          <t>A-220</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Economic life of trunk drainage</t>
+          <t>Electricity use per unit of output: tanning</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>30</v>
+        <v>1.5</v>
       </c>
       <c r="E209" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F209" t="n">
         <v>89.76052799999999</v>
@@ -19968,34 +19968,34 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>249033.3966</v>
+        <v>238984.4093810272</v>
       </c>
       <c r="AB209" t="n">
-        <v>249033.3966</v>
+        <v>240815.4413810272</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>1831.031999999977</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A-218</t>
+          <t>A-221</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Share of the parks' electricity demand met by the solar-plus-storage system</t>
+          <t>Electricity use per unit of output: fish</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.5</v>
+        <v>97</v>
       </c>
       <c r="D210" t="n">
-        <v>0.7</v>
+        <v>110</v>
       </c>
       <c r="E210" t="n">
-        <v>0.85</v>
+        <v>200</v>
       </c>
       <c r="F210" t="n">
         <v>89.76052799999999</v>
@@ -20061,34 +20061,34 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>240269.355</v>
+        <v>239238.1381010272</v>
       </c>
       <c r="AB210" t="n">
-        <v>255606.4278</v>
+        <v>240854.6777810272</v>
       </c>
       <c r="AC210" t="n">
-        <v>15337.07280000002</v>
+        <v>1616.539680000016</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A-219</t>
+          <t>A-222</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: meat</t>
+          <t>Electricity use per unit of output: sesame</t>
         </is>
       </c>
       <c r="C211" t="n">
+        <v>40</v>
+      </c>
+      <c r="D211" t="n">
+        <v>60</v>
+      </c>
+      <c r="E211" t="n">
         <v>100</v>
-      </c>
-      <c r="D211" t="n">
-        <v>150</v>
-      </c>
-      <c r="E211" t="n">
-        <v>250</v>
       </c>
       <c r="F211" t="n">
         <v>89.76052799999999</v>
@@ -20154,34 +20154,34 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>248542.9416</v>
+        <v>239289.5813810272</v>
       </c>
       <c r="AB211" t="n">
-        <v>250014.3066</v>
+        <v>239747.3393810272</v>
       </c>
       <c r="AC211" t="n">
-        <v>1471.36500000002</v>
+        <v>457.7580000000016</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A-220</t>
+          <t>A-223</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: tanning</t>
+          <t>Electricity use per unit of output: sesame oil</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D212" t="n">
-        <v>1.5</v>
+        <v>60</v>
       </c>
       <c r="E212" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="F212" t="n">
         <v>89.76052799999999</v>
@@ -20247,34 +20247,34 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>248575.6386</v>
+        <v>239411.6501810272</v>
       </c>
       <c r="AB212" t="n">
-        <v>250406.6706</v>
+        <v>239503.2017810272</v>
       </c>
       <c r="AC212" t="n">
-        <v>1831.032000000007</v>
+        <v>91.55160000000615</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A-221</t>
+          <t>A-224</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: fish</t>
+          <t>Electricity use per unit of output: fruit</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="D213" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="E213" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F213" t="n">
         <v>89.76052799999999</v>
@@ -20340,34 +20340,34 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>247463.9406</v>
+        <v>239285.2217810272</v>
       </c>
       <c r="AB213" t="n">
-        <v>252172.3086</v>
+        <v>239834.5313810272</v>
       </c>
       <c r="AC213" t="n">
-        <v>4708.368000000017</v>
+        <v>549.3096000000078</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A-222</t>
+          <t>A-225</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: sesame</t>
+          <t>Electricity use per unit of output: flour</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D214" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E214" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F214" t="n">
         <v>89.76052799999999</v>
@@ -20433,34 +20433,34 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>248880.8106</v>
+        <v>236652.0233810272</v>
       </c>
       <c r="AB214" t="n">
-        <v>249338.5686</v>
+        <v>242232.3113810272</v>
       </c>
       <c r="AC214" t="n">
-        <v>457.7580000000016</v>
+        <v>5580.288</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A-223</t>
+          <t>A-226</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: sesame oil</t>
+          <t>Electricity use per unit of output: dairy</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>50</v>
+        <v>0.02</v>
       </c>
       <c r="D215" t="n">
-        <v>80</v>
+        <v>0.03</v>
       </c>
       <c r="E215" t="n">
-        <v>120</v>
+        <v>0.06</v>
       </c>
       <c r="F215" t="n">
         <v>89.76052799999999</v>
@@ -20526,34 +20526,34 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>248987.6208</v>
+        <v>239285.2217810272</v>
       </c>
       <c r="AB215" t="n">
-        <v>249094.431</v>
+        <v>239913.0041810272</v>
       </c>
       <c r="AC215" t="n">
-        <v>106.8102000000072</v>
+        <v>627.7823999999964</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A-224</t>
+          <t>A-227</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: fruit</t>
+          <t>Electricity use per unit of output: soap</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D216" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E216" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F216" t="n">
         <v>89.76052799999999</v>
@@ -20619,34 +20619,34 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>248876.451</v>
+        <v>239311.3793810272</v>
       </c>
       <c r="AB216" t="n">
-        <v>249425.7606</v>
+        <v>239703.7433810272</v>
       </c>
       <c r="AC216" t="n">
-        <v>549.3095999999787</v>
+        <v>392.3640000000014</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A-225</t>
+          <t>A-228</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: flour</t>
+          <t>Electricity use per unit of output: diapers</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D217" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="E217" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F217" t="n">
         <v>89.76052799999999</v>
@@ -20712,34 +20712,34 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>247638.3246</v>
+        <v>239167.5125810272</v>
       </c>
       <c r="AB217" t="n">
-        <v>251126.0046</v>
+        <v>239808.3737810272</v>
       </c>
       <c r="AC217" t="n">
-        <v>3487.679999999993</v>
+        <v>640.8612000000139</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A-226</t>
+          <t>A-229</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: dairy</t>
+          <t>Electricity use per unit of output: garments</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.05</v>
+        <v>1000</v>
       </c>
       <c r="D218" t="n">
-        <v>0.1</v>
+        <v>2000</v>
       </c>
       <c r="E218" t="n">
-        <v>0.2</v>
+        <v>3000</v>
       </c>
       <c r="F218" t="n">
         <v>89.76052799999999</v>
@@ -20805,34 +20805,34 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>248248.6686</v>
+        <v>235954.4873810272</v>
       </c>
       <c r="AB218" t="n">
-        <v>250602.8526</v>
+        <v>242929.8473810272</v>
       </c>
       <c r="AC218" t="n">
-        <v>2354.184000000008</v>
+        <v>6975.359999999986</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A-227</t>
+          <t>A-230</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: soap</t>
+          <t>Electricity use per unit of output: aromatics</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D219" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="E219" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="F219" t="n">
         <v>89.76052799999999</v>
@@ -20898,34 +20898,34 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>248706.4266</v>
+        <v>239327.7278810272</v>
       </c>
       <c r="AB219" t="n">
-        <v>249687.3366</v>
+        <v>239671.0463810272</v>
       </c>
       <c r="AC219" t="n">
-        <v>980.9099999999744</v>
+        <v>343.3184999999939</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A-228</t>
+          <t>A-231</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: diapers</t>
+          <t>Electricity use per unit of output: stoves</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="D220" t="n">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="E220" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F220" t="n">
         <v>89.76052799999999</v>
@@ -20991,34 +20991,34 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>248758.7418</v>
+        <v>239245.9853810272</v>
       </c>
       <c r="AB220" t="n">
-        <v>249399.603</v>
+        <v>239769.1373810272</v>
       </c>
       <c r="AC220" t="n">
-        <v>640.8612000000139</v>
+        <v>523.1520000000019</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A-229</t>
+          <t>A-232</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: garments</t>
+          <t>Electricity use per unit of output: pellets</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="D221" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="E221" t="n">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="F221" t="n">
         <v>89.76052799999999</v>
@@ -21084,34 +21084,34 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>245545.7166</v>
+        <v>238953.8921810272</v>
       </c>
       <c r="AB221" t="n">
-        <v>252521.0766</v>
+        <v>240052.5113810272</v>
       </c>
       <c r="AC221" t="n">
-        <v>6975.359999999986</v>
+        <v>1098.619199999986</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A-230</t>
+          <t>A-233</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: aromatics</t>
+          <t>Electricity use per unit of output: bpo</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="D222" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="E222" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F222" t="n">
         <v>89.76052799999999</v>
@@ -21177,34 +21177,34 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>248918.9571</v>
+        <v>237698.3273810272</v>
       </c>
       <c r="AB222" t="n">
-        <v>249262.2756</v>
+        <v>242929.8473810272</v>
       </c>
       <c r="AC222" t="n">
-        <v>343.3184999999939</v>
+        <v>5231.51999999999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A-231</t>
+          <t>A-234</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: stoves</t>
+          <t>Irrigated land converted from diesel to solar pumping by 2032</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>20000</v>
       </c>
       <c r="E223" t="n">
-        <v>10</v>
+        <v>40000</v>
       </c>
       <c r="F223" t="n">
         <v>89.76052799999999</v>
@@ -21270,34 +21270,34 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>248837.2146</v>
+        <v>236531.6120905136</v>
       </c>
       <c r="AB223" t="n">
-        <v>249360.3666</v>
+        <v>245263.2779620544</v>
       </c>
       <c r="AC223" t="n">
-        <v>523.1520000000019</v>
+        <v>8731.665871540783</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A-232</t>
+          <t>A-235</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: pellets</t>
+          <t>Irrigation water pumped per hectare per season</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>60</v>
+        <v>1871</v>
       </c>
       <c r="D224" t="n">
-        <v>100</v>
+        <v>4151</v>
       </c>
       <c r="E224" t="n">
-        <v>150</v>
+        <v>6168</v>
       </c>
       <c r="F224" t="n">
         <v>89.76052799999999</v>
@@ -21363,34 +21363,34 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>248545.1214</v>
+        <v>236244.833696435</v>
       </c>
       <c r="AB224" t="n">
-        <v>249643.7406</v>
+        <v>242270.685820423</v>
       </c>
       <c r="AC224" t="n">
-        <v>1098.619199999986</v>
+        <v>6025.852123987919</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A-233</t>
+          <t>A-236</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Electricity use per unit of output: bpo</t>
+          <t>Irrigated seasons a year (Gu and Deyr)</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="E225" t="n">
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="F225" t="n">
         <v>89.76052799999999</v>
@@ -21456,13 +21456,292 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>247289.5566</v>
+        <v>236531.6120905136</v>
       </c>
       <c r="AB225" t="n">
-        <v>252521.0766</v>
+        <v>239442.1673810272</v>
       </c>
       <c r="AC225" t="n">
-        <v>5231.51999999996</v>
+        <v>2910.555290513614</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>A-237</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Total pumping head: lift from the river to the field plus pipe losses</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>5</v>
+      </c>
+      <c r="D226" t="n">
+        <v>8</v>
+      </c>
+      <c r="E226" t="n">
+        <v>12</v>
+      </c>
+      <c r="F226" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G226" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J226" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P226" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V226" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W226" t="n">
+        <v>0</v>
+      </c>
+      <c r="X226" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>237259.250913142</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>242352.7226715408</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>5093.471758398809</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>A-238</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Fuel-to-water efficiency of a small diesel pump set</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F227" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G227" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J227" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P227" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V227" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W227" t="n">
+        <v>0</v>
+      </c>
+      <c r="X227" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>242352.7226715408</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>237986.8897357704</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>4365.832935770391</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>A-240</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Solar pumping system cost per hectare served</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F228" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="G228" t="n">
+        <v>89.76052799999999</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="J228" t="n">
+        <v>200.5319613970588</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0.008231460283483844</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="P228" t="n">
+        <v>120.3191768382353</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0.8695073991176471</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="V228" t="n">
+        <v>17836.8</v>
+      </c>
+      <c r="W228" t="n">
+        <v>0</v>
+      </c>
+      <c r="X228" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>227.379276</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>239442.1673810272</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>239442.1673810272</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21518,13 +21797,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81.44596327597952</v>
+        <v>80.01450453081577</v>
       </c>
       <c r="D2" t="n">
-        <v>97.63404874142611</v>
+        <v>97.55424818941891</v>
       </c>
       <c r="E2" t="n">
-        <v>116.8126343691399</v>
+        <v>116.6902896509217</v>
       </c>
     </row>
     <row r="3">
@@ -21539,13 +21818,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>172.1118091905987</v>
+        <v>171.0615511569489</v>
       </c>
       <c r="D3" t="n">
-        <v>212.8904495380881</v>
+        <v>211.7242378714222</v>
       </c>
       <c r="E3" t="n">
-        <v>262.534945747679</v>
+        <v>262.5888261359762</v>
       </c>
     </row>
     <row r="4">
@@ -21560,13 +21839,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.007077910492579431</v>
+        <v>0.007058128779457551</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00879795446367878</v>
+        <v>0.008741395750606387</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01082217852013053</v>
+        <v>0.01085112479533864</v>
       </c>
     </row>
     <row r="5">
@@ -21581,13 +21860,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>97.83814728936549</v>
+        <v>96.8287752359673</v>
       </c>
       <c r="D5" t="n">
-        <v>127.3436906898425</v>
+        <v>126.2660440651065</v>
       </c>
       <c r="E5" t="n">
-        <v>165.6513162072338</v>
+        <v>164.2965744792341</v>
       </c>
     </row>
     <row r="6">
@@ -21602,13 +21881,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.282847262687824</v>
+        <v>-1.217309278744646</v>
       </c>
       <c r="D6" t="n">
-        <v>1.167649896930699</v>
+        <v>1.156291883231889</v>
       </c>
       <c r="E6" t="n">
-        <v>3.779589108507905</v>
+        <v>3.767653763517596</v>
       </c>
     </row>
     <row r="7">
@@ -21623,13 +21902,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15406.88953188914</v>
+        <v>15046.4234779565</v>
       </c>
       <c r="D7" t="n">
-        <v>19183.643069857</v>
+        <v>19101.8635046619</v>
       </c>
       <c r="E7" t="n">
-        <v>23786.2079315459</v>
+        <v>23907.97259964541</v>
       </c>
     </row>
     <row r="8">
@@ -21644,13 +21923,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>195.3903185770723</v>
+        <v>192.4034536708326</v>
       </c>
       <c r="D8" t="n">
-        <v>241.8317638397809</v>
+        <v>239.8817097453584</v>
       </c>
       <c r="E8" t="n">
-        <v>299.2290659270003</v>
+        <v>297.2283112075796</v>
       </c>
     </row>
     <row r="9">
@@ -21665,13 +21944,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>174070.2198095541</v>
+        <v>164140.5167101344</v>
       </c>
       <c r="D9" t="n">
-        <v>251471.456493912</v>
+        <v>238748.564921736</v>
       </c>
       <c r="E9" t="n">
-        <v>346872.4762293933</v>
+        <v>338876.8500391305</v>
       </c>
     </row>
   </sheetData>
@@ -21685,7 +21964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K234"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31802,19 +32081,24 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G220" t="n">
-        <v>250</v>
+        <v>300</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>C-0545</t>
+        </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>IFC EHS Guidelines for Meat Processing (European Commission 2005 benchmark)</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Slaughter, chilling to 0 to 4 C and chilled storage. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+          <t>Cattle slaughtering uses 90 to 1,094 kWh of fuel and electricity per tonne of carcass (C-0545, C-0546). Chilling to 0 to 4 C and chilled storage dominate the electrical part; with heat from a boiler, about 150 kWh of electricity per tonne sits in the lower half of the total-energy range. To be replaced by the load study.</t>
         </is>
       </c>
       <c r="K220" t="b">
@@ -31882,7 +32166,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -31890,19 +32174,24 @@
         </is>
       </c>
       <c r="F222" t="n">
+        <v>97</v>
+      </c>
+      <c r="G222" t="n">
         <v>200</v>
       </c>
-      <c r="G222" t="n">
-        <v>500</v>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D-0092</t>
+        </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>IFC EHS Guidelines for Fish Processing (2007)</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Ice making, blast freezing and cold storage. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+          <t>Blast freezing uses about 350 MJ of energy per tonne of raw fish, an estimated 97.2 kWh (C-0564, D-0092), which the model treats as electricity because freezing plants run on electric compressors (engineering judgment); ice making and cold storage add to it. The range runs from freezing alone to a plant with long cold storage.</t>
         </is>
       </c>
       <c r="K222" t="b">
@@ -31970,7 +32259,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -31978,19 +32267,24 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G224" t="n">
-        <v>120</v>
+        <v>100</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>C-0553</t>
+        </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>IFC EHS Guidelines for Vegetable Oil Processing (European Commission 2006)</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Expellers, filtration and refining. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+          <t>Refining steps use up to 150 MJ (about 42 kWh) of electricity per tonne of oil for deodorisation (C-0553), plus neutralisation; expeller pressing adds the larger share. The range covers pressing only to pressing with full refining.</t>
         </is>
       </c>
       <c r="K224" t="b">
@@ -32058,7 +32352,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -32069,16 +32363,21 @@
         <v>50</v>
       </c>
       <c r="G226" t="n">
-        <v>100</v>
+        <v>130</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D-0084</t>
+        </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>EU BAT conclusions for grain milling (JRC 2019)</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Milling, conveying and silo aeration. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+          <t>The EU indicative level for grain milling is 0.05 to 0.13 MWh per tonne of products (C-0551, C-0552), nearly all of it electricity for mills, conveyors and aspiration. The base is the middle of the range, allowing for silo aeration.</t>
         </is>
       </c>
       <c r="K226" t="b">
@@ -32102,7 +32401,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -32110,19 +32409,24 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G227" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D-0082</t>
+        </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>IFC EHS Guidelines for Dairy Processing; EU dairy energy structure (JRC 2019)</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Chilling, pasteurisation and packing. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+          <t>The IFC industry benchmark for market milk is 0.1 to 0.2 kWh of energy per litre (C-0548, C-0549), and about 20 percent of dairy energy is electricity (C-0550), so 0.02 to 0.04 kWh of electricity per litre (D-0082, D-0083), likely a lower bound because the share includes powder plants. The base of 0.03 and the high end allow for that, for UHT and more refrigeration in a hot climate.</t>
         </is>
       </c>
       <c r="K227" t="b">
@@ -32146,7 +32450,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -32154,19 +32458,24 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G228" t="n">
-        <v>250</v>
+        <v>80</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>C-0554</t>
+        </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>None (judgment; no credible benchmark found)</t>
+          <t>ZAK soap site, Ethiopia (MIGA)</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Mixing, milling, plodding and stamping. Design estimate for a plant of this type; no metered Somali data exist (judgment). The range spans efficient and less efficient plants.</t>
+          <t>The ZAK soap site uses about 1,000 kWh of electricity a day with heat from an oil-fired boiler (C-0554). Against its capacity of 16,000 to 64,000 tonnes a year (C-0242), that is roughly 20 to 60 kWh per tonne depending on output; the base takes 40.</t>
         </is>
       </c>
       <c r="K228" t="b">
@@ -32434,6 +32743,334 @@
         </is>
       </c>
       <c r="K234" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>A-234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>irrigation.hectares</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Irrigated land converted from diesel to solar pumping by 2032</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>hectares</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G235" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>C-0562</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Afgoi district irrigated area (land-cover estimate cited in a 2026 preprint)</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>A 2026 preprint reports about 113,652 hectares of irrigated agriculture in the Afgoi district, from a 2012 remote-sensing estimate that may include irrigable land (C-0562); the Shabelle and Juba valleys irrigated 222,950 hectares before the war (C-0206). Converting 20,000 hectares, under a fifth of Afgoi's irrigated area, is a first-phase target (judgment); the programme is sized in hectares because no count of pumps exists.</t>
+        </is>
+      </c>
+      <c r="K235" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>A-235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>irrigation.water_m3_per_ha_season</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Irrigation water pumped per hectare per season</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>4151</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>m3 per hectare</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>1871</v>
+      </c>
+      <c r="G236" t="n">
+        <v>6168</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D-0091</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Afgoi district, flow-meter measurements (2026 preprint)</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Ten sampled sesame plots received on average 415.1 mm in the 2021 season (C-0563), 4,151 m3 per hectare (D-0091). The range runs from sorghum (187.1 mm) to tomato (616.8 mm) in the same study. Solar pumping should come with scheduling advice, since farmers over-irrigate most crops.</t>
+        </is>
+      </c>
+      <c r="K236" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>A-236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>irrigation.seasons_per_year</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Irrigated seasons a year (Gu and Deyr)</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>2</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>seasons</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>1</v>
+      </c>
+      <c r="G237" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Two cropping seasons a year along the rivers; some land is irrigated only once.</t>
+        </is>
+      </c>
+      <c r="K237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>A-237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>irrigation.head_m</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Total pumping head: lift from the river to the field plus pipe losses</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>8</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>5</v>
+      </c>
+      <c r="G238" t="n">
+        <v>12</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>River-bank pumps lift water over the embankment into field channels; 8 m includes friction in pipes (judgment; to be measured in the pump survey).</t>
+        </is>
+      </c>
+      <c r="K238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>A-238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>irrigation.pumpset_efficiency</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Fuel-to-water efficiency of a small diesel pump set</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>None (judgment; no credible benchmark found)</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Small diesel engines convert about a third of fuel energy to shaft work and centrifugal pumps about half of that to water, so 10 to 20 percent overall is typical of smallholder pump sets (judgment).</t>
+        </is>
+      </c>
+      <c r="K239" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>A-239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>fuel.diesel_kwh_per_litre</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Energy content of diesel</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>kWh per litre (net CV)</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="G240" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>D-0086</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>UK government conversion factors 2026</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2.66155 kg CO2e per litre divided by 0.26806 kg CO2e per kWh (D-0086).</t>
+        </is>
+      </c>
+      <c r="K240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>A-240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>irrigation.solar_capex_per_ha</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Solar pumping system cost per hectare served</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>USD per hectare</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>D-0087</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Philippines, NIA solar pump projects (2021)</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Two Philippine solar pump projects cost USD 1,100 and USD 1,788 per hectare served (D-0087, D-0088), including canal works; the base is their midpoint. Somali farm-level systems may cost less per hectare, but no Somali per-hectare figure exists.</t>
+        </is>
+      </c>
+      <c r="K241" t="b">
         <v>1</v>
       </c>
     </row>
@@ -32448,7 +33085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35864,12 +36501,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>irrigation.pumps</t>
+          <t>irrigation.hectares</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>A-145</t>
+          <t>A-234</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -35881,12 +36518,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>irrigation.diesel_litres_per_pump</t>
+          <t>irrigation.water_m3_per_ha_season</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>A-146</t>
+          <t>A-235</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -35898,29 +36535,29 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>irrigation.capex_per_pump</t>
+          <t>irrigation.seasons_per_year</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>A-147</t>
+          <t>A-236</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>irrigation.lifetime_years</t>
+          <t>irrigation.head_m</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>A-148</t>
+          <t>A-237</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -35932,80 +36569,80 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>waste.tonnes_per_year</t>
+          <t>irrigation.pumpset_efficiency</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>A-149</t>
+          <t>A-238</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>waste.capture_efficiency</t>
+          <t>fuel.diesel_kwh_per_litre</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>A-150</t>
+          <t>A-239</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>waste.lo_tco2e_per_t_mcf1</t>
+          <t>irrigation.solar_capex_per_ha</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>A-151</t>
+          <t>A-240</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>waste.capex_per_t_per_year</t>
+          <t>irrigation.lifetime_years</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>A-152</t>
+          <t>A-148</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>waste.lifetime_years</t>
+          <t>waste.tonnes_per_year</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>A-153</t>
+          <t>A-149</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -36017,63 +36654,63 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>resilience.aal_musd</t>
+          <t>waste.capture_efficiency</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>A-212</t>
+          <t>A-150</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>resilience.loss_growth</t>
+          <t>waste.lo_tco2e_per_t_mcf1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>A-213</t>
+          <t>A-151</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>resilience.drainage_coverage</t>
+          <t>waste.capex_per_t_per_year</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>A-214</t>
+          <t>A-152</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>resilience.flood_reduction</t>
+          <t>waste.lifetime_years</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>A-215</t>
+          <t>A-153</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -36085,46 +36722,46 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>resilience.capex_per_usd_avoided</t>
+          <t>resilience.aal_musd</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>A-216</t>
+          <t>A-212</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>resilience.lifetime_years</t>
+          <t>resilience.loss_growth</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>A-217</t>
+          <t>A-213</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ebus.buses</t>
+          <t>resilience.drainage_coverage</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>A-154</t>
+          <t>A-214</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -36136,12 +36773,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ebus.km_per_bus</t>
+          <t>resilience.flood_reduction</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>A-155</t>
+          <t>A-215</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -36153,46 +36790,46 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ebus.diesel_litres_per_km</t>
+          <t>resilience.capex_per_usd_avoided</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>A-156</t>
+          <t>A-216</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ebus.kwh_per_km</t>
+          <t>resilience.lifetime_years</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>A-157</t>
+          <t>A-217</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ebus.solar_charged_share</t>
+          <t>ebus.buses</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>A-158</t>
+          <t>A-154</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -36204,29 +36841,29 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ebus.capex_per_bus</t>
+          <t>ebus.km_per_bus</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>A-159</t>
+          <t>A-155</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ebus.diesel_bus_capex</t>
+          <t>ebus.diesel_litres_per_km</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>A-160</t>
+          <t>A-156</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -36238,29 +36875,29 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ebus.lifetime_years</t>
+          <t>ebus.kwh_per_km</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>A-161</t>
+          <t>A-157</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>cooking.charcoal_saved_t_per_stove</t>
+          <t>ebus.solar_charged_share</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>A-163</t>
+          <t>A-158</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -36272,63 +36909,63 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>cooking.fnrb_national</t>
+          <t>ebus.capex_per_bus</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>A-164</t>
+          <t>A-159</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>cooking.fnrb_banaadir_creditable</t>
+          <t>ebus.diesel_bus_capex</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>A-165</t>
+          <t>A-160</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>cooking.banaadir_share</t>
+          <t>ebus.lifetime_years</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>A-166</t>
+          <t>A-161</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>cooking.stove_lifetime_years</t>
+          <t>cooking.charcoal_saved_t_per_stove</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>A-169</t>
+          <t>A-163</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -36340,12 +36977,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>cooking.charcoal_price_usd_per_kg</t>
+          <t>cooking.fnrb_national</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>A-170</t>
+          <t>A-164</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -36357,112 +36994,80 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>gdp.2028</t>
+          <t>cooking.fnrb_banaadir_creditable</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>C-0020</t>
+          <t>A-165</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
           <t>none</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>16875104000</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 16.875 billion in 2028 (WEO April 2026).</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>gdp.2029</t>
+          <t>cooking.banaadir_share</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>C-0021</t>
+          <t>A-166</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>18340870000</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 18.341 billion in 2029 (WEO April 2026).</t>
+          <t>down</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>gdp.2030</t>
+          <t>cooking.stove_lifetime_years</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>C-0022</t>
+          <t>A-169</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>19851193000</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 19.851 billion in 2030 (WEO April 2026).</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>gdp.2031</t>
+          <t>cooking.charcoal_price_usd_per_kg</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>C-0023</t>
+          <t>A-170</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>21991019000</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>IMF projects Somalia's GDP at current prices, USD at USD 21.991 billion in 2031 (WEO April 2026).</t>
+          <t>up</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>fuel.diesel_kgco2e_per_litre</t>
+          <t>gdp.2028</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>C-0306</t>
+          <t>C-0020</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -36471,23 +37076,23 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>2.66155</v>
+        <v>16875104000</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>The UK Government's 2026 conversion factors put direct (Scope 1) emissions from burning 100% mineral diesel at 2.66155 kg CO2e per litre.</t>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 16.875 billion in 2028 (WEO April 2026).</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>waste.mcf_baseline</t>
+          <t>gdp.2029</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>C-0319</t>
+          <t>C-0021</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -36496,23 +37101,23 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.6</v>
+        <v>18340870000</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>The IPCC default methane correction factor for an uncategorised disposal site is 0.6.</t>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 18.341 billion in 2029 (WEO April 2026).</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>waste.mcf_project</t>
+          <t>gdp.2030</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>C-0318</t>
+          <t>C-0022</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -36521,34 +37126,184 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>19851193000</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>The IPCC default methane correction factor for a managed anaerobic disposal site is 1.0.</t>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 19.851 billion in 2030 (WEO April 2026).</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
+          <t>gdp.2031</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>C-0023</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>21991019000</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>IMF projects Somalia's GDP at current prices, USD at USD 21.991 billion in 2031 (WEO April 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>fuel.diesel_kgco2e_per_litre</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>C-0306</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>2.66155</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>The UK Government's 2026 conversion factors put direct (Scope 1) emissions from burning 100% mineral diesel at 2.66155 kg CO2e per litre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>fuel.diesel_price_before_shock</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>C-0039</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Domestic fuel prices in Mogadishu rose from USD 0.60 to USD 1.50 per litre within days of the escalation of the Iran conflict in late February 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>fuel.diesel_price_after_shock</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>C-0040</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Domestic fuel prices in Mogadishu reached about USD 1.50 per litre after the escalation of the Iran conflict in late February 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>waste.mcf_baseline</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>C-0319</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>The IPCC default methane correction factor for an uncategorised disposal site is 0.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>waste.mcf_project</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>C-0318</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>The IPCC default methane correction factor for a managed anaerobic disposal site is 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
           <t>cooking.co2_per_t_charcoal</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>D-0029</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D237" t="n">
+      <c r="D243" t="n">
         <v>3.3</v>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>Burning a tonne of charcoal releases about 3.30 tonnes of CO2 on IPCC defaults (29.5 TJ per Gg, 112,000 kg CO2 per TJ). This CO2 is biogenic and is excluded from national inventory totals; methane and nitrous oxide are not included.</t>
         </is>
@@ -59099,10 +59854,10 @@
         <v>2028</v>
       </c>
       <c r="D2" t="n">
-        <v>117.06564</v>
+        <v>106.64412</v>
       </c>
       <c r="E2" t="n">
-        <v>1215918.31557585</v>
+        <v>1107673.769660071</v>
       </c>
       <c r="F2" t="n">
         <v>-6.843106392136601</v>
@@ -59123,10 +59878,10 @@
         <v>2029</v>
       </c>
       <c r="D3" t="n">
-        <v>741.41572</v>
+        <v>675.4127599999999</v>
       </c>
       <c r="E3" t="n">
-        <v>3647754.94672755</v>
+        <v>3323021.308980213</v>
       </c>
       <c r="F3" t="n">
         <v>-6.843106392136601</v>
@@ -59147,10 +59902,10 @@
         <v>2030</v>
       </c>
       <c r="D4" t="n">
-        <v>2029.13776</v>
+        <v>1848.49808</v>
       </c>
       <c r="E4" t="n">
-        <v>4863673.262303399</v>
+        <v>4430695.078640284</v>
       </c>
       <c r="F4" t="n">
         <v>-6.843106392136601</v>
@@ -59171,10 +59926,10 @@
         <v>2031</v>
       </c>
       <c r="D5" t="n">
-        <v>3590.01296</v>
+        <v>3270.41968</v>
       </c>
       <c r="E5" t="n">
-        <v>4863673.262303398</v>
+        <v>4430695.078640283</v>
       </c>
       <c r="F5" t="n">
         <v>-6.843106392136601</v>
@@ -59195,10 +59950,10 @@
         <v>2032</v>
       </c>
       <c r="D6" t="n">
-        <v>5150.88816</v>
+        <v>4692.34128</v>
       </c>
       <c r="E6" t="n">
-        <v>4863673.2623034</v>
+        <v>4430695.078640286</v>
       </c>
       <c r="F6" t="n">
         <v>-6.843106392136601</v>
@@ -59219,13 +59974,13 @@
         <v>2028</v>
       </c>
       <c r="D7" t="n">
-        <v>59.884875</v>
+        <v>5.124564250849697</v>
       </c>
       <c r="E7" t="n">
-        <v>400000</v>
+        <v>900000</v>
       </c>
       <c r="F7" t="n">
-        <v>158.7316480366227</v>
+        <v>9875.456716009954</v>
       </c>
     </row>
     <row r="8">
@@ -59243,13 +59998,13 @@
         <v>2029</v>
       </c>
       <c r="D8" t="n">
-        <v>379.270875</v>
+        <v>32.45557358871475</v>
       </c>
       <c r="E8" t="n">
-        <v>1200000</v>
+        <v>2700000</v>
       </c>
       <c r="F8" t="n">
-        <v>158.7316480366227</v>
+        <v>9875.456716009954</v>
       </c>
     </row>
     <row r="9">
@@ -59267,13 +60022,13 @@
         <v>2030</v>
       </c>
       <c r="D9" t="n">
-        <v>1038.0045</v>
+        <v>88.82578034806143</v>
       </c>
       <c r="E9" t="n">
-        <v>1600000</v>
+        <v>3600000</v>
       </c>
       <c r="F9" t="n">
-        <v>158.7316480366227</v>
+        <v>9875.456716009954</v>
       </c>
     </row>
     <row r="10">
@@ -59291,13 +60046,13 @@
         <v>2031</v>
       </c>
       <c r="D10" t="n">
-        <v>1836.4695</v>
+        <v>157.1533036927241</v>
       </c>
       <c r="E10" t="n">
-        <v>1600000</v>
+        <v>3599999.999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>158.7316480366227</v>
+        <v>9875.456716009954</v>
       </c>
     </row>
     <row r="11">
@@ -59315,13 +60070,13 @@
         <v>2032</v>
       </c>
       <c r="D11" t="n">
-        <v>2634.9345</v>
+        <v>225.4808270373867</v>
       </c>
       <c r="E11" t="n">
-        <v>1600000</v>
+        <v>3600000.000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>158.7316480366227</v>
+        <v>9875.456716009954</v>
       </c>
     </row>
     <row r="12">
@@ -59699,10 +60454,10 @@
         <v>2028</v>
       </c>
       <c r="D27" t="n">
-        <v>2556.178799999999</v>
+        <v>2269.8984</v>
       </c>
       <c r="E27" t="n">
-        <v>5911761.348374966</v>
+        <v>5249670.964276121</v>
       </c>
       <c r="F27" t="n">
         <v>-412.1244334084436</v>
@@ -59723,10 +60478,10 @@
         <v>2029</v>
       </c>
       <c r="D28" t="n">
-        <v>8520.595999999998</v>
+        <v>7566.328</v>
       </c>
       <c r="E28" t="n">
-        <v>7882348.464499954</v>
+        <v>6999561.285701495</v>
       </c>
       <c r="F28" t="n">
         <v>-412.1244334084436</v>
@@ -59747,10 +60502,10 @@
         <v>2030</v>
       </c>
       <c r="D29" t="n">
-        <v>16189.1324</v>
+        <v>14376.0232</v>
       </c>
       <c r="E29" t="n">
-        <v>9852935.580624944</v>
+        <v>8749451.607126869</v>
       </c>
       <c r="F29" t="n">
         <v>-412.1244334084436</v>
@@ -59771,10 +60526,10 @@
         <v>2031</v>
       </c>
       <c r="D30" t="n">
-        <v>23857.6688</v>
+        <v>21185.7184</v>
       </c>
       <c r="E30" t="n">
-        <v>7882348.464499957</v>
+        <v>6999561.285701497</v>
       </c>
       <c r="F30" t="n">
         <v>-412.1244334084436</v>
@@ -59795,10 +60550,10 @@
         <v>2032</v>
       </c>
       <c r="D31" t="n">
-        <v>30674.1456</v>
+        <v>27238.7808</v>
       </c>
       <c r="E31" t="n">
-        <v>7882348.464499953</v>
+        <v>6999561.285701493</v>
       </c>
       <c r="F31" t="n">
         <v>-412.1244334084436</v>
@@ -59819,13 +60574,13 @@
         <v>2028</v>
       </c>
       <c r="D32" t="n">
-        <v>998.08125</v>
+        <v>485.0925484189326</v>
       </c>
       <c r="E32" t="n">
-        <v>1500000</v>
+        <v>4350000</v>
       </c>
       <c r="F32" t="n">
-        <v>-276.9260191336836</v>
+        <v>213.765495175369</v>
       </c>
     </row>
     <row r="33">
@@ -59843,13 +60598,13 @@
         <v>2029</v>
       </c>
       <c r="D33" t="n">
-        <v>3326.9375</v>
+        <v>1616.975161396442</v>
       </c>
       <c r="E33" t="n">
-        <v>2000000</v>
+        <v>5799999.999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-276.9260191336836</v>
+        <v>213.765495175369</v>
       </c>
     </row>
     <row r="34">
@@ -59867,13 +60622,13 @@
         <v>2030</v>
       </c>
       <c r="D34" t="n">
-        <v>6321.18125</v>
+        <v>3072.25280665324</v>
       </c>
       <c r="E34" t="n">
-        <v>2500000</v>
+        <v>7250000</v>
       </c>
       <c r="F34" t="n">
-        <v>-276.9260191336836</v>
+        <v>213.765495175369</v>
       </c>
     </row>
     <row r="35">
@@ -59891,13 +60646,13 @@
         <v>2031</v>
       </c>
       <c r="D35" t="n">
-        <v>9315.424999999999</v>
+        <v>4527.530451910037</v>
       </c>
       <c r="E35" t="n">
-        <v>2000000</v>
+        <v>5800000.000000002</v>
       </c>
       <c r="F35" t="n">
-        <v>-276.9260191336836</v>
+        <v>213.765495175369</v>
       </c>
     </row>
     <row r="36">
@@ -59915,13 +60670,13 @@
         <v>2032</v>
       </c>
       <c r="D36" t="n">
-        <v>11976.975</v>
+        <v>5821.110581027191</v>
       </c>
       <c r="E36" t="n">
-        <v>2000000</v>
+        <v>5799999.999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-276.9260191336836</v>
+        <v>213.765495175369</v>
       </c>
     </row>
     <row r="37">
@@ -60299,10 +61054,10 @@
         <v>2028</v>
       </c>
       <c r="D52" t="n">
-        <v>16477.8348</v>
+        <v>14142.079</v>
       </c>
       <c r="E52" t="n">
-        <v>14886408.9741594</v>
+        <v>12776239.97898505</v>
       </c>
       <c r="F52" t="n">
         <v>-677.5362002721241</v>
@@ -60323,10 +61078,10 @@
         <v>2029</v>
       </c>
       <c r="D53" t="n">
-        <v>40017.59879999999</v>
+        <v>34345.049</v>
       </c>
       <c r="E53" t="n">
-        <v>14886408.9741594</v>
+        <v>12776239.97898505</v>
       </c>
       <c r="F53" t="n">
         <v>-677.5362002721241</v>
@@ -60347,10 +61102,10 @@
         <v>2030</v>
       </c>
       <c r="D54" t="n">
-        <v>63557.3628</v>
+        <v>54548.019</v>
       </c>
       <c r="E54" t="n">
-        <v>14886408.9741594</v>
+        <v>12776239.97898505</v>
       </c>
       <c r="F54" t="n">
         <v>-677.5362002721241</v>
@@ -60371,10 +61126,10 @@
         <v>2031</v>
       </c>
       <c r="D55" t="n">
-        <v>80505.99288000001</v>
+        <v>69094.1574</v>
       </c>
       <c r="E55" t="n">
-        <v>8931845.384495642</v>
+        <v>7665743.987391035</v>
       </c>
       <c r="F55" t="n">
         <v>-677.5362002721241</v>
@@ -60395,10 +61150,10 @@
         <v>2032</v>
       </c>
       <c r="D56" t="n">
-        <v>91334.28431999999</v>
+        <v>78387.52359999999</v>
       </c>
       <c r="E56" t="n">
-        <v>5954563.589663759</v>
+        <v>5110495.991594021</v>
       </c>
       <c r="F56" t="n">
         <v>-677.5362002721241</v>
@@ -60419,13 +61174,13 @@
         <v>2028</v>
       </c>
       <c r="D57" t="n">
-        <v>7452.34</v>
+        <v>7568.42539287009</v>
       </c>
       <c r="E57" t="n">
-        <v>4000000</v>
+        <v>11000000</v>
       </c>
       <c r="F57" t="n">
-        <v>-525.3133667137005</v>
+        <v>-459.9584955010438</v>
       </c>
     </row>
     <row r="58">
@@ -60443,13 +61198,13 @@
         <v>2029</v>
       </c>
       <c r="D58" t="n">
-        <v>18098.54</v>
+        <v>18380.46166839879</v>
       </c>
       <c r="E58" t="n">
-        <v>4000000</v>
+        <v>11000000</v>
       </c>
       <c r="F58" t="n">
-        <v>-525.3133667137005</v>
+        <v>-459.9584955010438</v>
       </c>
     </row>
     <row r="59">
@@ -60467,13 +61222,13 @@
         <v>2030</v>
       </c>
       <c r="D59" t="n">
-        <v>28744.74</v>
+        <v>29192.49794392749</v>
       </c>
       <c r="E59" t="n">
-        <v>4000000</v>
+        <v>11000000</v>
       </c>
       <c r="F59" t="n">
-        <v>-525.3133667137005</v>
+        <v>-459.9584955010438</v>
       </c>
     </row>
     <row r="60">
@@ -60491,13 +61246,13 @@
         <v>2031</v>
       </c>
       <c r="D60" t="n">
-        <v>36410.004</v>
+        <v>36977.16406230815</v>
       </c>
       <c r="E60" t="n">
-        <v>2400000</v>
+        <v>6600000.000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-525.3133667137005</v>
+        <v>-459.9584955010438</v>
       </c>
     </row>
     <row r="61">
@@ -60515,13 +61270,13 @@
         <v>2032</v>
       </c>
       <c r="D61" t="n">
-        <v>41307.256</v>
+        <v>41950.70074905136</v>
       </c>
       <c r="E61" t="n">
-        <v>1600000</v>
+        <v>4399999.999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>-525.3133667137005</v>
+        <v>-459.9584955010438</v>
       </c>
     </row>
     <row r="62">
